--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -11557,10 +11557,14 @@
       </c>
       <c r="J14" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K14" s="67" t="n"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="K14" s="67" t="inlineStr">
+        <is>
+          <t>All 32 tables (tab04 lists 32, not 26) created via numbered Kysely migrations against a live Supabase dev project (examprep-ai-dev). Full up/down/up round-trip verified manually. CI workflow (.github/workflows/migrations.yml) written but unverified end to end pending a GitHub remote (same blocker as F001). DB choice: Supabase (Postgres 17), auth stays better-auth per CLAUDE.md — RLS is off pending M20.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="23.25" customHeight="1" s="59">
       <c r="A15" s="67" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -11663,10 +11663,14 @@
       </c>
       <c r="J16" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K16" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K16" s="67" t="inlineStr">
+        <is>
+          <t>Kysely types generated from the live schema (kysely-codegen, src/db/types.ts), with hand-written literal-union overrides (src/db/enums.ts) for CHECK-constrained columns since Postgres CHECK constraints are not introspectable as enums. Repository-per-entity pattern in src/db/repositories/ (grouped by module: identity, curriculum, questions, papers, attempts, evaluations, tracking, ops); tables with a direct household_id/student_id column require that scope as a parameter on every read, verified at runtime (cross-household query returns zero rows, not an error). No delete method anywhere per invariant 4. "No raw untyped SQL in feature code" enforced by an eslint no-restricted-imports rule blocking pg/kysely imports outside src/db/**, verified it actually fires.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="59">
       <c r="A17" s="67" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -11302,10 +11302,14 @@
       </c>
       <c r="J9" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K9" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K9" s="67" t="inlineStr">
+        <is>
+          <t>better-auth mounted at /api/auth/$ (catch-all, src/routes/api/auth/$.ts). Email+password with required email verification (verified end-to-end: sign-up -&gt; logged verification link -&gt; verify-email -&gt; sign-in). Google OAuth wired but conditional on GOOGLE_CLIENT_ID/SECRET, which are not set in dev -- needs real credentials before it is testable. Session cookie confirmed httpOnly+SameSite=Lax via curl; Secure is added automatically once BETTER_AUTH_URL is https in prod. Sign-out/session endpoints come from betterauth's own router, not hand-written. Resend (M16) does not exist yet, so verification emails are logged server-side, not delivered -- flagged, not silently faked.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="23.25" customHeight="1" s="59">
       <c r="A10" s="67" t="inlineStr">
@@ -11353,10 +11357,14 @@
       </c>
       <c r="J10" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K10" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K10" s="67" t="inlineStr">
+        <is>
+          <t>Role stored on users.role (parent/student/admin), assigned server-side only (better-auth additionalFields role/household_id have input:false; a signup payload cannot set them). src/lib/session.ts requireUser/requireRole enforce auth on the request itself. Verified live: unauthenticated request to GET /api/students -&gt; 401; a directly-seeded student-role user -&gt; 403 on GET and POST /api/students. No admin or evaluation-override route exists yet to test T01 literally against, but the same guard is what any future one will use.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="23.25" customHeight="1" s="59">
       <c r="A11" s="67" t="inlineStr">
@@ -11404,10 +11412,14 @@
       </c>
       <c r="J11" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K11" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K11" s="67" t="inlineStr">
+        <is>
+          <t>GET/POST /api/students and PATCH /api/students/:id (src/routes/api/students.ts, .../students/.ts), all household-scoped via studentsRepository (F013). Verified live with two separate parent signups: parent B's list is empty and never sees parent A's student; parent B's PATCH on parent A's student returns 404, not 403 or a leaked row. No student switcher UI yet -- no screens exist in src/ at all still, this is API-layer only.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="23.25" customHeight="1" s="59">
       <c r="A12" s="67" t="inlineStr">
@@ -11458,7 +11470,11 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K12" s="67" t="n"/>
+      <c r="K12" s="67" t="inlineStr">
+        <is>
+          <t>All listed fields (name, class, section, roll_no, board, school, target_exams) already exist on students via F011/F013 and are settable through the F008 endpoints. Left Not Started because the AC's 'used in paper header automatically' cannot be verified until M07 (paper rendering) exists -- marking Done now would be checking a box the spec does not actually let me check yet.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="23.25" customHeight="1" s="59">
       <c r="A13" s="67" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -11785,10 +11785,14 @@
       </c>
       <c r="J18" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K18" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K18" s="67" t="inlineStr">
+        <is>
+          <t>Scoped down with the user's agreement: tab05 lists no create/update routes for subjects/chapters/concepts (only reads + scope-writing), and the project's own M17 skills (examprep-ingest-source, examprep-scope-authoring) are the intended authoring path, not a REST CRUD API. Built GET /api/syllabus/subjects and GET /api/syllabus/chapters (with live IN/OUT scope counts via a join) plus src/db/seed.ts, a minimal *test fixture* (clearly labelled '(seed)', not real approved curriculum -- the scope-authoring skill explicitly warns against fabricating scope from memory). Soft delete / retire is not implemented for subjects/chapters/concepts -- no lifecycle column exists on those tables yet; flagged for M17, not solved here.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="23.25" customHeight="1" s="59">
       <c r="A19" s="67" t="inlineStr">
@@ -11836,10 +11840,14 @@
       </c>
       <c r="J19" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K19" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K19" s="67" t="inlineStr">
+        <is>
+          <t>GET and POST /api/syllabus/chapters/:id/scope (src/routes/api/syllabus/chapters//scope.ts), POST restricted to admin role. Verified live: a non-admin gets 403, an admin's POST creates IN/OUT rows, and GET /api/syllabus/chapters correctly reflects live in_scope_count/out_scope_count via a join. The generator refusing out-of-scope concepts (the other half of this AC) can't be verified until the generator exists (M06).</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="23.25" customHeight="1" s="59">
       <c r="A20" s="67" t="inlineStr">
@@ -11887,10 +11895,14 @@
       </c>
       <c r="J20" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K20" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K20" s="67" t="inlineStr">
+        <is>
+          <t>sources table + repository already existed from F011/F013; no additional route needed beyond what chapters already expose (source_id, and chapter creation happens via the skill/seed path per F015's resolution, not a REST endpoint).</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="23.25" customHeight="1" s="59">
       <c r="A21" s="67" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -12052,10 +12052,14 @@
       </c>
       <c r="J23" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K23" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K23" s="67" t="inlineStr">
+        <is>
+          <t>POST/GET /api/questions, PATCH /api/questions/:id (admin-only). Question+options+step_marks written as one transaction (src/lib/questions.ts). Type-specific validation via Zod: mcq requires exactly one correct option. Verified live end to end.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="23.25" customHeight="1" s="59">
       <c r="A24" s="67" t="inlineStr">
@@ -12103,10 +12107,14 @@
       </c>
       <c r="J24" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K24" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K24" s="67" t="inlineStr">
+        <is>
+          <t>Step marks stored in question_step_marks (F011/F013); creation validates sum(step_marks.marks) === question.marks server-side, verified live (mismatched sum -&gt; 400 with the actual vs expected numbers in the message).</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="23.25" customHeight="1" s="59">
       <c r="A25" s="67" t="inlineStr">
@@ -16854,12 +16862,12 @@
       </c>
       <c r="J117" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K117" s="67" t="inlineStr">
         <is>
-          <t>Added from parent requirements, 05 Sep 2026</t>
+          <t>Already schema-complete from F011 (questions.difficulty / concepts.difficulty_base check(Easy|Hard|Hardest)). Written calibration rules per tier and per subject are domain-expert content, not code -- not fabricated here, left for whoever authors the actual curriculum content. "Paper reports its actual tier mix" is M06.</t>
         </is>
       </c>
     </row>
@@ -17019,12 +17027,12 @@
       </c>
       <c r="J120" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K120" s="67" t="inlineStr">
         <is>
-          <t>Added from parent requirements, 05 Sep 2026</t>
+          <t>src/lib/questions.ts computeReviewTier() assigns tier deterministically from the question's own shape (marks, type, language, diagram) -- never admin-discretionary, matching the skill's 'never mark Tier A to avoid review' rule. Tier A auto-approves at creation; Tier B stays draft until POST /api/questions/:id/approve, which requires a reviewer note for Tier B (verified: rejected with 400 when missing) and records reviewed_by/reviewed_at for audit (migration 0037). The 'sampled QA check' on auto-approved Tier A items is not built -- no sampling mechanism exists yet.</t>
         </is>
       </c>
     </row>
@@ -17294,12 +17302,12 @@
       </c>
       <c r="J125" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K125" s="67" t="inlineStr">
         <is>
-          <t>Added 05 Sep 2026 — keeps the 20-per-concept launch upgradable</t>
+          <t>concepts.target_question_count added (migration 0037), not null default 20 matching the launch target. Per-concept override already works via PATCH-style updates on concepts (no dedicated route yet since F015 has no concept PATCH endpoint either -- same skills-driven scoping decision). The actual top-up generation job (target minus current approved count per cell) is F025/F116 -- AI generation -- not built this pass.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -14151,10 +14151,14 @@
       </c>
       <c r="J64" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K64" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K64" s="67" t="inlineStr">
+        <is>
+          <t>concept_mastery ledger (F011/F013) + src/lib/mastery.ts recordMasteryAttempt(), which is a service function, not a route -- nothing in the app can call it yet since it is meant to run when an evaluation is confirmed (POST /api/evaluations/:id/confirm, M09), which does not exist. Verified via a fixture chain (blueprint-&gt;paper-&gt;attempt-&gt;evaluation created directly through existing repositories) that the ledger writes correctly and ratios/dates are recorded as append-only rows.</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="23.25" customHeight="1" s="59">
       <c r="A65" s="67" t="inlineStr">
@@ -14202,10 +14206,14 @@
       </c>
       <c r="J65" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K65" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K65" s="67" t="inlineStr">
+        <is>
+          <t>Status thresholds (Strong&gt;=80/Needs Practice 50-79/Weak&lt;50) and trend (vs average of last 2 prior ratios) implemented in src/lib/mastery.ts, verified live through a 4-attempt sequence. Thresholds are named constants in one place ("configurable" in the sense of easy to change; not exposed as an admin-editable setting since no admin UI exists).</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="23.25" customHeight="1" s="59">
       <c r="A66" s="67" t="inlineStr">
@@ -14253,10 +14261,14 @@
       </c>
       <c r="J66" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K66" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K66" s="67" t="inlineStr">
+        <is>
+          <t>Weak-twice-&gt;Priority and &gt;=85%-twice-&gt;Maintenance both verified live end to end, including the bug caught during testing where Priority was incorrectly clearing after a single good score (fixed: Priority now persists as the stored status until the explicit two-in-a-row recovery, not just checked against the last ledger row's label). "Retire only after three" does not map onto a schema value -- concept_status.status is a fixed 5-value CHECK with no Retired option, not added this pass. The auto-triggered 5-question mini test is not built -- needs the paper generator (M06).</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="23.25" customHeight="1" s="59">
       <c r="A67" s="67" t="inlineStr">
@@ -14304,10 +14316,14 @@
       </c>
       <c r="J67" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K67" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K67" s="67" t="inlineStr">
+        <is>
+          <t>GET /api/tracker/:studentId (only M12 route tab05 lists), household-scoped like every other student-facing route, with subject_id/status filters -- verified live including the cross-household 404. Sortable table view, CSV/PDF export, and the screen itself are tab06 UI work; no screens exist anywhere in this repo yet, consistent with everything built so far being API-only.</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="23.25" customHeight="1" s="59">
       <c r="A68" s="67" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -12417,10 +12417,14 @@
       </c>
       <c r="J30" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K30" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K30" s="67" t="inlineStr">
+        <is>
+          <t>GET/POST /api/blueprints (admin-only POST), sections/bloom_targets/choice_rules as jsonb. total_marks is server-derived from sections, not client-supplied. choice_rules is accepted and stored but not used by the generator (F030 deferred). Verified live: non-admin POST -&gt; 403, admin POST -&gt; 201 with correct derived total_marks.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="23.25" customHeight="1" s="59">
       <c r="A31" s="67" t="inlineStr">
@@ -12468,10 +12472,14 @@
       </c>
       <c r="J31" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K31" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K31" s="67" t="inlineStr">
+        <is>
+          <t>src/lib/papers.ts generatePaper() buckets concepts into weak+priority / needs-practice / strong per the student's concept_status (no-status concepts default to needs-practice) and apportions each section's slots 40/40/20 via largest-remainder rounding so counts always sum exactly. Actual achieved bucket mix is written to papers.weighting.actual. Verified live end to end with a real weak/neutral/strong concept fixture -- correct per-bucket question counts, including a supply-constrained run that exercised partial fulfilment correctly.</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="23.25" customHeight="1" s="59">
       <c r="A32" s="67" t="inlineStr">
@@ -12519,10 +12527,14 @@
       </c>
       <c r="J32" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K32" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K32" s="67" t="inlineStr">
+        <is>
+          <t>Actual Bloom mix is computed post-selection and compared to blueprint.bloom_targets; any Bloom level off by more than 5 percentage points is appended to papers.shortfalls with the actual vs target numbers, verified live in the supply-constrained test run (correctly flagged both a 12pp Remember and 12pp Understand deviation once shortfalls skewed the mix).</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="23.25" customHeight="1" s="59">
       <c r="A33" s="67" t="inlineStr">
@@ -12621,10 +12633,14 @@
       </c>
       <c r="J34" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K34" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K34" s="67" t="inlineStr">
+        <is>
+          <t>POST /api/papers/:id/regenerate-slot swaps one slot in place (same concept/bloom/marks as the slot being replaced, excluding every question already used in that paper) without touching any other paper_questions row -- 'lock others' is inherent since only the named slot is ever updated. Verified live: regenerated a slot to a different question of the same shape, and confirmed cross-household denial (404). Drag-and-drop UI obviously doesn't exist -- no screens exist in this repo at all -- this is the API half only.</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="23.25" customHeight="1" s="59">
       <c r="A35" s="67" t="inlineStr">
@@ -12672,10 +12688,14 @@
       </c>
       <c r="J35" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K35" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K35" s="67" t="inlineStr">
+        <is>
+          <t>Unfillable slots do not block generation -- the paper is produced with a shortfalls entry naming the exact section, bucket, and constraint (bloom/difficulty/marks) that had no eligible approved question. Verified live: a deliberately undersupplied fixture (1 eligible question per bucket where 2 were needed) generated a 6-question paper instead of erroring, with 2 shortfall entries pinpointing exactly which slots came up short.</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="23.25" customHeight="1" s="59">
       <c r="A36" s="67" t="inlineStr">
@@ -17153,12 +17173,12 @@
       </c>
       <c r="J122" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K122" s="67" t="inlineStr">
         <is>
-          <t>Added from parent requirements, 05 Sep 2026</t>
+          <t>difficulty_ceiling only narrows the difficulty tiers passed to the eligible-question query (difficultiesUpTo helper); the 40/40/20 concept bucketing runs identically regardless of ceiling and always before difficulty filtering is applied within a bucket, so a student picking Easy cannot dodge weak-concept weighting. papers.weighting.actual discloses the real mix achieved. Not separately load-bearing-tested against Hard/Hardest fixtures this pass since the fixture data was all Easy-tier -- the ceiling logic itself is a 3-line pure slice, low risk.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -13049,10 +13049,14 @@
       </c>
       <c r="J42" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K42" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K42" s="67" t="inlineStr">
+        <is>
+          <t>Server side only: POST /api/attempts records a server-side started_at, and POST /api/attempts/:id/submit computes duration_used_sec from it -- this is the honest server half of the AC. Countdown UI, visible section navigator, 10-minute warning, and genuine auto-submit-at-zero all need a client timer or a background job; none exist. No screens exist anywhere in this repo, and no background-job infra is installed (tab09 names Inngest/Trigger.dev, neither chosen).</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="23.25" customHeight="1" s="59">
       <c r="A43" s="67" t="inlineStr">
@@ -13100,10 +13104,14 @@
       </c>
       <c r="J43" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K43" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K43" s="67" t="inlineStr">
+        <is>
+          <t>PATCH /api/attempts/:id/answer is the autosave endpoint itself -- one upsert per call on the (attempt_id, paper_question_id) unique constraint from F011, verified live. The "within 2s" debounce and "resume at the same question" are client behaviour; the server makes resume possible (GET /api/papers/:id + the saved attempt_answers already give a client everything needed to restore state) but no client exists to do it.</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="23.25" customHeight="1" s="59">
       <c r="A44" s="67" t="inlineStr">
@@ -13151,10 +13159,14 @@
       </c>
       <c r="J44" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K44" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K44" s="67" t="inlineStr">
+        <is>
+          <t>time_spent_sec is accepted and stored per answer via PATCH /api/attempts/:id/answer (verified live). The pacing-anomaly report ('flags questions consuming &gt;2x their mark-proportional time budget') is not built -- that is an analysis/reporting endpoint over this data, not storage, and no such route is listed in tab05.</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="23.25" customHeight="1" s="59">
       <c r="A45" s="67" t="inlineStr">
@@ -13202,10 +13214,14 @@
       </c>
       <c r="J45" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K45" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K45" s="67" t="inlineStr">
+        <is>
+          <t>Schema already carries whatever shape each type needs (attempt_answers.response_text / selected_option); the PATCH /answer endpoint accepts both generically and does not care which input widget produced them. Radio/textarea/rich-text/math-symbol widgets are UI components -- not applicable without screens.</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="23.25" customHeight="1" s="59">
       <c r="A46" s="67" t="inlineStr">
@@ -13253,10 +13269,14 @@
       </c>
       <c r="J46" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K46" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K46" s="67" t="inlineStr">
+        <is>
+          <t>The blank-answer block is real and server-enforced, not just a UI nag (T11): POST /api/attempts/:id/submit computes which paper_questions have no non-empty answer and returns 409 with the exact blank question positions unless the client resubmits with confirm_blanks:true. Verified live: submitting with 1 of 3 blank -&gt; 409 naming position 3; resubmitting with the override -&gt; closes the attempt. The review grid itself (answered/unanswered/flagged visual) is UI, not built.</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="23.25" customHeight="1" s="59">
       <c r="A47" s="67" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -13324,10 +13324,14 @@
       </c>
       <c r="J47" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K47" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K47" s="67" t="inlineStr">
+        <is>
+          <t>src/lib/scoring.ts scoreObjectiveAnswer(), matching tab07 AI-04 exactly ('deterministic code, no AI'). normalizeAnswer() strips case/commas/currency-percent-degree symbols/common unit words so Indian '1,00,000' and international '100,000' grouping compare equal. Verified live: a correct MCQ auto-scored full marks with zero AI involvement.</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="23.25" customHeight="1" s="59">
       <c r="A48" s="67" t="inlineStr">
@@ -13375,10 +13379,14 @@
       </c>
       <c r="J48" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K48" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K48" s="67" t="inlineStr">
+        <is>
+          <t>src/lib/ai-grading.ts gradeSubjectiveAnswer() implements AI-05 (Claude Sonnet, tab07's 'strong model' tier): proposes marks per step with justification, error_type, and feedback as JSON, written to ai_marks/ai_error_type -- never to marks_awarded/error_type directly, so nothing it produces counts until a human confirms (CLAUDE.md hard rule). Gracefully returns null with no ANTHROPIC_API_KEY configured (none is, in this dev environment), and the caller falls back to tab07's own documented fallback ('needs manual marking'), verified live. Real AI grading itself is UNTESTED end-to-end -- needs a real API key to exercise.</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="23.25" customHeight="1" s="59">
       <c r="A49" s="67" t="inlineStr">
@@ -13426,10 +13434,14 @@
       </c>
       <c r="J49" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K49" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K49" s="67" t="inlineStr">
+        <is>
+          <t>The 6-category error_type is now a real CHECK constraint (migration 0038), not free text. Objective wrong answers default to Conceptual Gap (an objective question can't show *why* it was wrong without shown work); subjective error_type comes from AI-05's classification when available. Verified live end to end as part of the full evaluate flow.</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="23.25" customHeight="1" s="59">
       <c r="A50" s="67" t="inlineStr">
@@ -13477,10 +13489,14 @@
       </c>
       <c r="J50" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K50" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K50" s="67" t="inlineStr">
+        <is>
+          <t>PATCH /api/evaluations/:id/items/:itemId: any evaluation item is editable up until confirm (409 after), the original AI value survives untouched in ai_marks/ai_error_type (marks_awarded/error_type are the only fields the PATCH touches), and every override writes a full before/after audit_log row. Verified live: overrode a needs-manual-marking item to 3/3, confirmed the audit_log row captured the exact before/after JSON, and confirmed a second PATCH after confirm() correctly 409s.</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="23.25" customHeight="1" s="59">
       <c r="A51" s="67" t="inlineStr">
@@ -13579,10 +13595,14 @@
       </c>
       <c r="J52" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K52" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K52" s="67" t="inlineStr">
+        <is>
+          <t>templateFeedback() in src/lib/scoring.ts implements tab07 AI-08's documented fallback ('template feedback from error type') -- used for every objective error (which is never AI-graded) and whenever subjective AI grading is unavailable. Real AI-authored feedback (the higher-quality path) comes from gradeSubjectiveAnswer's 'feedback' field when AI-05 runs, same caveat as F045: untested live without an API key.</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="23.25" customHeight="1" s="59">
       <c r="A53" s="67" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -13905,10 +13905,14 @@
       </c>
       <c r="J58" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K58" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K58" s="67" t="inlineStr">
+        <is>
+          <t>knowledge_known was already collectible per item via F047's PATCH endpoint (built in M09); this feature is the missing computation: Knowledge Score = actual_score plus every lost mark where the reviewer marked knowledge_known=true, computed in confirmEvaluation(). Verified live: two 1-mark items both scored 0, one marked knowledge_known=false (real gap) and one true (delivery issue) -&gt; knowledge_score=1, crediting back exactly the delivery-issue mark.</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="23.25" customHeight="1" s="59">
       <c r="A59" s="67" t="inlineStr">
@@ -13956,10 +13960,14 @@
       </c>
       <c r="J59" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K59" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K59" s="67" t="inlineStr">
+        <is>
+          <t>delivery_gap = knowledge_score - actual_score, computed and stored at confirm time alongside percentage and a grade band. Verified live (delivery_gap=1 in the same test). 'Charted over time against a configurable target' is a tab06 dashboard/chart concern -- no screens exist in this repo, so only the underlying per-evaluation number is built, not the rollup or chart.</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="23.25" customHeight="1" s="59">
       <c r="A60" s="67" t="inlineStr">
@@ -14007,10 +14015,14 @@
       </c>
       <c r="J60" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K60" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K60" s="67" t="inlineStr">
+        <is>
+          <t>The 6 named patterns (One-Idea Stop, Blank Retreat, First-Plausible Commit, Label Flip, Rule Over-Extension, Format Miss) seeded as real, editable patterns rows (npm run db:seed:patterns, idempotent -- verified by running it twice) rather than hardcoded in code, matching the AC's 'configurable, not hardcoded'. Descriptions are working definitions inferred from the names (only First-Plausible Commit had an existing definition, in the question-generation skill) -- meant to be refined by the user, not treated as authoritative. Attaching patterns to an answer piggybacks on PATCH /api/evaluations/:id/items/:itemId via an optional pattern_ids field, since tab05 lists no dedicated route for it; verified live end to end including the report correctly aggregating pattern counts.</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="23.25" customHeight="1" s="59">
       <c r="A61" s="67" t="inlineStr">
@@ -14109,10 +14121,14 @@
       </c>
       <c r="J62" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K62" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K62" s="67" t="inlineStr">
+        <is>
+          <t>GET /api/evaluations/:id/report, rule-based end to end (src/lib/diagnosis.ts) -- deliberately built as AI-10's own documented fallback ('rule-based template report') rather than a live AI call, since AI-10's guardrail already says 'the model never computes scores' regardless. Returns score/grade/gap, an error inventory (lost-mark questions only, with any attached pattern hits), aggregated pattern counts, and up to 3 ranked actions drawn from the student's Weak/Priority concepts tracker-wide (not just this paper) plus a single parent action. habit_status is an empty array (F058 not built). Verified live against the full report shape.</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="23.25" customHeight="1" s="59">
       <c r="A63" s="67" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -11098,10 +11098,14 @@
       </c>
       <c r="J5" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K5" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K5" s="67" t="inlineStr">
+        <is>
+          <t>src/lib/env.ts: a single Zod schema for every env var actually read anywhere in the codebase (DATABASE_URL, BETTER_AUTH_SECRET/URL required; GOOGLE_CLIENT_ID/SECRET and ANTHROPIC_API_KEY optional, matching their documented graceful-degradation paths). Replaced every scattered process.env.X read (connection.ts, auth-pool.ts, auth.ts, ai-grading.ts) with this validated object. Verified live: booting with BETTER_AUTH_SECRET removed throws immediately with the exact missing key named, not a confusing failure deep in a request; booting normally still works, confirmed via a live dev-server request. .env.example already existed and now documents ANTHROPIC_API_KEY too. "Secrets stored in Vercel, never in git" -- .env is already gitignored (verified back in F001) and no secret has been committed at any point this project.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="23.25" customHeight="1" s="59">
       <c r="A6" s="67" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -16389,10 +16389,14 @@
       </c>
       <c r="J106" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K106" s="67" t="n"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="K106" s="67" t="inlineStr">
+        <is>
+          <t>45 tests across 4 files, all passing, ~1.4s wall time (well under the 5-minute CI budget). Unit coverage (no DB): scoring.ts (normalizeAnswer/scoreObjectiveAnswer/templateFeedback -- writing these tests caught and fixed two real normalizeAnswer bugs that had shipped silently in M09: "5cm" vs "5 cm" did not normalize equal, and "Rs. 50" left a stray period behind), the full F063 mastery escalation state machine extracted as a pure determineNextStatus() function and tested against the exact Weak-&gt;Priority-&gt;Priority-&gt;Maintenance sequence verified live during M12, and papers.ts allocateByWeighting/difficultiesUpTo (F028/F119). One integration test (household-isolation.integration.test.ts) automates T02 against the real dev DB at the repository layer -- the layer that actually enforces isolation per the build-feature skill's own invariant -- rather than standing up the full HTTP/auth stack. .github/workflows/tests.yml provisions a scratch Postgres, migrates, seeds, lints, typechecks, and runs the suite -- written but unverified end-to-end, same GitHub-remote blocker as the migrations workflow (F001/F011). Auth-guard coverage (T01, actual 403 over HTTP) is not yet automated -- would need either a running server or direct route-handler invocation, neither built this pass. Marked In Progress, not Done: full unit+integration+E2E coverage across every route this session built is a larger undertaking than one pass covers.</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="23.25" customHeight="1" s="59">
       <c r="A107" s="67" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -16032,10 +16032,14 @@
       </c>
       <c r="J99" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K99" s="67" t="n"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="K99" s="67" t="inlineStr">
+        <is>
+          <t>Every route this session built already scopes through the repository layer (F013's createScopedRepository, used by every single route in the app) -- this feature is proving that live, automatically, calling the REAL route handler functions with genuine better-auth session cookies (no dev server needed -- src/db/test-helpers.ts drives auth.api.signUpEmail/verifyEmail/signInEmail directly, the same in-process calls the real /api/auth/$ catch-all uses). 7 tests in cross-household-access.integration.test.ts sweep GET/POST /api/students, PATCH /api/students/:id, POST /api/papers/generate, GET /api/papers/:id, GET /api/tracker/:studentId -- all 404 for a second household with the exact real ids, all 200 for the owner, plus T01 (401 unauthenticated). This also closes F103's stated auth-guard gap. Not yet swept: evaluations and attempts routes (would need a submitted-attempt fixture, a materially bigger setup) -- marked In Progress, not Done, since 'all endpoints' is not literally true yet.</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="23.25" customHeight="1" s="59">
       <c r="A100" s="67" t="inlineStr">
@@ -16394,7 +16398,7 @@
       </c>
       <c r="K106" s="67" t="inlineStr">
         <is>
-          <t>45 tests across 4 files, all passing, ~1.4s wall time (well under the 5-minute CI budget). Unit coverage (no DB): scoring.ts (normalizeAnswer/scoreObjectiveAnswer/templateFeedback -- writing these tests caught and fixed two real normalizeAnswer bugs that had shipped silently in M09: "5cm" vs "5 cm" did not normalize equal, and "Rs. 50" left a stray period behind), the full F063 mastery escalation state machine extracted as a pure determineNextStatus() function and tested against the exact Weak-&gt;Priority-&gt;Priority-&gt;Maintenance sequence verified live during M12, and papers.ts allocateByWeighting/difficultiesUpTo (F028/F119). One integration test (household-isolation.integration.test.ts) automates T02 against the real dev DB at the repository layer -- the layer that actually enforces isolation per the build-feature skill's own invariant -- rather than standing up the full HTTP/auth stack. .github/workflows/tests.yml provisions a scratch Postgres, migrates, seeds, lints, typechecks, and runs the suite -- written but unverified end-to-end, same GitHub-remote blocker as the migrations workflow (F001/F011). Auth-guard coverage (T01, actual 403 over HTTP) is not yet automated -- would need either a running server or direct route-handler invocation, neither built this pass. Marked In Progress, not Done: full unit+integration+E2E coverage across every route this session built is a larger undertaking than one pass covers.</t>
+          <t>45 tests across 4 files, all passing, ~1.4s wall time (well under the 5-minute CI budget). Unit coverage (no DB): scoring.ts (normalizeAnswer/scoreObjectiveAnswer/templateFeedback -- writing these tests caught and fixed two real normalizeAnswer bugs that had shipped silently in M09: "5cm" vs "5 cm" did not normalize equal, and "Rs. 50" left a stray period behind), the full F063 mastery escalation state machine extracted as a pure determineNextStatus() function and tested against the exact Weak-&gt;Priority-&gt;Priority-&gt;Maintenance sequence verified live during M12, and papers.ts allocateByWeighting/difficultiesUpTo (F028/F119). One integration test (household-isolation.integration.test.ts) automates T02 against the real dev DB at the repository layer -- the layer that actually enforces isolation per the build-feature skill's own invariant -- rather than standing up the full HTTP/auth stack. .github/workflows/tests.yml provisions a scratch Postgres, migrates, seeds, lints, typechecks, and runs the suite -- written but unverified end-to-end, same GitHub-remote blocker as the migrations workflow (F001/F011). Auth-guard coverage (T01/T02, direct route-handler invocation with a real session cookie) was added under F096 (cross-household-access.integration.test.ts) shortly after this was first written -- see that feature's note. Marked In Progress, not Done: full unit+integration+E2E coverage across every route this session built is a larger undertaking than one pass covers.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -16037,7 +16037,7 @@
       </c>
       <c r="K99" s="67" t="inlineStr">
         <is>
-          <t>Every route this session built already scopes through the repository layer (F013's createScopedRepository, used by every single route in the app) -- this feature is proving that live, automatically, calling the REAL route handler functions with genuine better-auth session cookies (no dev server needed -- src/db/test-helpers.ts drives auth.api.signUpEmail/verifyEmail/signInEmail directly, the same in-process calls the real /api/auth/$ catch-all uses). 7 tests in cross-household-access.integration.test.ts sweep GET/POST /api/students, PATCH /api/students/:id, POST /api/papers/generate, GET /api/papers/:id, GET /api/tracker/:studentId -- all 404 for a second household with the exact real ids, all 200 for the owner, plus T01 (401 unauthenticated). This also closes F103's stated auth-guard gap. Not yet swept: evaluations and attempts routes (would need a submitted-attempt fixture, a materially bigger setup) -- marked In Progress, not Done, since 'all endpoints' is not literally true yet.</t>
+          <t>Every route this session built already scopes through the repository layer (F013's createScopedRepository, used by every single route in the app) -- this feature is proving that live, automatically, calling the REAL route handler functions with genuine better-auth session cookies (no dev server needed -- src/db/test-helpers.ts drives auth.api.signUpEmail/verifyEmail/signInEmail directly, the same in-process calls the real /api/auth/$ catch-all uses). 15 tests in cross-household-access.integration.test.ts now sweep GET/POST /api/students, PATCH /api/students/:id, POST /api/papers/generate, GET /api/papers/:id, GET /api/tracker/:studentId, POST /api/attempts, PATCH /api/attempts/:id/answer, POST /api/attempts/:id/submit, POST /api/evaluations, PATCH /api/evaluations/:id/items/:itemId, POST /api/evaluations/:id/confirm, GET /api/evaluations/:id/report -- all 404 for a second household/student with real ids (including a genuine second student login via createStudentSession, not just a second parent), 200 for the owner at every step including a real confirm and confirmed-report read, plus T01 (401 unauthenticated). This also closes F103's stated auth-guard gap. Not yet swept: POST /api/papers/:id/regenerate-slot (same household-scoping pattern as the rest, just not exercised by this test yet) -- marked In Progress, not Done, since 'all endpoints' is not literally true yet.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -16032,12 +16032,12 @@
       </c>
       <c r="J99" s="72" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K99" s="67" t="inlineStr">
         <is>
-          <t>Every route this session built already scopes through the repository layer (F013's createScopedRepository, used by every single route in the app) -- this feature is proving that live, automatically, calling the REAL route handler functions with genuine better-auth session cookies (no dev server needed -- src/db/test-helpers.ts drives auth.api.signUpEmail/verifyEmail/signInEmail directly, the same in-process calls the real /api/auth/$ catch-all uses). 15 tests in cross-household-access.integration.test.ts now sweep GET/POST /api/students, PATCH /api/students/:id, POST /api/papers/generate, GET /api/papers/:id, GET /api/tracker/:studentId, POST /api/attempts, PATCH /api/attempts/:id/answer, POST /api/attempts/:id/submit, POST /api/evaluations, PATCH /api/evaluations/:id/items/:itemId, POST /api/evaluations/:id/confirm, GET /api/evaluations/:id/report -- all 404 for a second household/student with real ids (including a genuine second student login via createStudentSession, not just a second parent), 200 for the owner at every step including a real confirm and confirmed-report read, plus T01 (401 unauthenticated). This also closes F103's stated auth-guard gap. Not yet swept: POST /api/papers/:id/regenerate-slot (same household-scoping pattern as the rest, just not exercised by this test yet) -- marked In Progress, not Done, since 'all endpoints' is not literally true yet.</t>
+          <t>Every route this session built already scopes through the repository layer (F013's createScopedRepository, used by every single route in the app) -- this feature is proving that live, automatically, calling the REAL route handler functions with genuine better-auth session cookies (no dev server needed -- src/db/test-helpers.ts drives auth.api.signUpEmail/verifyEmail/signInEmail directly, the same in-process calls the real /api/auth/$ catch-all uses). 17 tests in cross-household-access.integration.test.ts now sweep every household-scoped route in the app: GET/POST /api/students, PATCH /api/students/:id, POST /api/papers/generate, GET /api/papers/:id, POST /api/papers/:id/regenerate-slot, GET /api/tracker/:studentId, POST /api/attempts, PATCH /api/attempts/:id/answer, POST /api/attempts/:id/submit, POST /api/evaluations, PATCH /api/evaluations/:id/items/:itemId, POST /api/evaluations/:id/confirm, GET /api/evaluations/:id/report -- all 404 for a second household/student with real ids (including a genuine second student login via createStudentSession, not just a second parent), 200 for the owner at every step including a real confirm, confirmed-report read, and slot regeneration, plus T01 (401 unauthenticated). This also closes F103's stated auth-guard gap. Global/admin content routes (questions, syllabus, blueprints CRUD) are not household-scoped by design and are out of this sweep's scope. Verified live against the real Supabase dev DB; zero leftover fixture rows after cleanup.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -16911,12 +16911,12 @@
       </c>
       <c r="J116" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K116" s="67" t="inlineStr">
         <is>
-          <t>Added from parent requirements, 05 Sep 2026</t>
+          <t>POST /api/papers/generate already took chapter_ids as a multi-select array (that half predates this feature); the real gap was proportional distribution, now closed. generatePaper() computes each selected chapter's concept count, apportions the blueprint's nominal total marks across chapters via a new generic allocateProportionally() (largest-remainder, same algorithm F028's 40/40/20 bucket split now reuses), and picks each slot's question from whichever chapter has the largest remaining deficit first -- falling back to the full pool (and logging a shortfall, per F032) only when the target chapter has no eligible question left. chapter_weighting_override (chapter_id -&gt; percentage, validated to sum to 100) replaces the concept-count default when supplied. The paper's stored weighting JSON gains chapter_target/chapter_actual, and both POST /api/papers/generate and GET /api/papers/:id now return a resolved chapters[] (part/chapter_no/name) for the header -- actual PDF rendering doesn't exist yet (F033), so 'header' here means the data is ready, not printed. Verified live against the real Supabase dev DB: a 3-concept/2-concept two-chapter fixture with tightly-sized question supply produces an exact 6:4 split by default and an exact 1:4 split under a 20/80 override, both asserted via src/lib/papers.integration.test.ts (2 tests), plus 8 new unit tests in papers.test.ts for the pure allocation math (allocateProportionally, computeChapterMarksTargets). Full suite green (72 tests), zero leftover fixture rows after cleanup.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -12747,10 +12747,14 @@
       </c>
       <c r="J36" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K36" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K36" s="67" t="inlineStr">
+        <is>
+          <t>GET /api/papers/:id/pdf (tab05's exact contract: Parent role, theme + include_key query params, application/pdf stream) renders the paper via Playwright/headless Chromium (tab09's locked choice, now actually installed -- playwright + a downloaded Chromium build). A4 via page.pdf()'s margin option, printBackground:true, page-break-inside:avoid on every question block so a question is never split across a page. Embedded fonts happen automatically -- Chromium's PDF export always subsets and embeds whatever font the page actually renders with (Georgia here). theme is accepted per the contract but not yet acted on since no theme packs exist (F034/F120 Not Started) -- every request renders the one 'Plain' layout. Verified live: generated a real PDF against the real dev DB (src/routes/papers-pdf.integration.test.ts), confirmed the %PDF- magic header, a realistic byte size, and (via a manual screenshot render, not committed) that the layout actually looks like an exam paper -- header, sectioned questions, numbered continuously across sections, marks in brackets.</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="23.25" customHeight="1" s="59">
       <c r="A37" s="67" t="inlineStr">
@@ -12849,10 +12853,14 @@
       </c>
       <c r="J38" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K38" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K38" s="67" t="inlineStr">
+        <is>
+          <t>Built into the same paper-template.ts used by F033's route: a 16mm ruled rough-work column pinned with position:fixed so it repeats on every printed page (Chromium's standard trick, since @page margin boxes aren't supported), ruled answer-line panels sized to the question's marks (short_answer/long_answer scale with marks; fill_blank gets one line; mcq/assertion_reason/match/multi_statement get an options list instead), and a labelled 'Draw here' box whenever a question's diagram_kind is set, regardless of its base type. Not print-QA'd on a real printer/multiple devices (F107 Not Started) -- verified only via a rendered PDF/screenshot in this dev environment.</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="23.25" customHeight="1" s="59">
       <c r="A39" s="67" t="inlineStr">
@@ -12900,10 +12908,14 @@
       </c>
       <c r="J39" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K39" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K39" s="67" t="inlineStr">
+        <is>
+          <t>The same GET /api/papers/:id/pdf route (tab05 defines one route with an include_key boolean, not two separate paths) renders the answer key + step-wise marks + expected diagram description as a distinct trailing section (its own page-break-before, never interleaved with the paper's questions) when include_key=true -- and this branch is only ever reachable by the parent/admin-only route, so a student session can never produce or receive it, satisfying the hard rule structurally, not just by convention. Verified live: the include_key=true response is a strictly larger PDF with more pages than the default response (src/routes/papers-pdf.integration.test.ts), and a correct-option-letter test question round-trips through the key with the right label.</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="23.25" customHeight="1" s="59">
       <c r="A40" s="67" t="inlineStr">
@@ -12951,10 +12963,14 @@
       </c>
       <c r="J40" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K40" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K40" s="67" t="inlineStr">
+        <is>
+          <t>computeCoverageTable() (src/lib/pdf/coverage.ts) computes concept/questions/marks/%weight/Bloom-split per concept actually used on a paper. It's appended to the answer-key PDF (F036) and also served standalone as JSON at GET /api/papers/:id/coverage (tab05's exact route) -- the 'shown on screen' half of the AC has real data to call now, even though no screen exists anywhere in this repo (M14 dashboards are all Not Started). Verified live against the real dev DB with a 2-question, 2-Bloom-level fixture.</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="23.25" customHeight="1" s="59">
       <c r="A41" s="67" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -11471,12 +11471,12 @@
       </c>
       <c r="J12" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K12" s="67" t="inlineStr">
         <is>
-          <t>All listed fields (name, class, section, roll_no, board, school, target_exams) already exist on students via F011/F013 and are settable through the F008 endpoints. Left Not Started because the AC's 'used in paper header automatically' cannot be verified until M07 (paper rendering) exists -- marking Done now would be checking a box the spec does not actually let me check yet.</t>
+          <t>F008's schema already had name/class/section/roll_no/board/school/target_exams -- the real gap was that POST /api/students never accepted section or target_exams at creation, and PATCH /api/students/:id had no target_exams field at all, so a student's target exam dates could never be set or changed after creation (stuck at the hardcoded []). Both routes now accept target_exams as a validated {name, date}[] and POST accepts section too. 'subjects active' is intentionally not modelled: the whole product is single-subject today (CLAUDE.md's launch scope is CBSE Class 7 Maths only, and MATH-SEED is the only subject that has ever existed in this schema), so there is nothing yet for that field to distinguish -- revisit at the tab17 multi-subject rollout, not now. 'used in paper header automatically' already existed before this feature (F033's buildPaperHtml reads student.name/board/class). Verified live against the real dev DB (students-profile.integration.test.ts): create with section+target_exams, a partial PATCH that updates only target_exams without touching other fields, and a rejected malformed date.</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="K106" s="67" t="inlineStr">
         <is>
-          <t>45 tests across 4 files, all passing, ~1.4s wall time (well under the 5-minute CI budget). Unit coverage (no DB): scoring.ts (normalizeAnswer/scoreObjectiveAnswer/templateFeedback -- writing these tests caught and fixed two real normalizeAnswer bugs that had shipped silently in M09: "5cm" vs "5 cm" did not normalize equal, and "Rs. 50" left a stray period behind), the full F063 mastery escalation state machine extracted as a pure determineNextStatus() function and tested against the exact Weak-&gt;Priority-&gt;Priority-&gt;Maintenance sequence verified live during M12, and papers.ts allocateByWeighting/difficultiesUpTo (F028/F119). One integration test (household-isolation.integration.test.ts) automates T02 against the real dev DB at the repository layer -- the layer that actually enforces isolation per the build-feature skill's own invariant -- rather than standing up the full HTTP/auth stack. .github/workflows/tests.yml provisions a scratch Postgres, migrates, seeds, lints, typechecks, and runs the suite -- written but unverified end-to-end, same GitHub-remote blocker as the migrations workflow (F001/F011). Auth-guard coverage (T01/T02, direct route-handler invocation with a real session cookie) was added under F096 (cross-household-access.integration.test.ts) shortly after this was first written -- see that feature's note. Marked In Progress, not Done: full unit+integration+E2E coverage across every route this session built is a larger undertaking than one pass covers.</t>
+          <t>45 tests across 4 files, all passing, ~1.4s wall time (well under the 5-minute CI budget). Unit coverage (no DB): scoring.ts (normalizeAnswer/scoreObjectiveAnswer/templateFeedback -- writing these tests caught and fixed two real normalizeAnswer bugs that had shipped silently in M09: "5cm" vs "5 cm" did not normalize equal, and "Rs. 50" left a stray period behind), the full F063 mastery escalation state machine extracted as a pure determineNextStatus() function and tested against the exact Weak-&gt;Priority-&gt;Priority-&gt;Maintenance sequence verified live during M12, and papers.ts allocateByWeighting/difficultiesUpTo (F028/F119). One integration test (household-isolation.integration.test.ts) automates T02 against the real dev DB at the repository layer -- the layer that actually enforces isolation per the build-feature skill's own invariant -- rather than standing up the full HTTP/auth stack. .github/workflows/tests.yml provisions a scratch Postgres, migrates, seeds, lints, typechecks, and runs the suite -- written but unverified end-to-end, same GitHub-remote blocker as the migrations workflow (F001/F011). Auth-guard coverage (T01/T02, direct route-handler invocation with a real session cookie) was added under F096 (cross-household-access.integration.test.ts) shortly after this was first written -- see that feature's note. Marked In Progress, not Done: full unit+integration+E2E coverage across every route this session built is a larger undertaking than one pass covers. Update: now 79 tests across 8 files (added papers.integration.test.ts for F113's chapter proportionality, papers-pdf.integration.test.ts for F033/F035/F036/F037's real Chromium PDF render, students-profile.integration.test.ts for F009). Found and fixed a real cross-test contamination bug in the process: vitest's default file-level parallelism let two integration test files generate papers against the same shared reference chapter concurrently, so one file's in-flight fixture question became an eligible pick for another file's paper -- surfaced as a random-looking regenerate-slot 409 and an FK-violation cleanup failure. Fixed by setting fileParallelism:false in vitest.config.ts (all these tests share one live dev DB, so they were never safe to run concurrently); confirmed stable across 3 repeated full-suite runs afterward. tests.yml now also installs Playwright's Chromium before running the suite, needed for the new PDF test.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -14773,10 +14773,14 @@
       </c>
       <c r="J74" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K74" s="67" t="n"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="K74" s="67" t="inlineStr">
+        <is>
+          <t>GET /api/dashboard/:studentId (tab05's exact route) implements the data side of the AC: per subject, latest confirmed score + Delivery Gap, a trend (up/down/flat from the last 2 confirmed evaluations), top 3 priority/weak concepts (reusing conceptStatusRepository, same tracker data F064 already exposes), and a rule-based next_action sentence (same pattern as F059's buildDiagnosisReport). pending_uploads is always [] since F050 (photo/PDF upload) isn't built. No screen exists (M14 is all Not Started) -- this is the API half only, same pattern as every other route this session built ahead of any UI. Verified live against the real dev DB: two full generate-&gt;attempt-&gt;submit-&gt;evaluate-&gt;confirm cycles (a wrong answer then a right one) and the dashboard correctly reports a 100% latest score and an 'up' trend, plus a 404 for a second household. Marked In Progress, not Done, since there is no actual dashboard screen to show a parent.</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="59">
       <c r="A75" s="67" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -16001,10 +16001,14 @@
       </c>
       <c r="J98" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K98" s="67" t="n"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="K98" s="67" t="inlineStr">
+        <is>
+          <t>New consents table (migration 0040, append-only per CLAUDE.md invariant 4 -- withdrawal sets withdrawn_at, never deletes). POST /api/students now requires consent_accepted:true (literal true, not just truthy) and atomically inserts a consent row pinned to CURRENT_CONSENT_VERSION alongside the student in one transaction -- a student row can never exist without a matching consent event. POST /api/students/:id/consent/withdraw records withdrawal (not in tab05's listed routes -- that sheet has no consent endpoints at all -- added as the smallest reasonable path under the existing /api/students/:id resource since the AC explicitly requires withdrawal). POST /api/papers/generate now checks for an active consent before generating anything for that student and 403s otherwise, so withdrawal has a real, enforced effect rather than just sitting in a log. What this is NOT: 'verifiable parental consent' in the DPDP sense needs actual identity verification (a checkbox from whoever is logged in isn't that), and src/lib/consent.ts's purpose/retention wording is placeholder text, not lawyer-reviewed copy -- both need real product/legal decisions this session can't make on its own. Verified live against the real dev DB (consent.integration.test.ts, 8 tests): creation rejected without consent, accepted creation writes a matching row, generation succeeds while active and 403s after withdrawal, re-withdrawing 409s, and cross-household withdrawal attempts 404. Full suite green (89 tests).</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="23.25" customHeight="1" s="59">
       <c r="A99" s="67" t="inlineStr">
@@ -17481,7 +17485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="58" min="1" max="1"/>
@@ -18384,6 +18388,33 @@
         </is>
       </c>
       <c r="E35" s="67" t="inlineStr">
+        <is>
+          <t>M20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="58" t="inlineStr">
+        <is>
+          <t>consents</t>
+        </is>
+      </c>
+      <c r="B36" s="58" t="inlineStr">
+        <is>
+          <t>DPDP consent events (F095). Append-only -- withdrawal sets withdrawn_at, never deletes.</t>
+        </is>
+      </c>
+      <c r="C36" s="58" t="inlineStr">
+        <is>
+          <t>id, household_id, student_id, given_by_user_id, purpose_version, given_at, withdrawn_at</t>
+        </is>
+      </c>
+      <c r="D36" s="58" t="inlineStr">
+        <is>
+          <t>-&gt; households, students, users</t>
+        </is>
+      </c>
+      <c r="E36" s="58" t="inlineStr">
         <is>
           <t>M20</t>
         </is>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -11632,10 +11632,14 @@
       </c>
       <c r="J15" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K15" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K15" s="67" t="inlineStr">
+        <is>
+          <t>seed.ts now writes exactly the AC's numbers: 15 chapters (2 original + 13 new topic chapters), 60 concepts, 200 questions (all bulk-approved -- short_answer isn't an objective type so F117's tier logic would otherwise leave it in draft with no review-queue UI to approve it from), 2 subjects (MATH-SEED plus a deliberately small SCI-SEED stub -- CLAUDE.md's launch scope is Class 7 Maths only, so the second subject exists to prove multi-subject routes work, not to carry curriculum depth), 1 household with 2 students, and 3 confirmed historical evaluations (40%/80%/60%, via real generatePaper -&gt; attempt -&gt; answer -&gt; submit -&gt; createEvaluation -&gt; confirmEvaluation calls, not hand-inserted rows). All new volume lives under brand-new chapters (chapter_no 3-15) rather than the original chapter 1/2 -- four existing integration test files generate real papers scoped to 'chapter_no=1 of MATH-SEED' and depend on it having exactly their own fixture questions as eligible candidates; adding more approved questions there would have made those tests' random picks nondeterministic. seed.ts also gained an entry-point guard (only auto-runs main() when invoked directly, via pathToFileURL against process.argv[1] -- the Windows-safe pattern already used by the migration runner) so seedBulkFixtures can be called standalone against a DB that already has MATH-SEED, which is exactly how this was verified: run once against the real dev DB, counts confirmed by direct query (15/60/200/2/3), then the full test suite re-run clean (89 tests) to prove the isolation actually holds.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="23.25" customHeight="1" s="59">
       <c r="A16" s="67" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -17049,12 +17049,12 @@
       </c>
       <c r="J118" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="K118" s="67" t="inlineStr">
         <is>
-          <t>Added from parent requirements, 05 Sep 2026</t>
+          <t>GET /api/questions/coverage-grid (not in tab05's listed routes -- that sheet has no admin question-bank grid endpoint at all -- added under the existing /api/questions resource since this is a reporting view over the same data). concept_id returns one concept's 6 Bloom x 3 difficulty grid (counts of approved questions per cell); subject_id returns one grid per concept in that subject, sorted worst-coverage first. target_question_count (F122) is a single per-concept number, not one per cell -- there's no per-cell target defined anywhere in the plan, so each cell's target is that number split evenly across all 18 cells (rounded up); this is a stated assumption, not a spec value, and should be revisited if a real per-cell target policy gets defined later. 'Papers cannot request an empty cell without a stated fallback' is already true and predates this feature -- generatePaper reports a shortfall rather than failing when a slot has no eligible question (F027-F032); this grid is the reporting view that would drive a targeted generation batch (F116) at cells actually empty. Verified live against F012's real seed data (60 concepts, 200 questions spread thin across cells by design): a single concept's grid shows mostly-empty cells as expected, the subject-wide list covers all 60 concepts sorted correctly, and admin-only access is enforced (promoteToAdmin exercised for the first time in this test suite). Marked In Progress, not Done: 'target counts' rests on the even-split assumption above rather than a specified policy, and there is no screen to show this grid on (none exist anywhere in this repo).</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -14883,10 +14883,14 @@
       </c>
       <c r="J76" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K76" s="67" t="n"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="K76" s="67" t="inlineStr">
+        <is>
+          <t>GET /api/evaluations/:id/report/pdf (not in tab05's listed routes -- only the JSON GET /api/evaluations/:id/report exists there -- added as a sibling path the same way GET /api/papers/:id/pdf sits alongside GET /api/papers/:id). Renders the exact same buildDiagnosisReport() data the JSON route returns through the F033 PDF pipeline (Playwright/Chromium) -- not a second computation of the report, a second representation of it. Extended buildDiagnosisReport() itself with a real gap the AC named explicitly: 'concept-wise performance' didn't exist before this feature (only the error inventory did, which only covers items that lost marks) -- added as a per-concept marks-awarded/marks-max/% breakdown across every item, plus paper/student meta fields the PDF header needs. Verified live against the real dev DB: a real generate-&gt;attempt-&gt;submit-&gt;evaluate-&gt;confirm cycle with a deliberately wrong answer produces a genuine PDF (%PDF- header, real byte size) and correct household isolation (404 for a second household); layout also eyeballed via a rendered screenshot (score cards, error inventory table, concept performance table, actions) before calling this done. Marked In Progress, not Done: the 'web report' half of the AC doesn't exist -- no screens exist anywhere in this repo.</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="23.25" customHeight="1" s="59">
       <c r="A77" s="67" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -13022,10 +13022,14 @@
       </c>
       <c r="J41" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K41" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K41" s="67" t="inlineStr">
+        <is>
+          <t>"Every generated paper persisted with its question IDs" was already true (F011's schema: paper_questions rows are never touched once written, per the 'nothing is deleted' invariant). The real gap was 'blueprint version' -- papers stored only a live blueprint_id FK, so if a blueprint were ever edited in place, an old paper's notion of 'its blueprint' would silently mean whatever the blueprint looks like today. Migration 0041 adds papers.blueprint_version, backfilled from each existing paper's current blueprint.version (defaults to 1 for any future direct insert that doesn't specify one, matching blueprints.version's own default), and generatePaper() now snapshots it at generation time. No blueprint edit route exists yet (tab05 only lists POST /api/blueprints, no PATCH), so this was a forward-looking fix, not an active bug. 'Re-download reproduces the identical PDF' verified live via GET /api/papers/:id/pdf called twice against the real dev DB: identical page count and near-identical byte size -- not byte-for-byte identical, since Chromium stamps a fresh /CreationDate into every PDF export with no Playwright option to override it, so 'identical' here means identical rendered content, not an exact byte match. Full suite green (97 tests).</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="23.25" customHeight="1" s="59">
       <c r="A42" s="67" t="inlineStr">
@@ -17928,7 +17932,7 @@
       </c>
       <c r="C18" s="67" t="inlineStr">
         <is>
-          <t>id, student_id, blueprint_id, subject_id, chapter_ids[], title, total_marks, duration_min, weighting(jsonb), theme, generated_at, pdf_ref, key_pdf_ref, shortfalls(jsonb)</t>
+          <t>id, student_id, blueprint_id, blueprint_version, subject_id, chapter_ids[], title, total_marks, duration_min, weighting(jsonb), theme, generated_at, pdf_ref, key_pdf_ref, shortfalls(jsonb)</t>
         </is>
       </c>
       <c r="D18" s="67" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -16225,10 +16225,14 @@
       </c>
       <c r="J102" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K102" s="67" t="n"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="K102" s="67" t="inlineStr">
+        <is>
+          <t>audit_log itself already existed (F047's evaluation-item-override endpoint wrote to it). Two more sensitive writes now log to it: POST /api/evaluations/:id/confirm ('evaluation.confirmed' -- the 'score' event that actually finalises marks) and POST /api/students/:id/consent/withdraw ('consent.withdrawn'). Added GET /api/audit-log (not in tab05's listed routes -- no audit read endpoint exists there at all) so the trail is actually 'visible to household owner' rather than write-only; household-scoped via auth.householdId, capped at the 100 most recent entries. Not covered: 'role changes' (no route mutates a user's role at all -- promoteToAdmin is a test-only helper, not a real endpoint) and 'deletions' (nothing is ever hard-deleted in this schema per CLAUDE.md invariant 4, so there is no deletion event to log; the closest analogues -- question retirement, F098's data delete -- aren't built). Verified live against the real dev DB: a real evaluation confirm and a real consent withdrawal both produce matching audit_log rows visible through the new route, and a second household sees none of them. Marked In Progress: two of the four named write categories (role changes, deletions) have no corresponding mutation anywhere in the app yet to log.</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="15" customHeight="1" s="59">
       <c r="A103" s="67" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -12170,10 +12170,14 @@
       </c>
       <c r="J25" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K25" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K25" s="67" t="inlineStr">
+        <is>
+          <t>POST /api/questions/bulk-import (tab05's exact route, Admin, multipart file field, format inferred from the filename extension unless overridden). Extracted the single-question validation (previously inline in POST /api/questions) into a shared questionInputSchema (src/lib/questions.ts) so one question is never valid by different rules depending on which route it came through. Each row -- CSV via papaparse, JSON via a plain array -- is validated and inserted independently through the same schema + createQuestion(), so one bad row never blocks the rest ('partial import allowed'); the JSON response's per-row {row, status, question_id | errors} is the 'rejected rows with reasons' report itself, not a separate download artifact. CSV supports the common case only -- mcq/fill_blank/short_answer with up to 4 lettered options via option_a_text/option_a_correct-style columns -- since CSV can't naturally represent step_marks or open-ended option counts; JSON is the richer path for those. Verified live against the real dev DB: a 2-row CSV (1 valid mcq, 1 missing its answer) imports the valid row and reports the invalid one with a concept-specific error message, a JSON import does the same, and admin-only access is enforced. Full suite green (102 tests).</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="23.25" customHeight="1" s="59">
       <c r="A26" s="67" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -12225,10 +12225,14 @@
       </c>
       <c r="J26" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K26" s="67" t="n"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="K26" s="67" t="inlineStr">
+        <is>
+          <t>Exact-hash half only -- the embedding-similarity half of the AC needs an AI embeddings provider, and no ANTHROPIC_API_KEY (or any provider) is configured. Migration 0042 adds questions.text_hash (sha256 of lowercased, whitespace-collapsed text), backfilled in JS using the exact same computeTextHash() new inserts use (not a separately-written SQL equivalent, which risks silently diverging from the real algorithm), indexed per concept. createQuestion() now looks up an existing, non-retired question in the same concept with the same hash before inserting, and returns duplicate_of:{id,text} rather than blocking the save -- 'warns with a link to the existing question', not a hard stop. Wired through both POST /api/questions and F022's bulk import (each row's result). Scoped per-concept, not global: the same worked example can legitimately appear under two different concepts. Verified live against the real dev DB: an exact match (including a case/whitespace variant) in the same concept is flagged, the same text under a different concept is not, and a genuinely new question isn't flagged. Also cleaned up orphaned rows left behind by an unrelated Vitest worker crash during this same session (a one-off infra fluke, confirmed non-reproducible across two clean re-runs) -- unrelated to this feature but caught while verifying it. Full suite green (105 tests). Marked In Progress: the similarity-based near-duplicate half of the AC isn't built.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="23.25" customHeight="1" s="59">
       <c r="A27" s="67" t="inlineStr">
@@ -17805,7 +17809,7 @@
       </c>
       <c r="C13" s="67" t="inlineStr">
         <is>
-          <t>id, concept_id, bloom, difficulty, marks, type, text, answer, hint, tags[], diagram_kind, diagram_params(jsonb), language, status(draft|approved|retired), created_by, source_ref</t>
+          <t>id, concept_id, bloom, difficulty, marks, type, text, text_hash, answer, hint, tags[], diagram_kind, diagram_params(jsonb), language, status(draft|approved|retired), created_by, source_ref</t>
         </is>
       </c>
       <c r="D13" s="67" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -12382,10 +12382,14 @@
       </c>
       <c r="J29" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K29" s="67" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K29" s="67" t="inlineStr">
+        <is>
+          <t>The exclusion mechanic already existed (generatePaper's recentUsageWindowDays, default 14 days) but was only reachable by calling generatePaper() directly -- every test in this repo does that, but the real POST /api/papers/generate route never exposed it, so 'configurable window' wasn't actually true for a real caller. Added recent_usage_window_days to the route's schema (nonnegative int, passed through as-is). Added questionUsageRepository.summaryForStudent() (last_served_at via MAX(served_at), times_served via COUNT, grouped per question) and wired it into GET /api/questions via an opt-in student_id query param -- usage is meaningless without a specific student to ask about, so it's additive/opt-in rather than always joined. Verified live against the real dev DB with a fixture sized to make the window's effect directly observable (exactly one eligible question): first generation uses it, a second generation with the default window hits a shortfall (correctly excluded), and recent_usage_window_days:0 makes it eligible again through the real route -- then GET /api/questions?student_id=... reports times_served:2. Full suite green (109 tests).</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="23.25" customHeight="1" s="59">
       <c r="A30" s="67" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -17238,12 +17238,12 @@
       </c>
       <c r="J121" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="K121" s="67" t="inlineStr">
         <is>
-          <t>Added from parent requirements, 05 Sep 2026</t>
+          <t>GET /api/questions/:id/stats (not in tab05's listed routes -- no live-stats endpoint exists there -- added as a sibling path under the existing /api/questions/:id resource) computes attempts, success rate (full marks / total, a clean binary definition), mean time spent, and success rate broken down by the answering student's CURRENT concept_status -- 'by mastery level' reads literally as status at the time of THAT attempt, which has no historical snapshot anywhere in this schema, so this is a documented approximation using live status instead. Anomaly flagging (Easy question with &lt;30% success, or Hardest with &gt;90%) fires only once a question has &gt;=5 real attempts, so a fresh question can't be flagged off one fluke -- both the threshold and the minimum-attempts gate are stated defaults, not spec values, since none are defined anywhere in the plan. PATCH /api/questions/:id gained a status field so a question can actually be retired -- previously there was no route capable of doing this at all; retiring only flips the column, so every paper/attempt/evaluation that already used the question keeps referencing it untouched, satisfying 'without deleting historical results' structurally rather than by convention. Verified live against the real dev DB: 5 students all answering the same Easy question wrong produces a genuine 0% success rate and trips the anomaly rule, and retiring it afterward leaves all 5 evaluation_items rows intact. Also: while chasing this feature's test flakiness, diagnosed and fixed a real environment bug -- the project's DATABASE_URL used Supabase's direct-connection host, which resolves IPv6-only, and this dev sandbox's IPv6 routing was unreliable; switched to Supabase's session pooler (IPv4) and confirmed stable across repeated runs. Also made src/lib/pdf/render.ts reuse one warm Chromium instance instead of launching fresh per call (real perf win, and reduces launch/teardown churn that was contributing to occasional Vitest worker crashes on this memory-constrained host), and raised vitest's default timeouts (5s/10s -&gt; 15s/30s) since these tests hit a real remote database with real network latency, not a local one. Full suite green twice in a row (112 tests). Marked In Progress: success_rate_by_mastery is a documented approximation, and there is no screen to show this on.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -14110,10 +14110,14 @@
       </c>
       <c r="J61" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K61" s="67" t="n"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="K61" s="67" t="inlineStr">
+        <is>
+          <t>The H1-H10 habit library (habits/habit_observations tables) already existed in the schema with a bare repository wrapper, but nothing ever wrote to it -- buildDiagnosisReport's habit_status was a hardcoded []. Only the fact that ten named habits exist is actually specified anywhere in the plan (tab00/02/04/08 all say 'H1-H10' with no content); seeded db/seed-habits.ts with working definitions following the exact same honest-disclaimer convention seed-patterns.ts already established for P1-P6 -- H7-H10 themed around reading discipline per F060's own hint (NOT/least/false), H1-H6 general presentation habits. These are editable rows meant to be refined in the table, not code, same as the patterns. Added PATCH /api/evaluations/:id/habits (not in tab05's routes -- added as a sibling to F047's item-override endpoint, the same 'human reviews this evaluation' surface) to record present/partial/absent ratings before confirmation, a full-replace-per-call upsert matching pattern_hits' own idempotency pattern. buildDiagnosisReport now reads real habit_observations instead of the hardcoded []. Added GET /api/students/:id/habits/trend (also not in tab05) for the AC's 'trend line' -- every confirmed evaluation's ratings grouped per habit, oldest first. Verified live against the real dev DB: a real generate-&gt;attempt-&gt;submit-&gt;evaluate cycle rated two habits before confirming, the confirmed report reflected both ratings, editing after confirmation was rejected (409), the trend endpoint showed both habits' single observation each, and cross-household access was denied on both new routes. Full suite green (118 tests). Marked In Progress: the habit content itself is inferred, not spec text, and there is no screen to show ratings on.</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="23.25" customHeight="1" s="59">
       <c r="A62" s="67" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -14220,10 +14220,14 @@
       </c>
       <c r="J63" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K63" s="67" t="n"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="K63" s="67" t="inlineStr">
+        <is>
+          <t>migration 0043 adds questions.is_reversal_word (boolean, default false) and a new 'Reading Discipline' value to the error_type/ai_error_type CHECK constraints (now 7 values). scoreObjectiveAnswer() in scoring.ts takes an isReversalWord flag and returns errorType='Reading Discipline' instead of 'Conceptual Gap' when a reversal-word question is answered wrong; TEMPLATE_FEEDBACK has a matching feedback string ('...this needs a reading-discipline drill, not a concept re-teach.'). is_reversal_word is settable via POST /api/questions and CSV/JSON bulk import, flows through paper generation (paperQuestionsRepository.listForPaperWithQuestions now selects it) into createEvaluation(), and is verified end-to-end by a new integration test (reversal-word.integration.test.ts) that runs two real generate-&gt;attempt-&gt;submit-&gt;evaluate-&gt;confirm cycles side by side, one on a tagged question and one on an otherwise-identical untagged question, both answered wrong, and asserts the tagged one comes back as 'Reading Discipline' and the other as 'Conceptual Gap'. 'Routed to a drill' is only satisfied at the feedback-text level (the report text tells the parent it needs a reading-discipline drill, not a concept re-teach) -- there is no actual drill/remediation-pack entity or routing mechanism, since that depends on F066 (remediation packs), which does not exist yet. No UI exists for tagging is_reversal_word on a question (it's API/CSV-only for now) and no UI surfaces the Reading Discipline category differently from other error types on any screen. Marked In Progress rather than Done because of both gaps.</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="23.25" customHeight="1" s="59">
       <c r="A64" s="67" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -11255,10 +11255,14 @@
       </c>
       <c r="J8" s="72" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K8" s="67" t="n"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="K8" s="67" t="inlineStr">
+        <is>
+          <t>shadcn/ui is now actually wired in (components.json was configured but nothing had been added yet) -- hand-written Button (5 variants: default/destructive/outline/secondary/ghost/link, 4 sizes) and Card (+ Header/Title/Description/Content/Footer) primitives now live at src/components/ui/, matching the existing "new-york" style config and using the pre-existing cn() helper. A ThemeProvider (next-themes, class-based, system-aware, SSR-safe via suppressHydrationWarning) wraps the whole app in __root.tsx, plus a working ThemeToggle component. A typography scale (.text-display/.text-h1/.text-h2/.text-h3/.text-body/.text-small/.text-caption) is defined once in src/styles.css for every future screen to reuse instead of ad-hoc text-* sizes. A print stylesheet (@media print) flattens colors to black-on-white, drops anything marked .no-print, and cleans up card borders/shadows for printouts -- this covers screens a parent might Ctrl+P directly (e.g. a report page), separate from the existing server-side Playwright PDF pipeline used for generated papers/reports. Also removed roughly 180 lines of dead, unreferenced "ocean/island" decorative CSS (sea-ink/lagoon/palm color variables, island-shell, feature-card, nav-link, site-footer classes) that had been sitting in styles.css since the initial scaffold but were never used by any actual component -- confirmed via grep before removing. The updated homepage (src/routes/index.tsx) exercises all of this (all four button variants, a card, the type scale, the theme toggle) and was verified by hand in a real running dev server: fetched the rendered HTML, confirmed the shadcn button/card classes and data-slot attributes are present, confirmed the inline theme-detection script runs and toggles the "dark" class correctly, confirmed the print media query and type-scale classes are in the served CSS bundle, and confirmed the old dead classes are gone from the served CSS. Full test suite (19 files / 119 tests) still passes after the change, tsc and eslint are clean. No dark-mode-aware redesign of any other screen exists yet (there's only the one placeholder route to redesign so far) -- this lays the foundation tokens/primitives down for the 24 screens in tab06 to build on, not a finished visual identity for the product. No Storybook or visual regression tooling, and no accessibility audit beyond what shadcn's defaults already provide. Marked In Progress rather than Done since a design system isn't really finished until more than one real screen has exercised it.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="23.25" customHeight="1" s="59">
       <c r="A9" s="67" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -11315,7 +11315,7 @@
       </c>
       <c r="K9" s="67" t="inlineStr">
         <is>
-          <t>better-auth mounted at /api/auth/$ (catch-all, src/routes/api/auth/$.ts). Email+password with required email verification (verified end-to-end: sign-up -&gt; logged verification link -&gt; verify-email -&gt; sign-in). Google OAuth wired but conditional on GOOGLE_CLIENT_ID/SECRET, which are not set in dev -- needs real credentials before it is testable. Session cookie confirmed httpOnly+SameSite=Lax via curl; Secure is added automatically once BETTER_AUTH_URL is https in prod. Sign-out/session endpoints come from betterauth's own router, not hand-written. Resend (M16) does not exist yet, so verification emails are logged server-side, not delivered -- flagged, not silently faked.</t>
+          <t>better-auth mounted at /api/auth/$ (catch-all, src/routes/api/auth/$.ts). Email+password with required email verification (verified end-to-end: sign-up -&gt; logged verification link -&gt; verify-email -&gt; sign-in). Google OAuth wired but conditional on GOOGLE_CLIENT_ID/SECRET, which are not set in dev -- needs real credentials before it is testable; the UI has no Google sign-in button yet for the same reason. Session cookie confirmed httpOnly+SameSite=Lax via curl; Secure is added automatically once BETTER_AUTH_URL is https in prod. Sign-out/session endpoints come from betterauth's own router, not hand-written. Resend (M16) does not exist yet, so verification emails are logged server-side, not delivered -- flagged, not silently faked. UI now exists -- see `/` (sign-in/sign-up) and `/onboarding` (add-student wizard), browser-verified end to end including the real email-verification link from the server log.</t>
         </is>
       </c>
     </row>
@@ -11425,7 +11425,7 @@
       </c>
       <c r="K11" s="67" t="inlineStr">
         <is>
-          <t>GET/POST /api/students and PATCH /api/students/:id (src/routes/api/students.ts, .../students/.ts), all household-scoped via studentsRepository (F013). Verified live with two separate parent signups: parent B's list is empty and never sees parent A's student; parent B's PATCH on parent A's student returns 404, not 403 or a leaked row. No student switcher UI yet -- no screens exist in src/ at all still, this is API-layer only.</t>
+          <t>GET/POST /api/students and PATCH /api/students/:id (src/routes/api/students.ts, .../students/.ts), all household-scoped via studentsRepository (F013). Verified live with two separate parent signups: parent B's list is empty and never sees parent A's student; parent B's PATCH on parent A's student returns 404, not 403 or a leaked row. UI now exists -- see `/` (sign-in/sign-up) and `/onboarding` (lists existing students, form to add a new one with name/class/board/school/consent), browser-verified end to end including the real email-verification link from the server log. No student switcher in the header yet though -- that's a separate screen from the onboarding wizard and still doesn't exist.</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="K12" s="67" t="inlineStr">
         <is>
-          <t>F008's schema already had name/class/section/roll_no/board/school/target_exams -- the real gap was that POST /api/students never accepted section or target_exams at creation, and PATCH /api/students/:id had no target_exams field at all, so a student's target exam dates could never be set or changed after creation (stuck at the hardcoded []). Both routes now accept target_exams as a validated {name, date}[] and POST accepts section too. 'subjects active' is intentionally not modelled: the whole product is single-subject today (CLAUDE.md's launch scope is CBSE Class 7 Maths only, and MATH-SEED is the only subject that has ever existed in this schema), so there is nothing yet for that field to distinguish -- revisit at the tab17 multi-subject rollout, not now. 'used in paper header automatically' already existed before this feature (F033's buildPaperHtml reads student.name/board/class). Verified live against the real dev DB (students-profile.integration.test.ts): create with section+target_exams, a partial PATCH that updates only target_exams without touching other fields, and a rejected malformed date.</t>
+          <t>F008's schema already had name/class/section/roll_no/board/school/target_exams -- the real gap was that POST /api/students never accepted section or target_exams at creation, and PATCH /api/students/:id had no target_exams field at all, so a student's target exam dates could never be set or changed after creation (stuck at the hardcoded []). Both routes now accept target_exams as a validated {name, date}[] and POST accepts section too. 'subjects active' is intentionally not modelled: the whole product is single-subject today (CLAUDE.md's launch scope is CBSE Class 7 Maths only, and MATH-SEED is the only subject that has ever existed in this schema), so there is nothing yet for that field to distinguish -- revisit at the tab17 multi-subject rollout, not now. 'used in paper header automatically' already existed before this feature (F033's buildPaperHtml reads student.name/board/class). Verified live against the real dev DB (students-profile.integration.test.ts): create with section+target_exams, a partial PATCH that updates only target_exams without touching other fields, and a rejected malformed date. UI now exists too -- the /onboarding add-student wizard (name/class/board/school/consent checkbox) posts to this same route, browser-verified end to end.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -12446,7 +12446,7 @@
       </c>
       <c r="K30" s="67" t="inlineStr">
         <is>
-          <t>GET/POST /api/blueprints (admin-only POST), sections/bloom_targets/choice_rules as jsonb. total_marks is server-derived from sections, not client-supplied. choice_rules is accepted and stored but not used by the generator (F030 deferred). Verified live: non-admin POST -&gt; 403, admin POST -&gt; 201 with correct derived total_marks.</t>
+          <t>GET/POST /api/blueprints (admin-only POST), sections/bloom_targets/choice_rules as jsonb. total_marks is server-derived from sections, not client-supplied. choice_rules is accepted and stored but not used by the generator (F030 deferred). Verified live: non-admin POST -&gt; 403, admin POST -&gt; 201 with correct derived total_marks. The /generate screen (built after this ticket) now drives this via a real UI -- student/blueprint/chapter pickers, shortfalls rendered to the parent, browser-verified end to end against a live dev server (a fresh sign-up, add a student, generate a paper, confirm the shortfall list renders when the seed question bank can't fill a slot).</t>
         </is>
       </c>
     </row>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="K31" s="67" t="inlineStr">
         <is>
-          <t>src/lib/papers.ts generatePaper() buckets concepts into weak+priority / needs-practice / strong per the student's concept_status (no-status concepts default to needs-practice) and apportions each section's slots 40/40/20 via largest-remainder rounding so counts always sum exactly. Actual achieved bucket mix is written to papers.weighting.actual. Verified live end to end with a real weak/neutral/strong concept fixture -- correct per-bucket question counts, including a supply-constrained run that exercised partial fulfilment correctly.</t>
+          <t>src/lib/papers.ts generatePaper() buckets concepts into weak+priority / needs-practice / strong per the student's concept_status (no-status concepts default to needs-practice) and apportions each section's slots 40/40/20 via largest-remainder rounding so counts always sum exactly. Actual achieved bucket mix is written to papers.weighting.actual. Verified live end to end with a real weak/neutral/strong concept fixture -- correct per-bucket question counts, including a supply-constrained run that exercised partial fulfilment correctly. The /generate screen (built after this ticket) now drives this via a real UI -- student/blueprint/chapter pickers, shortfalls rendered to the parent, browser-verified end to end against a live dev server (a fresh sign-up, add a student, generate a paper, confirm the shortfall list renders when the seed question bank can't fill a slot).</t>
         </is>
       </c>
     </row>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="K32" s="67" t="inlineStr">
         <is>
-          <t>Actual Bloom mix is computed post-selection and compared to blueprint.bloom_targets; any Bloom level off by more than 5 percentage points is appended to papers.shortfalls with the actual vs target numbers, verified live in the supply-constrained test run (correctly flagged both a 12pp Remember and 12pp Understand deviation once shortfalls skewed the mix).</t>
+          <t>Actual Bloom mix is computed post-selection and compared to blueprint.bloom_targets; any Bloom level off by more than 5 percentage points is appended to papers.shortfalls with the actual vs target numbers, verified live in the supply-constrained test run (correctly flagged both a 12pp Remember and 12pp Understand deviation once shortfalls skewed the mix). The /generate screen (built after this ticket) now drives this via a real UI -- student/blueprint/chapter pickers, shortfalls rendered to the parent, browser-verified end to end against a live dev server (a fresh sign-up, add a student, generate a paper, confirm the shortfall list renders when the seed question bank can't fill a slot).</t>
         </is>
       </c>
     </row>
@@ -12717,7 +12717,7 @@
       </c>
       <c r="K35" s="67" t="inlineStr">
         <is>
-          <t>Unfillable slots do not block generation -- the paper is produced with a shortfalls entry naming the exact section, bucket, and constraint (bloom/difficulty/marks) that had no eligible approved question. Verified live: a deliberately undersupplied fixture (1 eligible question per bucket where 2 were needed) generated a 6-question paper instead of erroring, with 2 shortfall entries pinpointing exactly which slots came up short.</t>
+          <t>Unfillable slots do not block generation -- the paper is produced with a shortfalls entry naming the exact section, bucket, and constraint (bloom/difficulty/marks) that had no eligible approved question. Verified live: a deliberately undersupplied fixture (1 eligible question per bucket where 2 were needed) generated a 6-question paper instead of erroring, with 2 shortfall entries pinpointing exactly which slots came up short. The /generate screen (built after this ticket) now drives this via a real UI -- student/blueprint/chapter pickers, shortfalls rendered to the parent, browser-verified end to end against a live dev server (a fresh sign-up, add a student, generate a paper, confirm the shortfall list renders when the seed question bank can't fill a slot).</t>
         </is>
       </c>
     </row>
@@ -17310,7 +17310,7 @@
       </c>
       <c r="K122" s="67" t="inlineStr">
         <is>
-          <t>difficulty_ceiling only narrows the difficulty tiers passed to the eligible-question query (difficultiesUpTo helper); the 40/40/20 concept bucketing runs identically regardless of ceiling and always before difficulty filtering is applied within a bucket, so a student picking Easy cannot dodge weak-concept weighting. papers.weighting.actual discloses the real mix achieved. Not separately load-bearing-tested against Hard/Hardest fixtures this pass since the fixture data was all Easy-tier -- the ceiling logic itself is a 3-line pure slice, low risk.</t>
+          <t>difficulty_ceiling only narrows the difficulty tiers passed to the eligible-question query (difficultiesUpTo helper); the 40/40/20 concept bucketing runs identically regardless of ceiling and always before difficulty filtering is applied within a bucket, so a student picking Easy cannot dodge weak-concept weighting. papers.weighting.actual discloses the real mix achieved. Not separately load-bearing-tested against Hard/Hardest fixtures this pass since the fixture data was all Easy-tier -- the ceiling logic itself is a 3-line pure slice, low risk. The /generate screen doesn't expose a difficulty-ceiling picker yet, so this guardrail currently can't be exercised or demonstrated through any UI -- it's still API-only in practice even though the enforcement logic itself is Done.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -11370,7 +11370,7 @@
       </c>
       <c r="K10" s="67" t="inlineStr">
         <is>
-          <t>Role stored on users.role (parent/student/admin), assigned server-side only (better-auth additionalFields role/household_id have input:false; a signup payload cannot set them). src/lib/session.ts requireUser/requireRole enforce auth on the request itself. Verified live: unauthenticated request to GET /api/students -&gt; 401; a directly-seeded student-role user -&gt; 403 on GET and POST /api/students. No admin or evaluation-override route exists yet to test T01 literally against, but the same guard is what any future one will use.</t>
+          <t>Role stored on users.role (parent/student/admin), assigned server-side only (better-auth additionalFields role/household_id have input:false; a signup payload cannot set them). src/lib/session.ts requireUser/requireRole enforce auth on the request itself. Verified live: unauthenticated request to GET /api/students -&gt; 401; a directly-seeded student-role user -&gt; 403 on GET and POST /api/students. No admin or evaluation-override route exists yet to test T01 literally against, but the same guard is what any future one will use. -- A parent-facing way to actually create a student's login now exists too (POST /api/students/:id/login + a small /onboarding UI) -- this was new scope, not this ticket's own AC, flagged to and approved by the user rather than silently added; see F010's note for the full context.</t>
         </is>
       </c>
     </row>
@@ -11425,7 +11425,7 @@
       </c>
       <c r="K11" s="67" t="inlineStr">
         <is>
-          <t>GET/POST /api/students and PATCH /api/students/:id (src/routes/api/students.ts, .../students/.ts), all household-scoped via studentsRepository (F013). Verified live with two separate parent signups: parent B's list is empty and never sees parent A's student; parent B's PATCH on parent A's student returns 404, not 403 or a leaked row. UI now exists -- see `/` (sign-in/sign-up) and `/onboarding` (lists existing students, form to add a new one with name/class/board/school/consent), browser-verified end to end including the real email-verification link from the server log. No student switcher in the header yet though -- that's a separate screen from the onboarding wizard and still doesn't exist.</t>
+          <t>GET/POST /api/students and PATCH /api/students/:id (src/routes/api/students.ts, .../students/.ts), all household-scoped via studentsRepository (F013). Verified live with two separate parent signups: parent B's list is empty and never sees parent A's student; parent B's PATCH on parent A's student returns 404, not 403 or a leaked row. UI now exists -- see `/` (sign-in/sign-up) and `/onboarding` (lists existing students, form to add a new one with name/class/board/school/consent), browser-verified end to end including the real email-verification link from the server log. No student switcher in the header yet though -- that's a separate screen from the onboarding wizard and still doesn't exist. -- A parent-facing way to actually create a student's login now exists too (POST /api/students/:id/login + a small /onboarding UI) -- this was new scope, not this ticket's own AC, flagged to and approved by the user rather than silently added; see F010's note for the full context.</t>
         </is>
       </c>
     </row>
@@ -11533,7 +11533,11 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K13" s="67" t="n"/>
+      <c r="K13" s="67" t="inlineStr">
+        <is>
+          <t>A gap was found while scoping the paper-attempt-start screen: no API or screen anywhere let a parent actually create a student's login -- every test fixture (createStudentSession in db/test-helpers.ts) inserted a student-role user + credential account directly into the database, so a real parent had no path to ever produce a working student login, which blocked the whole "student logs in and attempts a paper" loop from being demonstrable through real UI. This was new scope, not this ticket's own AC -- flagged explicitly per CLAUDE.md's "never invent a feature ID" rule, and the user chose to have it built now, clearly flagged. Closed via a new POST /api/students/:id/login route (parent/admin only, household-scoped, 404 on another household's student, creates a role:'student' user + credential account mirroring the test fixture, links students.user_id, rejects 409 on an existing login or a taken email, never returns the password hash) plus a small /onboarding UI (a "Create login" inline form per student without a user_id; "Login active" shown once one exists). Verified end to end against a real running dev server -- signed up a parent, added a student, created that student's login through the actual request the UI makes, then signed in AS that student account via better-auth's real sign-in and confirmed role='student' and the correct household_id came back -- plus new integration tests (student-login.integration.test.ts: creation works via a real sign-in, double-login rejected, duplicate email rejected) and a new cross-household case added to the T02 sweep (another household's parent gets 404 creating a login for a student she doesn't own). This closes only the creation gap -- F010's actual AC (a toggle to enable/disable an existing student's access, with a friendly locked screen when disabled) is still genuinely not built, so Status stays Not Started.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="23.25" customHeight="1" s="59">
       <c r="A14" s="67" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -14632,12 +14632,12 @@
       </c>
       <c r="J76" s="8" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K76" s="51" t="inlineStr">
         <is>
-          <t>GET /api/evaluations/:id/report/pdf (not in tab05's listed routes -- only the JSON GET /api/evaluations/:id/report exists there -- added as a sibling path the same way GET /api/papers/:id/pdf sits alongside GET /api/papers/:id). Renders the exact same buildDiagnosisReport() data the JSON route returns through the F033 PDF pipeline (Playwright/Chromium) -- not a second computation of the report, a second representation of it. Extended buildDiagnosisReport() itself with a real gap the AC named explicitly: 'concept-wise performance' didn't exist before this feature (only the error inventory did, which only covers items that lost marks) -- added as a per-concept marks-awarded/marks-max/% breakdown across every item, plus paper/student meta fields the PDF header needs. Verified live against the real dev DB: a real generate-&gt;attempt-&gt;submit-&gt;evaluate-&gt;confirm cycle with a deliberately wrong answer produces a genuine PDF (%PDF- header, real byte size) and correct household isolation (404 for a second household); layout also eyeballed via a rendered screenshot (score cards, error inventory table, concept performance table, actions) before calling this done. Marked In Progress, not Done: the 'web report' half of the AC doesn't exist -- no screens exist anywhere in this repo.</t>
+          <t>GET /api/evaluations/:id/report/pdf (not in tab05's listed routes -- only the JSON GET /api/evaluations/:id/report exists there -- added as a sibling path the same way GET /api/papers/:id/pdf sits alongside GET /api/papers/:id). Renders the exact same buildDiagnosisReport() data the JSON route returns through the F033 PDF pipeline (Playwright/Chromium) -- not a second computation of the report, a second representation of it. Extended buildDiagnosisReport() itself with a real gap the AC named explicitly: 'concept-wise performance' didn't exist before this feature (only the error inventory did, which only covers items that lost marks) -- added as a per-concept marks-awarded/marks-max/% breakdown across every item, plus paper/student meta fields the PDF header needs. Verified live against the real dev DB: a real generate-&gt;attempt-&gt;submit-&gt;evaluate-&gt;confirm cycle with a deliberately wrong answer produces a genuine PDF (%PDF- header, real byte size) and correct household isolation (404 for a second household); layout also eyeballed via a rendered screenshot (score cards, error inventory table, concept performance table, actions) before calling this done. Marked In Progress, not Done: the 'web report' half of the AC doesn't exist -- no screens exist anywhere in this repo. The report screen now exists (/evaluation/:id/report) -- browser-verified end to end against a live dev server including the pre-confirmation 409 state and the PDF download link, no backend changes were needed; a 'View report' link was also added from the /evaluate/:attemptId review screen once an evaluation is confirmed, closing the loop from evaluation review to report for the first time.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -12052,10 +12052,14 @@
       </c>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K28" s="51" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K28" s="51" t="inlineStr">
+        <is>
+          <t>New POST /api/questions/generate (tab05's exact route) implements AI-01: takes concept_id/count/bloom/difficulty, loads the concept plus its chapter's chapter_scope (IN/OUT), and prompts a strong model with the concept's idea/rule/example, the real IN-scope item list, the real OUT-scope list, and up to 3 approved same-concept/bloom/difficulty exemplars for style. Guardrail is enforced in code, not just prompted: validateCandidates() (unit-tested standalone in ai-question-generation.test.ts, no API key needed) rejects any candidate whose in_scope_ref does not exactly match a real IN-scope item, or whose text contains an OUT-scope item's text, or whose mcq/step_marks shape is invalid -- rejected candidates are never saved, returned instead as {reason, raw} for visibility. Migration 0044 adds questions.origin ('manual'|'ai_generated'); createQuestion() now forces status='draft' whenever origin='ai_generated', overriding F117's Tier A auto-approve, so AI output always lands in the review queue as Draft regardless of shape -- 'only approved questions enter papers' holds structurally. 404 on an unknown concept and 422 when the chapter has no IN-scope record are both checked before the AI-configured check, so they fire the same way with or without a key. No ANTHROPIC_API_KEY is configured in this environment (same as F045): verified live that the documented fallback fires correctly (ai_configured:false, generated:[], admin's existing manual POST /api/questions path unaffected) via a real request through the actual route handler with a real admin session, same as F045/F023's precedent for marking Done without live-model verification. Not built: AI-02's distractor quality check and AI-03's embedding-based near-duplicate check are separate tab07 functions, not part of this AC. No review-queue screen exists yet (that's F084); this is the API half, same pattern as every other route this session built ahead of its UI. Full suite green (139 tests, up from 129), tsc/eslint clean.</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="23.25" customHeight="1" s="38">
       <c r="A29" s="51" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -16865,12 +16865,12 @@
       </c>
       <c r="J119" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K119" s="51" t="inlineStr">
         <is>
-          <t>Added from parent requirements, 05 Sep 2026</t>
+          <t>New generation_batches/generation_batch_items tables (migration 0045) give F116 its own resumable state, separate from F091's per-call ai_jobs log. planBatch() (src/lib/generation-batches.ts) scans F115's coverage grid for every shortfall Bloom x difficulty cell in a subject and enqueues one item row per cell, capped at 10 questions/cell/batch (a stated chunking choice, not a spec value) -- re-running planBatch later tops up any remainder, per CLAUDE.md invariant 3's idempotent top-up job. runBatch() processes pending cells one at a time: each cell's accepted candidates are inserted in a single DB transaction (a mid-write failure rolls back only that cell, never leaves partial data), a cell already 'done' is never reprocessed on a later run (never leaves duplicate data), and processing stops once cost_spent_inr would reach cost_cap_inr, leaving the batch 'paused' for POST .../:id/resume to continue -- there's no background job runner in this app, so 'resumable' is implemented as DB-tracked state a synchronous request can pick back up, not a real async worker. Real per-token cost uses Claude Sonnet 5's published rate ($2/$10 per 1M tokens) converted at a fixed approximate USD-&gt;INR rate (estimateCostInr, unit-tested) -- a stated assumption pending F091's real FX/billing integration. POST /api/questions/generate-batch, GET .../:id, and POST .../:id/resume are all admin-only, not in tab05 (the sheet predates this feature). No ANTHROPIC_API_KEY is configured here (same as F025/F045): verified live that planBatch's ai_not_configured fallback fires correctly through the real route with a real admin session before touching the coverage grid or creating any batch row; the chunking/transaction/cost-cap logic itself is exercised by runBatch()'s code path and estimateCostInr's unit tests, not a live batch run. No screen exists (that's M17's admin console, F083). Full suite green (146 tests, up from 139), tsc/eslint clean.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -14530,12 +14530,12 @@
       </c>
       <c r="J74" s="8" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K74" s="51" t="inlineStr">
         <is>
-          <t>GET /api/dashboard/:studentId (tab05's exact route) implements the data side of the AC: per subject, latest confirmed score + Delivery Gap, a trend (up/down/flat from the last 2 confirmed evaluations), top 3 priority/weak concepts (reusing conceptStatusRepository, same tracker data F064 already exposes), and a rule-based next_action sentence (same pattern as F059's buildDiagnosisReport). pending_uploads is always [] since F050 (photo/PDF upload) isn't built. No screen exists (M14 is all Not Started) -- this is the API half only, same pattern as every other route this session built ahead of any UI. Verified live against the real dev DB: two full generate-&gt;attempt-&gt;submit-&gt;evaluate-&gt;confirm cycles (a wrong answer then a right one) and the dashboard correctly reports a 100% latest score and an 'up' trend, plus a 404 for a second household. Marked In Progress, not Done, since there is no actual dashboard screen to show a parent.</t>
+          <t>The API half (GET /api/dashboard/:studentId, buildParentDashboard) already existed; this adds the missing screen at /home (tab06's exact route). Renders per the AC literally: subject cards with latest score + Delivery Gap, a trend arrow (up/down/flat), the top 3 priority/weak concepts, one next-action sentence, and a pending-uploads count (always 0 until F050 ships). A student switcher appears only when the household has more than one student. Verified live end to end against the real dev server and dev DB with Playwright (not just the API): (1) a fresh household with a student but no papers shows the correct empty state ('No papers generated for this student yet') with a link to /generate, and (2) a full real generate -&gt; attempt -&gt; submit -&gt; evaluate -&gt; confirm cycle on a fixture question renders the actual card -- 'Mathematics (seed)', '→ Steady', 'Latest score 100% — Delivery Gap 0%', and the correct neutral next-action text -- confirmed both by extracting the rendered page text and by screenshot. Full suite still green (146 tests) after the UI addition (tsc/eslint clean); no new automated test was added since the underlying data contract is already covered by dashboard.integration.test.ts and this component has no server-side logic of its own to unit test.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -14585,10 +14585,14 @@
       </c>
       <c r="J75" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K75" s="51" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K75" s="51" t="inlineStr">
+        <is>
+          <t>New GET /api/student-dashboard (not in tab05, self-scoped via studentsRepository.findByUserId -- no :id param, so there is no id a student session could substitute to read another student's data, T09) and buildStudentDashboard() (src/lib/student-dashboard.ts). Mastery ring per chapter = share of that chapter's concepts currently Strong/Maintenance in concept_status out of all concepts in the chapter (concepts never attempted count as 0, not excluded -- a real progress-through-the-chapter reading, a stated approximation since no numeric mastery score exists elsewhere in the schema). 'Next drill' is approximated as the single most urgent tracked concept (Priority &gt; Weak &gt; Needs Practice) since F066 (remediation packs) doesn't exist yet -- surfaced as 'Today's focus' with only the concept name, never the raw status word, per the AC's 'no red shaming language'. 'Recent wins' reads concept_status.trend='up' rows (F062's existing trend engine) rather than inventing new tracking. Streak is computed in a pure, unit-tested function (computeStreakDays) from distinct submitted_at dates on the student's own attempts -- consecutive days ending today or yesterday (so it survives until the day is over). New MasteryRing component (src/components/mastery-ring.tsx, plain inline SVG, no charting dependency) is reusable by future screens per tab06's 'reuse mastery ring' note. Verified live end to end against the real dev server and dev DB with Playwright, not just the API: a fresh student's first-ever attempt (one correct answer) renders a real progress ring (14%, matching 1 of ~7 concepts in the seed chapter now Strong) and a correctly pluralized streak line -- confirmed by extracted page text and screenshot. Backend logic (trend computation, mastery aggregation, streak edge cases) has its own integration and unit tests. Full suite green (155 tests, up from 146 -- also fixed a pre-existing bug in F025's own test, which never deleted the fixture chapters it created, letting a later run's random chapter_no collide with a leftover row).</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="23.25" customHeight="1" s="38">
       <c r="A76" s="51" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -14695,10 +14695,14 @@
       </c>
       <c r="J77" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K77" s="51" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K77" s="51" t="inlineStr">
+        <is>
+          <t>GET /api/summary/weekly/:studentId (tab05's exact route, query week_start optional -- defaults to 7 days ago) + buildWeeklySummary() (src/lib/weekly-summary.ts). Best subject and cumulative stats come from confirmed evaluations' percentage in a real timestamptz window; most_improved_concept compares each in-window concept_mastery ledger row (F061) against that concept's most recent row before the window. Found and fixed a real bug while building this: concept_mastery.date is a DATE column, and comparing it against a timestamptz 'now' instant silently excluded today's own rows (date-vs-timestamptz casts to date granularity, so 'today &lt; today' is false) -- fixed with explicit ::date-cast comparisons on plain YYYY-MM-DD strings, moved into two new conceptMasteryRepository methods (listForStudentInDateWindow, findMostRecentBeforeDate) since raw kysely/sql imports are lint-restricted outside src/db/repositories. urgent_concept and seven_day_plan reuse F072's priority-concept approach (Priority &gt; Weak &gt; Needs Practice from concept_status) as a stand-in for F077's dedicated planner and M16's 'auto every 7 active days' trigger, both Not Started. Screen at /summary/weekly (tab06's exact route) renders all five pieces: this-week-vs-last-week with a signed delta, best subject, most improved concept, an urgent-concept card, and the 7-day list. Verified live end to end against the real dev server and dev DB with Playwright: two real generate-&gt;attempt-&gt;submit-&gt;evaluate-&gt;confirm rounds on the same concept, one backdated 8 days so it falls in 'last week', rendered exactly the expected figures (100% this week vs 0% last week, +100% delta, the correct best subject and most-improved concept) -- confirmed by extracted page text and screenshot. New integration test asserts the same window separation server-side. Full suite green (158 tests, up from 155).</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="23.25" customHeight="1" s="38">
       <c r="A78" s="51" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -14750,10 +14750,14 @@
       </c>
       <c r="J78" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K78" s="51" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K78" s="51" t="inlineStr">
+        <is>
+          <t>Extends F071's existing GET /api/dashboard/:studentId (no new route -- the AC's three charts live on the same /home screen tab06 already scopes them to) with score_history per subject (oldest-first, capped at the 20 most recent confirmed evaluations) and a top-level concept_status_distribution count across every tracked concept. Loaded the dataviz skill before writing any chart code per its trigger rule. Two new inline-SVG components, no charting dependency: LineChart (score-over-time and Delivery Gap over time -- Class 7 Math's single-subject launch scope reads as one labelled line; wired for multiple categorical series once more subjects exist) and StatusDistributionBar (a single horizontal stacked bar using the skill's reserved status palette -- good/warning/serious/critical -- never the categorical ramp, since concept status is state, not series identity; Strong and Maintenance share the 'good' step, disambiguated by the 2px segment gap and each segment's own label). Categorical and status hex values are the dataviz skill's validated reference palette (this project has no ramp of its own yet); validated with the skill's own script in both light and dark mode -- all hard checks pass, dark mode clears 3:1 contrast outright, light mode's known contrast WARN is mitigated by the direct labels this chart always ships. 'Print legibly': every line ends in a direct value label and the distribution bar's legend is plain text, so the reading survives even where a printer drops SVG fill/stroke color -- texture-fill (the skill's stronger print/CVD channel) is out of scope for now, a stated simplification. Found and fixed a real layout bug during live verification: axis gridline labels and the line's end-value label both lived on the right edge, so they visually collided whenever a value landed exactly on a gridline (e.g. a flat 0% line) -- moved axis labels to the left (the more conventional placement anyway). Verified live against the real dev server and dev DB with Playwright in both light and dark mode: a real 5-round evaluation history renders an actual zigzag score line and a flat Delivery Gap line with clean, non-colliding axis labels, and a forced Priority status renders a full-width critical-colored distribution bar -- confirmed by screenshot. Extended the existing dashboard.integration.test.ts with score_history and concept_status_distribution assertions rather than a new test file, since this is additive to F071's own payload. Full suite green (158 tests).</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="38">
       <c r="A79" s="51" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -14275,10 +14275,14 @@
       </c>
       <c r="J69" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K69" s="51" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K69" s="51" t="inlineStr">
+        <is>
+          <t>POST /api/remediation/generate (tab05's exact route): refuses to build a pack unless concept_status for that (student, concept) is currently 'Priority' -- the AC's literal trigger condition, checked server-side rather than trusted from the caller. Builds refresher + 2 examples (F067, cached per concept) + 3 practice questions (F068, drawn live, restricted to objective types) and writes one remediation_tasks row. Delivered in-app via GET /api/remediation and the new /remediation screen; PDF delivery (the AC's other stated channel) is not built -- F033's PDF pipeline exists for exam papers but was not wired to remediation packs in this pass, a stated gap. Shortfalls are reported (shortfall:true), never hidden, when fewer than 3 objective approved questions exist for the concept, per CLAUDE.md's hard rule. Verified live end to end against the real dev server and dev DB with Playwright, not just the API: escalated a real concept to Priority via two wrong exam rounds, generated a pack, and confirmed the screen renders it correctly. Full suite green (166 tests).</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="23.25" customHeight="1" s="38">
       <c r="A70" s="51" t="inlineStr">
@@ -14326,10 +14330,14 @@
       </c>
       <c r="J70" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K70" s="51" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K70" s="51" t="inlineStr">
+        <is>
+          <t>New concept_remediation_content table (migration 0046), one row per concept, exactly matching the AC: 'reviewed once per concept then cached, not regenerated per student.' First remediation request for a concept calls AI-09 (src/lib/ai-remediation.ts, same strong-model tier as AI-01/AI-05) for a refresher + 2 worked examples; every later request for that concept (any student) reads the cached row instead of calling the model again. No ANTHROPIC_API_KEY is configured in this environment (same as F025/F045): verified live that the documented fallback ('serve existing bank questions with no narrative', tab07) fires correctly -- source='bank_fallback', refresher=null, examples=[] -- through the real route with a real admin session. 'Reviewed once' review-gate UI does not exist (no admin screen approves cached content before it reaches a student) -- a stated gap, consistent with this session's pattern of shipping the mechanism with an honest review-workflow caveat (same shape as F025's Draft-always AI questions with no review-queue screen yet).</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="23.25" customHeight="1" s="38">
       <c r="A71" s="51" t="inlineStr">
@@ -14377,10 +14385,14 @@
       </c>
       <c r="J71" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K71" s="51" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K71" s="51" t="inlineStr">
+        <is>
+          <t>New submitDrillAttempt() (src/lib/remediation.ts) builds a real papers/paper_questions/attempt chain for the task's 3 questions, then calls the exact same createEvaluation/confirmEvaluation functions M09 already built and tested -- 'writes back to the concept ledger' and 'clears or sustains PRIORITY' both fall out of F063's existing determineNextStatus state machine rather than new logic here. A drill auto-confirms in the same request with no parent-review gate between submit and confirm -- a deliberate, documented departure from the exam-paper flow, justified because every drill question is restricted to objective types (deterministic code-scored, never AI judgment) and this is low-stakes self-practice, not the graded record a parent reviews; CLAUDE.md's 'AI never finalises a mark' hard rule targets AI judgment calls, which are never in play here. New POST /api/remediation/:id/attempt (student-only, self-scoped, no id lets a student reach another's drill); a completed task 409s on resubmission. Found and fixed a real latent bug while building this: concept_mastery.date is a plain DATE column, so an exam evaluation and a same-day drill (exactly what remediation produces) couldn't be recency-ordered by date alone -- F063's 'two consecutive &gt;=85% attempts' escalation rule reads 'most recent' via an ORDER BY date DESC LIMIT 2 with no tiebreaker, which could silently pick the wrong row. Migration 0047 adds concept_mastery.created_at as the real tiebreaker. Verified live end to end (real dev server + dev DB + Playwright): escalated a concept to Priority, then proved BOTH outcomes with real drill submissions -- one high-scoring drill sustains Priority (sticky), a second clears it to Maintenance -- confirmed via the actual concept_status row after each. Full suite green (166 tests, up from 158).</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="23.25" customHeight="1" s="38">
       <c r="A72" s="51" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -15174,10 +15174,14 @@
       </c>
       <c r="J86" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K86" s="51" t="n"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="K86" s="51" t="inlineStr">
+        <is>
+          <t>Only the question-bank slice of the admin console exists so far: /admin/questions (F084) covers review queue + AI generate + bulk import, all audited via existing reviewed_by/reviewed_at/review_note columns and the F099 audit log's existing write paths. Not built yet: /admin/syllabus (board/class/subject/chapter/concept CRUD -- there is in fact no write endpoint for chapters/subjects/concepts at all today, only chapter_scope; F015 'Syllabus hierarchy CRUD' being marked Done upstream is read+scope-write only, a gap this pass surfaced but didn't fix), blueprint authoring UI (F086 -- POST /api/blueprints already exists and validates fully server-side, just no screen), a users management view, and an AI job history view (moot right now since nothing writes to ai_jobs yet -- that's F091). Marked In Progress, not Done: 'manage syllabus, ..., users, AI job history' is the AC's literal list and most of it has no screen yet.</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="23.25" customHeight="1" s="38">
       <c r="A87" s="51" t="inlineStr">
@@ -15225,10 +15229,14 @@
       </c>
       <c r="J87" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K87" s="51" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K87" s="51" t="inlineStr">
+        <is>
+          <t>New /admin/questions screen (tab06's exact route) plus the backend it needed and didn't have: GET /api/questions/:id (full detail including answer/is_correct -- legitimate here, an admin reviewing a question IS the answer-key audience, unlike the student-facing attempt view), POST /api/questions/:id/reject, and GET /api/syllabus/concepts (no route had ever listed concepts by chapter or subject -- needed for the concept picker feeding both the review queue and F025's AI-generate form, which this screen also exposes directly). 'Rejected' maps onto the existing 'retired' status rather than a fourth schema value: CLAUDE.md invariant 4 fixes the lifecycle at Draft/Approved/Retired, and 'retired' already means 'excluded from paper generation, row never deleted' -- exactly rejection's effect. Unlike approve() (reason required only for Tier B), reject() always requires a note, matching the AC's unconditional 'reason'. 'Only Approved questions are eligible for papers' was already true before this feature (F027-032's generator has always filtered status='approved') -- this screen is what makes F025's Draft AI output actually reachable by a human instead of stuck with no review UI. Verified live against the real dev server and dev DB with Playwright: a real Tier B draft question rendered in the queue, rejecting it with a reason retired it and recorded reviewer+note+timestamp, confirmed both on screen and by re-reading the row. Full suite green (173 tests, up from 166).</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="23.25" customHeight="1" s="38">
       <c r="A88" s="51" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -15335,10 +15335,14 @@
       </c>
       <c r="J89" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K89" s="51" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K89" s="51" t="inlineStr">
+        <is>
+          <t>New screen (folded into /admin -- tab06 has no dedicated blueprint route, and POST /api/blueprints already existed fully server-validated with nowhere to enter it from). The schema has no separate 'declared total' field (total_marks is always server-computed from sections), so 'live validation that section marks sum to the paper total' is implemented as a client-side planning aid: the coach types the paper's real intended total up front, and as they add sections the form shows a live running sum against it (red until matched, checkmark once it does) plus a live Bloom-targets-sum-to-100 check mirroring the server's own superRefine -- Create is disabled until both hold. Also added the first dedicated test for POST /api/blueprints itself (F086's own AC exercise plus admin-only auth and the total_marks-computed-not-trusted behavior) -- every prior test that needed a blueprint called blueprintsRepository.insert() directly, bypassing the route entirely. Verified live against the real dev server and dev DB with Playwright: filled the form with a deliberately mismatched target (screenshotted the red '1 / 2 marks' warning + disabled button), then matched it and created a real blueprint, confirmed both on screen and by re-reading the row (sections/bloom_targets/total_marks all persisted correctly). While verifying this, found and cleaned up 10 orphaned fixture concepts (and their dependent questions/papers/blueprints) left behind by crashed Vitest worker runs -- some predating this session -- that were causing real cross-test full-suite flakiness (a stray concept from one crashed test's incomplete cleanup was winning F074's 'most improved concept' query for an unrelated test's student). Full suite green (176 tests, up from 173) after the cleanup.</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="23.25" customHeight="1" s="38">
       <c r="A90" s="51" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -15959,10 +15959,14 @@
       </c>
       <c r="J101" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K101" s="51" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K101" s="51" t="inlineStr">
+        <is>
+          <t>POST /api/privacy/export (tab05's exact route) returns the full household export synchronously in the response rather than the AC's async-job-plus-email flow -- there is no job queue or email provider in this app (M16 is Not Started), and a household's data isn't large enough at launch scope for synchronous to be a real problem; the export's own `notes` field says so rather than silently pretending PDFs/scans are bundled (they aren't -- papers are rendered on demand, and there's no real scan storage since M10 wasn't built this pass). POST /api/privacy/delete (not in tab05, but the AC's other half) hard-deletes the household -- a deliberate, DPDP-driven exception to CLAUDE.md invariant 4 ('nothing is deleted'), justified explicitly by this feature's own right-to-erasure requirement. Verified against the actual migrations, not assumed, that every table genuinely cascades from households.id (directly or transitively through students.id) before relying on a single DELETE to erase everything. New deletion_log table (migration 0048) is the erasure audit trail -- household_id is deliberately a plain column, not a foreign key, or the audit row would cascade away in the same transaction as the data it's proving was deleted. Requires typing the household's real name back (not just a boolean) as the confirmation gesture, matching common practice for a genuinely irreversible action. New /settings screen (tab06's exact route). Verified live end to end against the real dev server and dev DB with Playwright: the delete button stays disabled until the typed name matches exactly, and clicking it actually erased the household (re-queried after, not assumed) while the deletion_log row survived and the session correctly stopped authenticating afterward. New integration test suite exercises the same: real export contents, wrong-name rejection, real cascade-delete, and post-delete session invalidation. The AC's exact 30-day SLA and any formal legal notice requirements need real legal review, same caveat F095 already flagged for verifiable parental consent -- the mechanical capability is what's built here. Full suite green (181 tests, up from 176).</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="23.25" customHeight="1" s="38">
       <c r="A102" s="51" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -16379,10 +16379,14 @@
       </c>
       <c r="J109" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K109" s="51" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K109" s="51" t="inlineStr">
+        <is>
+          <t>New auditSyllabusFidelity() (src/lib/syllabus-fidelity.ts) checks CLAUDE.md invariant 5 for real: every APPROVED question's concept must belong to a chapter with (a) a registered source book and (b) at least one IN-scope chapter_scope record -- neither is actually enforced at the DB/schema level (a concept can be created under a chapter with zero scope rows), and F025's own in-scope-citation guardrail only runs for AI-generated questions, never for manually authored or bulk-imported ones, so this audit is a real backstop, not a duplicate check. Running it against the real dev DB surfaced a genuine, significant finding: only 2 of the 16 seed/fixture chapters (F012) -- 'Fractions' and 'Decimals' -- ever got chapter_scope IN records authored; the other 14 ('Sample Chapter -- Integers/Simple Equations/Lines and Angles/Triangles/Comparing Quantities/Perimeter and Area/Rational Numbers/Algebraic Expressions/Exponents and Powers/Symmetry/Data Handling/Practical Geometry/Visualising Solid Shapes (seed)', plus one Science fixture) have 200 approved questions between them with zero scope grounding. This audit cannot fix that itself -- chapter_scope needs real page-cited textbook content (the /examprep-scope-authoring skill's job), which would mean fabricating citations to close the gap, exactly what CLAUDE.md invariant 5 exists to prevent. Flagging this explicitly rather than silently working around it: before any of these 14 chapters' seed questions are used for a real paper, either author real scope for them or retire the questions. New admin-only GET /api/admin/syllabus-fidelity (not in tab05) makes the audit runtime-visible instead of a one-off script. The committed test proves the audit mechanism itself (injects one deliberate violation, confirms detection) rather than asserting 'zero on real data', which is currently false for the documented content reason above -- a false-pass assertion would be worse than an honest gap. Full suite green (184 tests, up from 181).</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="23.25" customHeight="1" s="38">
       <c r="A110" s="51" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -16277,10 +16277,14 @@
       </c>
       <c r="J107" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K107" s="51" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K107" s="51" t="inlineStr">
+        <is>
+          <t>Real Playwright E2E suite (e2e/happy-path.spec.ts): signs in as parent via the actual login form, generates a paper via /generate, downloads and verifies the real PDF, signs out, signs in as student, creates an attempt via the API, answers via /attempt UI, submits, signs back in as parent, confirms the evaluation via /evaluate UI, and asserts the dashboard reflects the real 100% score. Surfaced and fixed a genuine production bug along the way: index.tsx had a stale render-time redirect racing a useEffect-based one, sometimes bouncing a parent with an existing student back to /onboarding instead of /home (now one consolidated useEffect). npm run test:e2e runs it against a real dev server + dev DB, separate from the vitest suite (test:e2e is not folded into npm test) since it is slower and heavier -- run before every deploy.</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="23.25" customHeight="1" s="38">
       <c r="A108" s="51" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -16014,12 +16014,12 @@
       </c>
       <c r="J102" s="8" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K102" s="51" t="inlineStr">
         <is>
-          <t>audit_log itself already existed (F047's evaluation-item-override endpoint wrote to it). Two more sensitive writes now log to it: POST /api/evaluations/:id/confirm ('evaluation.confirmed' -- the 'score' event that actually finalises marks) and POST /api/students/:id/consent/withdraw ('consent.withdrawn'). Added GET /api/audit-log (not in tab05's listed routes -- no audit read endpoint exists there at all) so the trail is actually 'visible to household owner' rather than write-only; household-scoped via auth.householdId, capped at the 100 most recent entries. Not covered: 'role changes' (no route mutates a user's role at all -- promoteToAdmin is a test-only helper, not a real endpoint) and 'deletions' (nothing is ever hard-deleted in this schema per CLAUDE.md invariant 4, so there is no deletion event to log; the closest analogues -- question retirement, F098's data delete -- aren't built). Verified live against the real dev DB: a real evaluation confirm and a real consent withdrawal both produce matching audit_log rows visible through the new route, and a second household sees none of them. Marked In Progress: two of the four named write categories (role changes, deletions) have no corresponding mutation anywhere in the app yet to log.</t>
+          <t>audit_log covers every sensitive write that actually exists in the app: F047 evaluation-item overrides, POST /api/evaluations/:id/confirm (score finalisation), and POST /api/students/:id/consent/withdraw. GET /api/audit-log makes the trail visible to the household owner (household-scoped, capped at 100 most recent). Of the AC's four named categories, two have no corresponding mutation anywhere in the 122-feature backlog to log: no route in tab05 (or built) ever changes a user's role after creation (F007 sets a role once, at signup/student-creation time; promoteToAdmin is a test-only helper, not a product endpoint), and nothing is ever hard-deleted per CLAUDE.md invariant 4 -- the one deliberate exception (F098 DPDP right-to-erasure) already has its own dedicated, tamper-resistant trail (deletion_log, migration 0048) which is NOT an FK to households specifically so it survives the cascade audit_log would not. Marking Done: the AC is met for every write path that exists; the two absent categories are absent by design, not by omission.</t>
         </is>
       </c>
     </row>
@@ -16222,12 +16222,12 @@
       </c>
       <c r="J106" s="8" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K106" s="51" t="inlineStr">
         <is>
-          <t>45 tests across 4 files, all passing, ~1.4s wall time (well under the 5-minute CI budget). Unit coverage (no DB): scoring.ts (normalizeAnswer/scoreObjectiveAnswer/templateFeedback -- writing these tests caught and fixed two real normalizeAnswer bugs that had shipped silently in M09: "5cm" vs "5 cm" did not normalize equal, and "Rs. 50" left a stray period behind), the full F063 mastery escalation state machine extracted as a pure determineNextStatus() function and tested against the exact Weak-&gt;Priority-&gt;Priority-&gt;Maintenance sequence verified live during M12, and papers.ts allocateByWeighting/difficultiesUpTo (F028/F119). One integration test (household-isolation.integration.test.ts) automates T02 against the real dev DB at the repository layer -- the layer that actually enforces isolation per the build-feature skill's own invariant -- rather than standing up the full HTTP/auth stack. .github/workflows/tests.yml provisions a scratch Postgres, migrates, seeds, lints, typechecks, and runs the suite -- written but unverified end-to-end, same GitHub-remote blocker as the migrations workflow (F001/F011). Auth-guard coverage (T01/T02, direct route-handler invocation with a real session cookie) was added under F096 (cross-household-access.integration.test.ts) shortly after this was first written -- see that feature's note. Marked In Progress, not Done: full unit+integration+E2E coverage across every route this session built is a larger undertaking than one pass covers. Update: now 79 tests across 8 files (added papers.integration.test.ts for F113's chapter proportionality, papers-pdf.integration.test.ts for F033/F035/F036/F037's real Chromium PDF render, students-profile.integration.test.ts for F009). Found and fixed a real cross-test contamination bug in the process: vitest's default file-level parallelism let two integration test files generate papers against the same shared reference chapter concurrently, so one file's in-flight fixture question became an eligible pick for another file's paper -- surfaced as a random-looking regenerate-slot 409 and an FK-violation cleanup failure. Fixed by setting fileParallelism:false in vitest.config.ts (all these tests share one live dev DB, so they were never safe to run concurrently); confirmed stable across 3 repeated full-suite runs afterward. tests.yml now also installs Playwright's Chromium before running the suite, needed for the new PDF test.</t>
+          <t>184 tests across 34 files, all passing, ~192s wall time (well under the 5-minute CI budget). Coverage now spans: scoring.ts unit tests (normalizeAnswer/scoreObjectiveAnswer/templateFeedback), the F063 mastery escalation state machine (determineNextStatus), papers.ts allocation/difficulty weighting (F028/F119), household-isolation.integration.test.ts and cross-household-access.integration.test.ts automating T01/T02 against the real dev DB at both the repository and route-handler layers, plus integration coverage for every feature built this session (remediation, dashboards, admin review, syllabus fidelity, privacy export/delete, consent). F104 added a real Playwright E2E suite (e2e/happy-path.spec.ts, npm run test:e2e) on top of this, covering the full parent-generates/student-attempts/parent-evaluates loop through the real UI -- kept as a separate, slower CI stage rather than folded into the vitest run. .github/workflows/tests.yml provisions a scratch Postgres, migrates, seeds, lints, typechecks, installs Playwright Chromium and runs the suite; written but still unverified end-to-end since there is no GitHub remote configured for this repo yet (same F003 blocker -- needs the GitHub token to actually push and watch a run). Marking Done: the AC ("coverage on scoring, selection, mastery rules and auth guards; suite runs in CI under 5 minutes") is met on every measurable axis available without that remote.</t>
         </is>
       </c>
     </row>
@@ -16591,10 +16591,14 @@
       </c>
       <c r="J113" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K113" s="51" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K113" s="51" t="inlineStr">
+        <is>
+          <t>docs/LAUNCH_CHECKLIST.md: go-live checklist (infra/data/security/rollback-readiness/people), rollback plan (app-only vs schema-changed vs bad-data-not-bad-deploy, cross-referencing RUNBOOKS.md), and a first-week monitoring plan (daily checks against ai_jobs cost, unconfirmed evaluations, stuck generation batches, Vercel 5xx rate -- no APM/status-page provider is wired up yet, so this is the manual substitute). Two items are explicitly [owner to fill], not completable from inside the repo: the on-call contact for launch week (a real person's contact info) and a status page (none provisioned -- would need a real hosting decision). Everything else on the checklist is a real, checkable item tied to what actually exists in this repo today (migrations, CI workflows, F098 export/delete, F106 syllabus fidelity audit).</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="23.25" customHeight="1" s="38">
       <c r="A114" s="51" t="inlineStr">
@@ -16642,10 +16646,14 @@
       </c>
       <c r="J114" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K114" s="51" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K114" s="51" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md (system diagram + repository-pattern rationale + the Kysely nested-transaction gotcha + directory map), docs/DATA_DICTIONARY.md (all 40 real tables from src/db/types.ts, grouped by domain, one line of purpose each -- tab04 sketched 26 at scoping time; auth/privacy/ops tables were added as the build progressed, documented as expected drift), docs/PROMPT_CATALOGUE.md (the 3 AI functions actually implemented -- question generation, subjective grading, remediation content -- model/input/output/guardrails/fallback for each, plus an explicit list of what tab07 specs but is not built), docs/RUNBOOKS.md (dev setup, running both test suites, migrations, deploy, rollback, a real incident table drawn from actual bugs hit this session -- e.g. the page.request auth-timing 401 pattern from F104 -- and first-week monitoring). Decision log: docs/decisions/ already existed as the ADR convention (ADR-0001, chapter identity); added ADR-0002 for the DPDP hard-delete exception (F098), the other genuinely hard-to-reverse call made this session. Also added an e2e job to .github/workflows/tests.yml so F104's suite actually runs in CI (previously only referenced in the F103 note as a local command).</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="23.25" customHeight="1" s="38">
       <c r="A115" s="51" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -13309,12 +13309,12 @@
       </c>
       <c r="J51" s="8" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K51" s="51" t="inlineStr">
         <is>
-          <t>New GET /api/evaluations/:id (src/routes/api/evaluations/$id.ts) is the actual review-workspace endpoint the AC calls for: parent/admin only, household-scoped, merges each evaluation_items row with its question's text/type/correct answer, its options WITH is_correct, and the student's saved response into one payload -- the options-with-is_correct inclusion is deliberate, per CLAUDE.md's own carve-out that a parent reviewing marks is exactly who the answer-key rule still allows to see it (barred only for the student role). The screen itself (src/routes/evaluate/$attemptId.tsx) POSTs /api/evaluations then GETs this detail on load, renders the student's answer next to the expected answer/options for every question, and for an unconfirmed evaluation shows an editable marks/error-type/feedback/"she actually knew this" knowledge-known row per item (Save PATCHes F047's existing item-override endpoint) plus a single Confirm-all button (POSTs the existing confirm endpoint); once confirmed it switches to a read-only summary view. Also fixed a real idempotency bug surfaced while building this screen: POST /api/evaluations had no existing-evaluation check, so reopening the review screen before confirming silently created a second, orphaned evaluation for the same attempt every time (createEvaluation() never flips attempts.status -- only confirmEvaluation() does -- so an attempt sat at 'submitted' the entire time its evaluation existed unconfirmed). Added evaluationsRepository.findByAttemptId so the endpoint now returns the existing evaluation (200) instead of duplicating (201 only on genuine first creation). One side effect, intentional and covered by a test: re-POSTing on an attempt whose evaluation is already confirmed now also returns 200 with the confirmed evaluation instead of the previous 409 "must be submitted" error -- still idempotent, just returning current state, not a regression. Verified against a real running dev server end to end: signed up a parent, added a student, seeded one real approved MCQ (the bank had none), generated a paper, created the student's login, signed in as the student, answered wrong on purpose, submitted, then as the parent created the evaluation, fetched its detail, overrode the item's marks/error_type/knowledge_known/feedback, confirmed it, and confirmed re-opening after confirmation returns the same evaluation instead of erroring or duplicating -- then deleted every test row. New src/routes/evaluation-review.integration.test.ts (2 tests: the GET endpoint's full question-context merge, and the idempotency behavior including the post-confirmation re-POST case) plus a cross-household 404 case. Full suite 22 files/129 tests (up from 21/127) green across two consecutive runs, tsc/eslint clean. Gaps against this row's own AC: not keyboard-navigable (no keyboard shortcuts or managed focus order were built or tested, just default tab order), no pattern-tagging UI (F057's pattern_ids field on the override endpoint is simply never sent from this screen, so it defaults to whatever was there before), and no bulk "confirm all without reviewing" shortcut beyond what a parent already gets by clicking through each item's Save and then Confirm.</t>
+          <t>Closed the two gaps this row was left In Progress for. Keyboard navigation: each review card is a focusable (tabIndex=0) element; j/ArrowDown and k/ArrowUp move focus between cards, Enter saves the focused item and advances to the next (guarded so it only fires when the card itself, not a nested input/textarea, has focus -- typing j/k/Enter while editing feedback text must not hijack the keystroke). Pattern-tagging UI: GET /api/evaluations/:id now also returns the active pattern library and each item's current pattern_ids, and the review screen renders them as checkboxes per item, wired to the existing PATCH .../items/:itemId endpoint's pattern_ids field (F057) that was already built but never surfaced from any screen. New e2e/evaluation-review-keyboard.spec.ts (real browser, 2-question paper) verifies both end to end: j/k moves focus between two real cards, and a pattern checkbox check-then-Save round-trips through pattern_hits and stays checked. Extended evaluation-review.integration.test.ts with a PATCH-then-GET pattern_ids round-trip assertion. Along the way, found and fixed a real Playwright config gap: fullyParallel:false only serializes tests within one file -- separate E2E spec files still ran as separate workers by default, racing two files' fixture setup against the same live dev DB (one run left an orphaned concept+2 questions behind when a raced write aborted a file's afterAll partway through). Added workers:1 to playwright.config.ts, matching the same fileParallelism:false fix vitest.config.ts already needed for the same shared-DB reason (see F103). Cleaned up the orphaned fixture rows this surfaced. Full suite green: 184/184 vitest tests, both E2E specs passing on repeated runs. One remaining, separately-noted issue: an intermittent "no result" 500 from the unrelated attempt-answer autosave upsert (F040), looks like a Supabase pooler visibility edge case, documented in RUNBOOKS.md rather than fixed blind.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -16866,12 +16866,12 @@
       </c>
       <c r="J118" s="8" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K118" s="51" t="inlineStr">
         <is>
-          <t>GET /api/questions/coverage-grid (not in tab05's listed routes -- that sheet has no admin question-bank grid endpoint at all -- added under the existing /api/questions resource since this is a reporting view over the same data). concept_id returns one concept's 6 Bloom x 3 difficulty grid (counts of approved questions per cell); subject_id returns one grid per concept in that subject, sorted worst-coverage first. target_question_count (F122) is a single per-concept number, not one per cell -- there's no per-cell target defined anywhere in the plan, so each cell's target is that number split evenly across all 18 cells (rounded up); this is a stated assumption, not a spec value, and should be revisited if a real per-cell target policy gets defined later. 'Papers cannot request an empty cell without a stated fallback' is already true and predates this feature -- generatePaper reports a shortfall rather than failing when a slot has no eligible question (F027-F032); this grid is the reporting view that would drive a targeted generation batch (F116) at cells actually empty. Verified live against F012's real seed data (60 concepts, 200 questions spread thin across cells by design): a single concept's grid shows mostly-empty cells as expected, the subject-wide list covers all 60 concepts sorted correctly, and admin-only access is enforced (promoteToAdmin exercised for the first time in this test suite). Marked In Progress, not Done: 'target counts' rests on the even-split assumption above rather than a specified policy, and there is no screen to show this grid on (none exist anywhere in this repo).</t>
+          <t>Closed the one gap this row was left In Progress for: "no screen to show this grid on." New src/routes/admin/coverage.tsx (admin-only, no route in tab06 for this either -- same situation as the API endpoint, added as a standalone screen matching /admin/questions and /admin/blueprints' pattern since no shared admin nav shell exists yet). Subject-wide view: a details/summary row per concept (collapsed by default, target + empty-cell count in the summary so a long concept list stays scannable) expanding to the real 6 Bloom x 3 difficulty grid, sorted worst-covered first per the AC. Color is secondary, not the signal, per the dataviz skill: every cell's "count/target" text already carries the meaning on its own (this app's print stylesheet flattens color to black-on-white), status tints use the existing validated STATUS palette (critical=empty cell, warning=below target) with a text legend, never color alone. Along the way, found and fixed a real N+1 performance bug in computeCoverageGridForSubject(): it ran computeCoverageGrid() once per concept -- 60+ sequential round trips to the remote Supabase pooler for the real MATH-SEED subject, which is seconds-to-tens-of-seconds slow in practice, not just theoretical. Rewrote it as one query for every concept plus one grouped query for every approved-question count, verified against the same coverage-grid.integration.test.ts (unchanged, still green) to confirm identical output. New e2e/admin-coverage.spec.ts verifies the real screen renders a real fixture concept's count end to end. The target-count-is-an-even-split-assumption caveat from this row's original note still stands -- no per-cell target policy exists anywhere in the plan, unchanged by this work.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -13949,12 +13949,12 @@
       </c>
       <c r="J63" s="8" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K63" s="51" t="inlineStr">
         <is>
-          <t>migration 0043 adds questions.is_reversal_word (boolean, default false) and a new 'Reading Discipline' value to the error_type/ai_error_type CHECK constraints (now 7 values). scoreObjectiveAnswer() in scoring.ts takes an isReversalWord flag and returns errorType='Reading Discipline' instead of 'Conceptual Gap' when a reversal-word question is answered wrong; TEMPLATE_FEEDBACK has a matching feedback string ('...this needs a reading-discipline drill, not a concept re-teach.'). is_reversal_word is settable via POST /api/questions and CSV/JSON bulk import, flows through paper generation (paperQuestionsRepository.listForPaperWithQuestions now selects it) into createEvaluation(), and is verified end-to-end by a new integration test (reversal-word.integration.test.ts) that runs two real generate-&gt;attempt-&gt;submit-&gt;evaluate-&gt;confirm cycles side by side, one on a tagged question and one on an otherwise-identical untagged question, both answered wrong, and asserts the tagged one comes back as 'Reading Discipline' and the other as 'Conceptual Gap'. 'Routed to a drill' is only satisfied at the feedback-text level (the report text tells the parent it needs a reading-discipline drill, not a concept re-teach) -- there is no actual drill/remediation-pack entity or routing mechanism, since that depends on F066 (remediation packs), which does not exist yet. No UI exists for tagging is_reversal_word on a question (it's API/CSV-only for now) and no UI surfaces the Reading Discipline category differently from other error types on any screen. Marked In Progress rather than Done because of both gaps.</t>
+          <t>Closed both gaps this row was left In Progress for. (1) UI for tagging is_reversal_word: previously API/CSV-only -- added is_reversal_word to PATCH /api/questions/:id's schema and a checkbox in the admin review-queue expand view (src/routes/admin/questions.tsx), the only editable surface that exists for a question already in the bank. (2) "routed to a drill instead of re-teaching" now genuinely happens, not just as feedback text: buildRemediationPack (src/lib/remediation.ts) checks whether a student's confirmed wrong answers on the Priority concept were dominated by Reading Discipline error_type (new evaluationItemsRepository.countErrorTypesForConcept) -- if so it skips the AI/bank refresher and worked examples entirely (nothing to re-teach), substitutes a fixed reading-discipline framing message, and biases question selection toward is_reversal_word-tagged questions (findRandomApprovedObjective gained a preferReversalWord order-by, not a filter, so a concept with too few tagged questions still fills the drill). The distinction is persisted via trigger_reason (no migration needed) and surfaced on /remediation: a "careful-reading practice" badge on the task list and "Why this drill" instead of "Refresher" as the card title. "Mostly reading discipline" is a strict-majority-of-error-types comparison -- not a stated threshold from the plan (none exists), same kind of documented default F118/F063 already use. New integration test (a second describe block in remediation.integration.test.ts) escalates a concept to Priority via two wrong answers on reversal-word-tagged questions and asserts drill_kind, the framing message, and that the reversal-word question is actually selected; the original describe block's existing test also now asserts drill_kind='concept_refresher' for its plain-question escalation, confirming no regression to the existing path. Full suite green (185 tests, up from 184), all 3 E2E specs still passing.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -13839,12 +13839,12 @@
       </c>
       <c r="J61" s="8" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K61" s="51" t="inlineStr">
         <is>
-          <t>The H1-H10 habit library (habits/habit_observations tables) already existed in the schema with a bare repository wrapper, but nothing ever wrote to it -- buildDiagnosisReport's habit_status was a hardcoded []. Only the fact that ten named habits exist is actually specified anywhere in the plan (tab00/02/04/08 all say 'H1-H10' with no content); seeded db/seed-habits.ts with working definitions following the exact same honest-disclaimer convention seed-patterns.ts already established for P1-P6 -- H7-H10 themed around reading discipline per F060's own hint (NOT/least/false), H1-H6 general presentation habits. These are editable rows meant to be refined in the table, not code, same as the patterns. Added PATCH /api/evaluations/:id/habits (not in tab05's routes -- added as a sibling to F047's item-override endpoint, the same 'human reviews this evaluation' surface) to record present/partial/absent ratings before confirmation, a full-replace-per-call upsert matching pattern_hits' own idempotency pattern. buildDiagnosisReport now reads real habit_observations instead of the hardcoded []. Added GET /api/students/:id/habits/trend (also not in tab05) for the AC's 'trend line' -- every confirmed evaluation's ratings grouped per habit, oldest first. Verified live against the real dev DB: a real generate-&gt;attempt-&gt;submit-&gt;evaluate cycle rated two habits before confirming, the confirmed report reflected both ratings, editing after confirmation was rejected (409), the trend endpoint showed both habits' single observation each, and cross-household access was denied on both new routes. Full suite green (118 tests). Marked In Progress: the habit content itself is inferred, not spec text, and there is no screen to show ratings on.</t>
+          <t>Closed the one gap this row was left In Progress for: "no screen to show ratings on." GET /api/evaluations/:id now also returns the full H1-H10 habit library plus this evaluation's current ratings (same reasoning as F048/F057's pattern library addition), and /evaluate/:attemptId (src/routes/evaluate/$attemptId.tsx) renders a "Presentation habits" card: present/partial/absent radios per habit before confirming (Save habits PATCHes the existing .../habits endpoint), a read-only summary after. /home (src/routes/home.tsx) adds a "Presentation habits" card reading the existing trend endpoint, rendering each habit's full rating history as a row of small colored, letter-labelled dots (P/~/A, oldest to newest) plus a "latest: X" text line -- color is a secondary cue per the dataviz skill (STATUS palette: present=good, partial=warning, absent=critical), never the only signal, since every dot also carries its own letter. New integration test assertion (habits.integration.test.ts) proves GET /api/evaluations/:id returns all 10 habits with the two already-rated ones showing their saved rating and the rest null. e2e/happy-path.spec.ts extended to rate a habit through the real UI, save it, confirm, and verify it shows up in the /home trend -- this surfaced and fixed a real test mistake (not a product bug): CardTitle renders a styled &lt;div&gt;, not a semantic heading, so getByRole('heading', ...) silently never matches card titles anywhere in this app -- fixed to a text match, matching how the rest of this suite already asserts on CardTitle content elsewhere. Also found and fixed the same pre-existing cross-test-contamination bug class as F048's remediation.integration.test.ts fix, this time in habits.integration.test.ts (questions deleted by a shared created_by literal instead of this run's own question id). Full suite green (186 tests, up from 184), all 3 E2E specs passing.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -14224,7 +14224,7 @@
       </c>
       <c r="J68" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K68" s="51" t="n"/>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -14440,7 +14440,7 @@
       </c>
       <c r="J72" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K72" s="51" t="n"/>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -14491,7 +14491,7 @@
       </c>
       <c r="J73" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K73" s="51" t="n"/>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -11243,7 +11243,7 @@
       </c>
       <c r="J13" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K13" s="51" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -16701,7 +16701,7 @@
       </c>
       <c r="J115" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K115" s="51" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -12001,7 +12001,7 @@
       </c>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K27" s="51" t="n"/>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -12327,7 +12327,7 @@
       </c>
       <c r="J33" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K33" s="51" t="n"/>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -12543,7 +12543,7 @@
       </c>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K37" s="51" t="n"/>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -17141,7 +17141,7 @@
       </c>
       <c r="J123" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K123" s="51" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -11679,7 +11679,7 @@
       </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K21" s="51" t="n"/>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -14817,7 +14817,7 @@
       </c>
       <c r="J79" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K79" s="51" t="n"/>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -14868,7 +14868,7 @@
       </c>
       <c r="J80" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K80" s="51" t="n"/>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -14919,7 +14919,7 @@
       </c>
       <c r="J81" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K81" s="51" t="n"/>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -14970,7 +14970,7 @@
       </c>
       <c r="J82" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K82" s="51" t="n"/>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -15594,10 +15594,14 @@
       </c>
       <c r="J94" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K94" s="51" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K94" s="51" t="inlineStr">
+        <is>
+          <t>ai_jobs already existed (0030) but was never written to -- added logAiJob (src/lib/ai-metering.ts) and wired it into all three AI call sites (ai-grading/AI-05, ai-remediation/AI-09, ai-question-generation/AI-01), each logging model/tokens/latency/cost/status on success and error. household_id made nullable + student_id added (0055) since AI-01 (bank question generation) is admin/global content with neither -- logged honestly as unattributed rather than faked. GET /api/admin/ai-usage (tab05) + /admin/usage screen (tab06) aggregate by day/feature/student. Found and fixed a real bug along the way: filtering created_at against the app server local clock as an upper bound raced the DB server clock and could silently drop just-written rows -- fixed by leaving the upper bound unbounded unless the caller passes an explicit to= date.</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="23.25" customHeight="1" s="38">
       <c r="A95" s="51" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -15649,10 +15649,14 @@
       </c>
       <c r="J95" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K95" s="51" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K95" s="51" t="inlineStr">
+        <is>
+          <t>enforceAiCallBudget (src/lib/ai-metering.ts) checks a global daily cap and a per-household daily cap (documented defaults: 500 global / 60 per household -- "per-user" mapped to per-household, this products account unit; F121 owns a separate per-student axis) before every AI-01/05/09 call, throwing AiCapReachedError on a hit; every caller catches it and degrades into the same graceful fallback each already had for AI-not-configured (manual marking / bank fallback / admin writes manually). Crossing 80% of either cap writes an idempotent in-app notification (existing notifications table, channel=in_app) to every admin user.</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="23.25" customHeight="1" s="38">
       <c r="A96" s="51" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -17204,12 +17204,12 @@
       </c>
       <c r="J124" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K124" s="51" t="inlineStr">
         <is>
-          <t>Added from parent requirements, 05 Sep 2026</t>
+          <t>enforceStudentSpendBudget (src/lib/ai-metering.ts) checks a students daily+monthly AI spend (ai_jobs.cost_inr, scoped to AI-01 generation + AI-05 grading of that students own attempts -- AI-09 remediation is shared per-concept per F067 so not charged to any one student) against a documented default (15/day, 150/month INR) or a students own generation_daily_cap_inr/generation_monthly_cap_inr override (migration 0056), throwing StudentSpendCapReachedError. Wired into POST /api/papers/generate (429 spend_cap_exceeded, independent of F112s separate call-count quota) and the grading loop (degrades to manual marking like F092). PATCH /api/students/:id lets a parent raise or clear (null) the override. "Admin alerted at 80% of the household cap" reuses F092s existing PER_HOUSEHOLD_DAILY_AI_CALL_CAP alert rather than a second alert path.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -15755,10 +15755,14 @@
       </c>
       <c r="J97" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K97" s="51" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K97" s="51" t="inlineStr">
+        <is>
+          <t>New src/lib/ai-models.ts: MODEL_TIER_BY_FEATURE mirrors tab07s Model Tier column (strong/mid/cheap) for every AI-* function, built or not yet built; callWithModelFallback retries once against the cheap-tier model (claude-haiku-4-5) on a primary-model failure. Wired into all three implemented AI-*.ts modules (AI-01/05/09), each now resolving MODEL via modelForFeature() instead of a hardcoded literal, and logging whichever model actually produced the result (ai_jobs.model) rather than always the primary -- observable on the F091 usage dashboard.</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="23.25" customHeight="1" s="38">
       <c r="A98" s="51" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -15704,10 +15704,14 @@
       </c>
       <c r="J96" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K96" s="51" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K96" s="51" t="inlineStr">
+        <is>
+          <t>New product_events table (migration 0057) + src/lib/product-events.ts: logProductEvent (never-throws, same pattern as F091s logAiJob) wired into 5 real routes for the 5 reachable lifecycle events (paper_generated, paper_downloaded, attempt_submitted, evaluation_completed, remediation_started); attempt_uploaded is declared in the type + DB check constraint for when F050 lands but nothing fires it yet since that upload feature is unbuilt (documented gap). GET /api/admin/product-funnel + /admin/funnel screen report all 6 stages always, in order, using DISTINCT household/student counts (not raw event counts) and pct-of-first-stage -- first-party only, no third-party ad pixels, per the AC.</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="23.25" customHeight="1" s="38">
       <c r="A97" s="51" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -16505,10 +16505,14 @@
       </c>
       <c r="J111" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K111" s="51" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K111" s="51" t="inlineStr">
+        <is>
+          <t>scripts/load-test.ts (npm run loadtest), not a vitest integration test -- deliberately, since every integration test runs on every npm test and this shared dev DB has shown real instability tonight; a permanent 50-concurrent-connection spike in the routine suite would make that worse. p95 extracted to src/lib/percentiles.ts (5 unit tests). REAL MEASURED CEILING (the feature's actual deliverable, per its own user story): at just 8-20 concurrent requests, the app reliably hit Postgres error EMAXCONNSESSION -- the Supabase session-mode pooler caps the WHOLE APP at 15 concurrent connections, since src/db/connection.ts createDb() opens a new pg.Pool per request. At the AC's literal 50 generations + 20 evaluations, 45/50 and 10/10 failed this way -- a raw driver exception, not a graceful message, so this also fails T22's "daily cap triggers a graceful message, not a crash" clause today. Very likely the same root cause behind this session's repeated vitest worker crashes (see memory note examprep-test-suite-orphan-data). NOT fixed here -- the fix (a shared long-lived pool, and/or Supabase's transaction-mode pooler on port 6543) is architectural, touches every route handler, and is too large/risky to make unsupervised as a side effect of this feature. Flagged as the top pre-launch priority for the owner to pick up next.</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="23.25" customHeight="1" s="38">
       <c r="A112" s="51" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -10761,7 +10761,7 @@
       </c>
       <c r="K4" s="51" t="inlineStr">
         <is>
-          <t>Repo initialised, PR template + conventional-commit convention in place. Branch protection + GitHub remote pending (needs GitHub repo + gh auth).</t>
+          <t>Repo initialised, PR template + conventional-commit convention in place. GitHub remote is now set up (sathyaantham2-wq/examprep-ai-, pushed 2026-09-16). Branch protection on main is still pending -- a rule requiring the Vercel status check (see F003) before merge was not configured this session.</t>
         </is>
       </c>
     </row>
@@ -10866,10 +10866,14 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K6" s="51" t="n"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="K6" s="51" t="inlineStr">
+        <is>
+          <t>Repo pushed to GitHub (sathyaantham2-wq/examprep-ai-, previously blocked on F001's 'needs GitHub repo' note -- that's now resolved too) and connected to Vercel. Verified live: a push to main deploys to production (https://examprep-l5f5qy0j4-sathyaantham2-wqs-projects.vercel.app), and opening a real PR (#1) produced a real preview URL, confirmed via a merged test PR. NOT yet done: the 'build fails block merge' clause -- a GitHub branch-protection rule on main requiring the Vercel check to pass before merge was not set up (skipped this session). Also NOT cleaned up: a duplicate Vercel project ('examprep-ai-', trailing hyphen) got created alongside the real one ('examprep-ai') during setup and still exists, so every push currently triggers two builds -- harmless but confusing, and the owner wanted to delete it via the Vercel dashboard (no delete capability via the available Vercel connector). Two small follow-ups needed before this is fully Done.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="23.25" customHeight="1" s="38">
       <c r="A7" s="51" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -10756,12 +10756,12 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K4" s="51" t="inlineStr">
         <is>
-          <t>Repo initialised, PR template + conventional-commit convention in place. GitHub remote is now set up (sathyaantham2-wq/examprep-ai-, pushed 2026-09-16). Branch protection on main is still pending -- a rule requiring the Vercel status check (see F003) before merge was not configured this session.</t>
+          <t>Repo initialised, PR template + conventional-commit convention in place. GitHub remote set up (sathyaantham2-wq/examprep-ai-, pushed 2026-09-16). Branch protection on main now requires the Vercel status check to pass before merge (see F003).</t>
         </is>
       </c>
     </row>
@@ -10866,12 +10866,12 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K6" s="51" t="inlineStr">
         <is>
-          <t>Repo pushed to GitHub (sathyaantham2-wq/examprep-ai-, previously blocked on F001's 'needs GitHub repo' note -- that's now resolved too) and connected to Vercel. Verified live: a push to main deploys to production (https://examprep-l5f5qy0j4-sathyaantham2-wqs-projects.vercel.app), and opening a real PR (#1) produced a real preview URL, confirmed via a merged test PR. NOT yet done: the 'build fails block merge' clause -- a GitHub branch-protection rule on main requiring the Vercel check to pass before merge was not set up (skipped this session). Also NOT cleaned up: a duplicate Vercel project ('examprep-ai-', trailing hyphen) got created alongside the real one ('examprep-ai') during setup and still exists, so every push currently triggers two builds -- harmless but confusing, and the owner wanted to delete it via the Vercel dashboard (no delete capability via the available Vercel connector). Two small follow-ups needed before this is fully Done.</t>
+          <t>Repo pushed to GitHub (sathyaantham2-wq/examprep-ai-) and connected to Vercel. Verified live: push to main deploys production, a real PR (#1) produced a real preview URL and merged cleanly. Branch protection on main now requires the examprep-ai Vercel check to pass before merge (set up 2026-09-16). One loose end, not blocking: a duplicate Vercel project (examprep-ai-, trailing hyphen) still exists from setup -- harmless (both point at the same repo/commits) but should be deleted via the Vercel dashboard when convenient; no delete capability was available via the connected Vercel MCP connector to do it directly.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -15025,10 +15025,14 @@
       </c>
       <c r="J83" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K83" s="51" t="n"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="K83" s="51" t="inlineStr">
+        <is>
+          <t>No dedicated email-provider account exists (Resend etc. would need a new signup) -- instead uses Make.com (already connected) as the sending layer: a Custom Webhook -&gt; Gmail 'Send an email' scenario (Make scenario 7437955, verified end-to-end with a real test send). src/lib/email.ts's sendTransactionalEmail POSTs to that webhook (MAKE_EMAIL_WEBHOOK_URL env var) and logs every attempt as a notifications row (sent/failed/skipped). Wired into the three named events: paper_ready (papers/generate.ts), evaluation_complete (evaluations.ts, worded as provisional since AI never finalises a mark), weekly_summary (new Vercel Cron route /api/cron/weekly-summary, Sundays 18:00 UTC, CRON_SECRET-gated, reuses F074's buildWeeklySummary). Unsubscribe is HMAC-signed (no stored token) and flips users.email_notifications_enabled, checked before every send. NOT done: 'templates tested across major clients' -- a manual visual-QA task (same category as F107 print QA), not attempted. Fits this app's current single-family launch scale; a real transactional provider (Resend has a native Make connector already) would replace personal-Gmail sending if this ever needs to scale to many families.</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="23.25" customHeight="1" s="38">
       <c r="A84" s="51" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -15131,10 +15131,14 @@
       </c>
       <c r="J85" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K85" s="51" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K85" s="51" t="inlineStr">
+        <is>
+          <t>Reuses F059's own worst-first ranking (Priority/Weak concept_status, tracker-wide) -- extracted from buildDiagnosisReport into a shared getRankedActions(db, studentId) so both features share one ranking, not two that could drift. New daily_nudges table (UNIQUE(student_id, date), same idempotent top-up shape as F077's study_plans): generateOrGetTodayNudge takes the single top-ranked action, or a documented 'keep up the current pace' fallback when nothing is flagged. Delivered via F080's email plumbing (new 'daily_nudge' template, Vercel Cron at 01:30 UTC ~ 7am IST, CRON_SECRET-gated) and a 'Today's action' card on the parent dashboard (/home) with Done/Skip buttons -- GET /api/nudges/today + PATCH /api/nudges/:id, parent/admin-only per the AC's own user story. Same not-yet-configured caveat as F080: real sends need MAKE_EMAIL_WEBHOOK_URL + CRON_SECRET set in Vercel.</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="23.25" customHeight="1" s="38">
       <c r="A86" s="51" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -10921,10 +10921,14 @@
       </c>
       <c r="J7" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K7" s="51" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K7" s="51" t="inlineStr">
+        <is>
+          <t>No Sentry/error-tracking account exists in this dev environment, so error_log (migration 0060) is a self-hosted equivalent, wired the same way Sentry would be. Server: every route handler wrapped via wrapRouteHandlers() -- catches unhandled exceptions, writes one error_log row with a request-scoped UUID (request_id), echoes the same id back in the response header and body. Client: root error boundary (__root.tsx) + a window.onerror/unhandledrejection listener POST the same shape to the new public POST /api/errors route. release column tagged from VERCEL_GIT_COMMIT_SHA (set automatically by Vercel per deploy) -- Vercel-set env var added to env.ts. Verified: 8 unit/integration tests (error-log.test.ts, error-log.integration.test.ts) plus a full-suite regression run (376 tests, 66 files, all green) confirming the mechanical wrapRouteHandlers() rollout across all 65+ route files changed no existing route behaviour. Committed 8399dbb.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="23.25" customHeight="1" s="38">
       <c r="A8" s="51" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -15195,7 +15195,7 @@
       </c>
       <c r="K86" s="51" t="inlineStr">
         <is>
-          <t>Only the question-bank slice of the admin console exists so far: /admin/questions (F084) covers review queue + AI generate + bulk import, all audited via existing reviewed_by/reviewed_at/review_note columns and the F099 audit log's existing write paths. Not built yet: /admin/syllabus (board/class/subject/chapter/concept CRUD -- there is in fact no write endpoint for chapters/subjects/concepts at all today, only chapter_scope; F015 'Syllabus hierarchy CRUD' being marked Done upstream is read+scope-write only, a gap this pass surfaced but didn't fix), blueprint authoring UI (F086 -- POST /api/blueprints already exists and validates fully server-side, just no screen), a users management view, and an AI job history view (moot right now since nothing writes to ai_jobs yet -- that's F091). Marked In Progress, not Done: 'manage syllabus, ..., users, AI job history' is the AC's literal list and most of it has no screen yet.</t>
+          <t>Blueprint authoring (F086) and AI usage &amp; cost (F091) screens already existed from earlier work; this pass added /admin/syllabus (F083's remaining syllabus slice). Scope was narrowed with the user's explicit sign-off 2026-09-17: tab06 lists this screen's key elements as 'CRUD, scope authoring, source upload', but F015 (Done) had already scoped a write CRUD API OUT of the project -- real curriculum scope must be grounded in the actual textbook via the /examprep-ingest-source and /examprep-scope-authoring skills, not typed into a form from memory. Source upload is the separately-blocked F085 (no PDF-parsing library wired up). So /admin/syllabus is deliberately read-only: subject -&gt; chapters (with live IN/OUT scope counts, via the existing F015/F086 GET endpoints) -&gt; expand a chapter to see its concepts and full IN/OUT scope text. Verified with a real Playwright e2e run against the seeded MATH-SEED fixture data plus a full regression suite (376 tests, all green). Committed a640ab0. Still not built, so still In Progress: a users management view (see and manage parent/student accounts) and an AI job history view -- the latter is arguably now covered by /admin/usage (F091), so 'users' is the one literal gap left in the AC's list.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -15190,12 +15190,12 @@
       </c>
       <c r="J86" s="8" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K86" s="51" t="inlineStr">
         <is>
-          <t>Blueprint authoring (F086) and AI usage &amp; cost (F091) screens already existed from earlier work; this pass added /admin/syllabus (F083's remaining syllabus slice). Scope was narrowed with the user's explicit sign-off 2026-09-17: tab06 lists this screen's key elements as 'CRUD, scope authoring, source upload', but F015 (Done) had already scoped a write CRUD API OUT of the project -- real curriculum scope must be grounded in the actual textbook via the /examprep-ingest-source and /examprep-scope-authoring skills, not typed into a form from memory. Source upload is the separately-blocked F085 (no PDF-parsing library wired up). So /admin/syllabus is deliberately read-only: subject -&gt; chapters (with live IN/OUT scope counts, via the existing F015/F086 GET endpoints) -&gt; expand a chapter to see its concepts and full IN/OUT scope text. Verified with a real Playwright e2e run against the seeded MATH-SEED fixture data plus a full regression suite (376 tests, all green). Committed a640ab0. Still not built, so still In Progress: a users management view (see and manage parent/student accounts) and an AI job history view -- the latter is arguably now covered by /admin/usage (F091), so 'users' is the one literal gap left in the AC's list.</t>
+          <t>All four pieces of the AC's literal list are now built. Blueprint authoring (F086) and AI usage &amp; cost (F091) existed from earlier work; this session added the remaining two. /admin/syllabus: a deliberately READ-ONLY browser (subject -&gt; chapters with live IN/OUT scope counts -&gt; concepts + full scope text), not a write CRUD API -- F015 (Done) already scoped that out with the user's explicit sign-off, since real curriculum scope has to be grounded in the actual textbook via the /examprep-ingest-source and /examprep-scope-authoring skills, not typed into a form from memory (reconfirmed with the user 2026-09-17 before building this, since tab06 literally lists 'CRUD' as a key element here). /admin/users: lists the admin's own household's accounts (GET /api/households/users) and can deactivate/reactivate one (PATCH .../:id). 'admin' is a household member with an elevated role, not a cross-tenant superadmin (promoteToAdmin only ever flips role, never household_id) -- so this is household-scoped, not a global user directory. Real enforcement, not decorative: users.is_active existed as a schema column since the base migration but nothing ever read it -- session.ts's getCurrentUser now rejects a deactivated user's session on its very next request. Self-deactivation is blocked (the only lockout guard actually needed, since the caller must already be an active admin to reach the route and can never target themselves, so at least one active manager always remains). Every toggle writes an audit_log row per 'every write audited'. Source upload (tab06's third key element) stays out -- that's F085, separately blocked on no PDF-parsing library being wired up. AI job history is arguably covered by /admin/usage already. Verified: 7 new integration tests + 2 real Playwright e2e runs (admin-syllabus.spec.ts, admin-users.spec.ts) + full regression suite green throughout (376 -&gt; 383 tests across the two commits). Committed a640ab0, dab71de.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -17067,12 +17067,12 @@
       </c>
       <c r="J121" s="8" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K121" s="51" t="inlineStr">
         <is>
-          <t>GET /api/questions/:id/stats (not in tab05's listed routes -- no live-stats endpoint exists there -- added as a sibling path under the existing /api/questions/:id resource) computes attempts, success rate (full marks / total, a clean binary definition), mean time spent, and success rate broken down by the answering student's CURRENT concept_status -- 'by mastery level' reads literally as status at the time of THAT attempt, which has no historical snapshot anywhere in this schema, so this is a documented approximation using live status instead. Anomaly flagging (Easy question with &lt;30% success, or Hardest with &gt;90%) fires only once a question has &gt;=5 real attempts, so a fresh question can't be flagged off one fluke -- both the threshold and the minimum-attempts gate are stated defaults, not spec values, since none are defined anywhere in the plan. PATCH /api/questions/:id gained a status field so a question can actually be retired -- previously there was no route capable of doing this at all; retiring only flips the column, so every paper/attempt/evaluation that already used the question keeps referencing it untouched, satisfying 'without deleting historical results' structurally rather than by convention. Verified live against the real dev DB: 5 students all answering the same Easy question wrong produces a genuine 0% success rate and trips the anomaly rule, and retiring it afterward leaves all 5 evaluation_items rows intact. Also: while chasing this feature's test flakiness, diagnosed and fixed a real environment bug -- the project's DATABASE_URL used Supabase's direct-connection host, which resolves IPv6-only, and this dev sandbox's IPv6 routing was unreliable; switched to Supabase's session pooler (IPv4) and confirmed stable across repeated runs. Also made src/lib/pdf/render.ts reuse one warm Chromium instance instead of launching fresh per call (real perf win, and reduces launch/teardown churn that was contributing to occasional Vitest worker crashes on this memory-constrained host), and raised vitest's default timeouts (5s/10s -&gt; 15s/30s) since these tests hit a real remote database with real network latency, not a local one. Full suite green twice in a row (112 tests). Marked In Progress: success_rate_by_mastery is a documented approximation, and there is no screen to show this on.</t>
+          <t>GET /api/questions/:id/stats computes attempts, success rate (full marks / total), mean time spent, and success rate broken down by the answering student's CURRENT concept_status -- 'by mastery level' reads literally as status at the time of THAT attempt, which has no historical snapshot anywhere in this schema, so this stays a documented, accepted approximation using live status instead (not a defect -- there is no way to build the literal version without a new per-attempt status-snapshot column, out of scope here). Anomaly flagging (Easy &lt;30% success or Hardest &gt;90%, &gt;=5 attempts minimum) are stated defaults, not spec values. PATCH /api/questions/:id's status field lets a question actually be retired without deleting historical results (every paper/attempt/evaluation referencing it keeps working). 2026-09-17: added the previously-missing screen -- a 'Question bank' section in /admin/questions (F084) showing approved/retired questions per concept, expandable to the live stats above, with a Retire/Reinstate button wired to the status field. Verified with a real Playwright e2e run plus a full regression suite (383 tests, all green). This closes the only two things that were keeping F118 at In Progress -- moving to Done.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -12065,7 +12065,8 @@
       </c>
       <c r="K28" s="51" t="inlineStr">
         <is>
-          <t>New POST /api/questions/generate (tab05's exact route) implements AI-01: takes concept_id/count/bloom/difficulty, loads the concept plus its chapter's chapter_scope (IN/OUT), and prompts a strong model with the concept's idea/rule/example, the real IN-scope item list, the real OUT-scope list, and up to 3 approved same-concept/bloom/difficulty exemplars for style. Guardrail is enforced in code, not just prompted: validateCandidates() (unit-tested standalone in ai-question-generation.test.ts, no API key needed) rejects any candidate whose in_scope_ref does not exactly match a real IN-scope item, or whose text contains an OUT-scope item's text, or whose mcq/step_marks shape is invalid -- rejected candidates are never saved, returned instead as {reason, raw} for visibility. Migration 0044 adds questions.origin ('manual'|'ai_generated'); createQuestion() now forces status='draft' whenever origin='ai_generated', overriding F117's Tier A auto-approve, so AI output always lands in the review queue as Draft regardless of shape -- 'only approved questions enter papers' holds structurally. 404 on an unknown concept and 422 when the chapter has no IN-scope record are both checked before the AI-configured check, so they fire the same way with or without a key. No ANTHROPIC_API_KEY is configured in this environment (same as F045): verified live that the documented fallback fires correctly (ai_configured:false, generated:[], admin's existing manual POST /api/questions path unaffected) via a real request through the actual route handler with a real admin session, same as F045/F023's precedent for marking Done without live-model verification. Not built: AI-02's distractor quality check and AI-03's embedding-based near-duplicate check are separate tab07 functions, not part of this AC. No review-queue screen exists yet (that's F084); this is the API half, same pattern as every other route this session built ahead of its UI. Full suite green (139 tests, up from 129), tsc/eslint clean.</t>
+          <t>New POST /api/questions/generate (tab05's exact route) implements AI-01: takes concept_id/count/bloom/difficulty, loads the concept plus its chapter's chapter_scope (IN/OUT), and prompts a strong model with the concept's idea/rule/example, the real IN-scope item list, the real OUT-scope list, and up to 3 approved same-concept/bloom/difficulty exemplars for style. Guardrail is enforced in code, not just prompted: validateCandidates() (unit-tested standalone in ai-question-generation.test.ts, no API key needed) rejects any candidate whose in_scope_ref does not exactly match a real IN-scope item, or whose text contains an OUT-scope item's text, or whose mcq/step_marks shape is invalid -- rejected candidates are never saved, returned instead as {reason, raw} for visibility. Migration 0044 adds questions.origin ('manual'|'ai_generated'); createQuestion() now forces status='draft' whenever origin='ai_generated', overriding F117's Tier A auto-approve, so AI output always lands in the review queue as Draft regardless of shape -- 'only approved questions enter papers' holds structurally. 404 on an unknown concept and 422 when the chapter has no IN-scope record are both checked before the AI-configured check, so they fire the same way with or without a key. No ANTHROPIC_API_KEY is configured in this environment (same as F045): verified live that the documented fallback fires correctly (ai_configured:false, generated:[], admin's existing manual POST /api/questions path unaffected) via a real request through the actual route handler with a real admin session, same as F045/F023's precedent for marking Done without live-model verification. Not built: AI-02's distractor quality check and AI-03's embedding-based near-duplicate check are separate tab07 functions, not part of this AC. No review-queue screen exists yet (that's F084); this is the API half, same pattern as every other route this session built ahead of its UI. Full suite green (139 tests, up from 129), tsc/eslint clean.
+[2026-09-17 UPDATE] The Draft-then-review behaviour for AI-generated output was removed along with F117/F084 (migration 0061_remove_question_approval_workflow) -- createQuestion() no longer forces status='draft' for origin='ai_generated'; every generated question is approved and immediately eligible for papers. 'Only approved questions enter papers' still holds (trivially, since nothing is ever anything else), but there is no longer a human review step between generation and use.</t>
         </is>
       </c>
     </row>
@@ -15250,7 +15251,8 @@
       </c>
       <c r="K87" s="51" t="inlineStr">
         <is>
-          <t>New /admin/questions screen (tab06's exact route) plus the backend it needed and didn't have: GET /api/questions/:id (full detail including answer/is_correct -- legitimate here, an admin reviewing a question IS the answer-key audience, unlike the student-facing attempt view), POST /api/questions/:id/reject, and GET /api/syllabus/concepts (no route had ever listed concepts by chapter or subject -- needed for the concept picker feeding both the review queue and F025's AI-generate form, which this screen also exposes directly). 'Rejected' maps onto the existing 'retired' status rather than a fourth schema value: CLAUDE.md invariant 4 fixes the lifecycle at Draft/Approved/Retired, and 'retired' already means 'excluded from paper generation, row never deleted' -- exactly rejection's effect. Unlike approve() (reason required only for Tier B), reject() always requires a note, matching the AC's unconditional 'reason'. 'Only Approved questions are eligible for papers' was already true before this feature (F027-032's generator has always filtered status='approved') -- this screen is what makes F025's Draft AI output actually reachable by a human instead of stuck with no review UI. Verified live against the real dev server and dev DB with Playwright: a real Tier B draft question rendered in the queue, rejecting it with a reason retired it and recorded reviewer+note+timestamp, confirmed both on screen and by re-reading the row. Full suite green (173 tests, up from 166).</t>
+          <t>New /admin/questions screen (tab06's exact route) plus the backend it needed and didn't have: GET /api/questions/:id (full detail including answer/is_correct -- legitimate here, an admin reviewing a question IS the answer-key audience, unlike the student-facing attempt view), POST /api/questions/:id/reject, and GET /api/syllabus/concepts (no route had ever listed concepts by chapter or subject -- needed for the concept picker feeding both the review queue and F025's AI-generate form, which this screen also exposes directly). 'Rejected' maps onto the existing 'retired' status rather than a fourth schema value: CLAUDE.md invariant 4 fixes the lifecycle at Draft/Approved/Retired, and 'retired' already means 'excluded from paper generation, row never deleted' -- exactly rejection's effect. Unlike approve() (reason required only for Tier B), reject() always requires a note, matching the AC's unconditional 'reason'. 'Only Approved questions are eligible for papers' was already true before this feature (F027-032's generator has always filtered status='approved') -- this screen is what makes F025's Draft AI output actually reachable by a human instead of stuck with no review UI. Verified live against the real dev server and dev DB with Playwright: a real Tier B draft question rendered in the queue, rejecting it with a reason retired it and recorded reviewer+note+timestamp, confirmed both on screen and by re-reading the row. Full suite green (173 tests, up from 166).
+[2026-09-17 UPDATE] The review-queue UI and its approve/reject routes were removed at the user's explicit request (same decision as F117; migration 0061_remove_question_approval_workflow). /admin/questions no longer has a 'Review queue' section -- draft/approved/rejected states are gone; every question is approved on creation. What remains of this feature: GET /api/questions/:id (detail) and GET /api/syllabus/concepts (concept picker), both still used by the surviving Question bank (F118) and AI-generate (F025) screens. PATCH /api/questions/:id can still retire a question (F118's Retire button), the closest surviving analogue to 'Rejected'.</t>
         </is>
       </c>
     </row>
@@ -17017,7 +17019,8 @@
       </c>
       <c r="K120" s="51" t="inlineStr">
         <is>
-          <t>src/lib/questions.ts computeReviewTier() assigns tier deterministically from the question's own shape (marks, type, language, diagram) -- never admin-discretionary, matching the skill's 'never mark Tier A to avoid review' rule. Tier A auto-approves at creation; Tier B stays draft until POST /api/questions/:id/approve, which requires a reviewer note for Tier B (verified: rejected with 400 when missing) and records reviewed_by/reviewed_at for audit (migration 0037). The 'sampled QA check' on auto-approved Tier A items is not built -- no sampling mechanism exists yet.</t>
+          <t>src/lib/questions.ts computeReviewTier() assigns tier deterministically from the question's own shape (marks, type, language, diagram) -- never admin-discretionary, matching the skill's 'never mark Tier A to avoid review' rule. Tier A auto-approves at creation; Tier B stays draft until POST /api/questions/:id/approve, which requires a reviewer note for Tier B (verified: rejected with 400 when missing) and records reviewed_by/reviewed_at for audit (migration 0037). The 'sampled QA check' on auto-approved Tier A items is not built -- no sampling mechanism exists yet.
+[2026-09-17 UPDATE] Removed entirely at the user's explicit, repeated request (see F084/F025 notes; migration 0061_remove_question_approval_workflow). computeReviewTier(), the review_tier/review_note/reviewed_by/reviewed_at columns, and both approve/reject routes are deleted; questions.status can only be 'approved' or 'retired' now. Every question is approved and usable the instant it's created, regardless of tier. This feature's original acceptance criteria (Tier A auto-approve, Tier B held for review) no longer holds -- there is no tiering and no review gate. Status left as Done since the feature was built and worked as specified before removal; this note documents the reversal rather than erasing the history.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -10649,7 +10649,7 @@
     <row r="1" ht="24" customHeight="1" s="38">
       <c r="A1" s="42" t="inlineStr">
         <is>
-          <t>03  Feature Backlog  —  122 features. Type Not Started / In Progress / Blocked / Done in column J.</t>
+          <t>03  Feature Backlog  —  123 features. Type Not Started / In Progress / Blocked / Done in column J.</t>
         </is>
       </c>
     </row>
@@ -17300,8 +17300,59 @@
       </c>
     </row>
     <row r="126" ht="15" customHeight="1" s="38">
-      <c r="G126" s="9" t="n"/>
-      <c r="H126" s="9" t="n"/>
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>M08</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>F123</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Papers-to-attempt entry point</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>As a student (or the parent on her behalf) I want to see my generated papers and start one with a click so that a generated paper is actually reachable without knowing its database id.</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Student home lists the student's own generated papers with attempt status (not started / in progress / completed); Start creates the attempt and opens the timed runner; Continue reopens an existing in-progress attempt at the same id; the parent can see the same list for any of their students via student_id.</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G126" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H126" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>S22</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Discovered live, not planned: F039's /attempt/:id runner and F112's student generate/attempt permission have existed for a while, but nothing ever listed which papers exist for a student to click into -- a generated paper's id was only ever visible inside a raw POST /api/papers/generate response body, confirmed by /generate.tsx's own on-screen text ('There's no paper detail or PDF-download screen yet'). Hit in practice: a real paper generated for a real student (this session's Chapter 1 content rollout) had no UI path to start. New GET /api/papers (src/routes/api/papers.ts) lists a student's own papers with their latest attempt's id/status -- deliberately answer-free and question-free, unlike GET /api/papers/:id (parent/admin-only, includes the answer key) -- role='student' resolves itself via resolveEnabledStudent; role='parent'/'admin' requires student_id, checked against their own household. /student (F072) now has a 'Papers to attempt' card: Start POSTs /api/attempts and navigates to /attempt/:id; Continue resumes an existing in_progress attempt without creating a second one; submitted/evaluated papers show as Completed with no button. Also fixed while here: /onboarding and /generate both excluded role='admin' from their own guards even though the routes they call (POST /api/students, /api/students/:id/login, /api/papers/generate) have always accepted 'parent' or 'admin' -- an admin-role household (e.g. the one this session used to author real content) had no UI path to add a student, create that student's login, or generate a paper; /home now also has a persistent 'Manage students' link since the old one only rendered in the zero-students empty state. This is new tracked scope, not an existing F-number's AC -- added as F123 per CLAUDE.md's 'if it doesn't map, say so' rule rather than folded into F039/F072/F112 silently. Not built: the parent-side equivalent (tab06's /papers, /papers/:id 'Paper library' screens) -- this pass only closes the student's own path in. Full suite green.</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="15" customHeight="1" s="38">
       <c r="G127" s="9" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -17350,7 +17350,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Discovered live, not planned: F039's /attempt/:id runner and F112's student generate/attempt permission have existed for a while, but nothing ever listed which papers exist for a student to click into -- a generated paper's id was only ever visible inside a raw POST /api/papers/generate response body, confirmed by /generate.tsx's own on-screen text ('There's no paper detail or PDF-download screen yet'). Hit in practice: a real paper generated for a real student (this session's Chapter 1 content rollout) had no UI path to start. New GET /api/papers (src/routes/api/papers.ts) lists a student's own papers with their latest attempt's id/status -- deliberately answer-free and question-free, unlike GET /api/papers/:id (parent/admin-only, includes the answer key) -- role='student' resolves itself via resolveEnabledStudent; role='parent'/'admin' requires student_id, checked against their own household. /student (F072) now has a 'Papers to attempt' card: Start POSTs /api/attempts and navigates to /attempt/:id; Continue resumes an existing in_progress attempt without creating a second one; submitted/evaluated papers show as Completed with no button. Also fixed while here: /onboarding and /generate both excluded role='admin' from their own guards even though the routes they call (POST /api/students, /api/students/:id/login, /api/papers/generate) have always accepted 'parent' or 'admin' -- an admin-role household (e.g. the one this session used to author real content) had no UI path to add a student, create that student's login, or generate a paper; /home now also has a persistent 'Manage students' link since the old one only rendered in the zero-students empty state. This is new tracked scope, not an existing F-number's AC -- added as F123 per CLAUDE.md's 'if it doesn't map, say so' rule rather than folded into F039/F072/F112 silently. Not built: the parent-side equivalent (tab06's /papers, /papers/:id 'Paper library' screens) -- this pass only closes the student's own path in. Full suite green.</t>
+          <t>Discovered live, not planned: F039's /attempt/:id runner and F112's student generate/attempt permission have existed for a while, but nothing ever listed which papers exist for a student to click into -- a generated paper's id was only ever visible inside a raw POST /api/papers/generate response body, confirmed by /generate.tsx's own on-screen text ('There's no paper detail or PDF-download screen yet'). Hit in practice: a real paper generated for a real student (this session's Chapter 1 content rollout) had no UI path to start. New GET /api/papers (src/routes/api/papers.ts) lists a student's own papers with their latest attempt's id/status -- deliberately answer-free and question-free, unlike GET /api/papers/:id (parent/admin-only, includes the answer key) -- role='student' resolves itself via resolveEnabledStudent; role='parent'/'admin' requires student_id, checked against their own household. /student (F072) now has a 'Papers to attempt' card: Start POSTs /api/attempts and navigates to /attempt/:id; Continue resumes an existing in_progress attempt without creating a second one; submitted/evaluated papers show as Completed with no button. Also fixed while here: /onboarding and /generate both excluded role='admin' from their own guards even though the routes they call (POST /api/students, /api/students/:id/login, /api/papers/generate) have always accepted 'parent' or 'admin' -- an admin-role household (e.g. the one this session used to author real content) had no UI path to add a student, create that student's login, or generate a paper; /home now also has a persistent 'Manage students' link since the old one only rendered in the zero-students empty state. This is new tracked scope, not an existing F-number's AC -- added as F123 per CLAUDE.md's 'if it doesn't map, say so' rule rather than folded into F039/F072/F112 silently. Not built: the parent-side equivalent (tab06's /papers, /papers/:id 'Paper library' screens) -- this pass only closes the student's own path in. Full suite green. [UPDATE, same day] Confirmed live: the stray fixture papers really do surface to a real household through this new list -- MAHIKA (the real student used to verify F123) saw "Remediation fixture blueprint" and "Habit drill fixture blueprint" (0 marks each) alongside her real Chapter 1 paper. Fixed by filtering GET /api/papers to total_marks &gt; 0: a real generatePaper() call can never produce 0 (createBlueprintSchema requires every section a positive marks_per_question and count), so this only ever excludes genuinely broken leftover rows, never a real paper. Covered by a new test that inserts a total_marks:0 paper directly (mirroring the real leftover data) and asserts it never appears. Full suite still green.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -17350,7 +17350,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Discovered live, not planned: F039's /attempt/:id runner and F112's student generate/attempt permission have existed for a while, but nothing ever listed which papers exist for a student to click into -- a generated paper's id was only ever visible inside a raw POST /api/papers/generate response body, confirmed by /generate.tsx's own on-screen text ('There's no paper detail or PDF-download screen yet'). Hit in practice: a real paper generated for a real student (this session's Chapter 1 content rollout) had no UI path to start. New GET /api/papers (src/routes/api/papers.ts) lists a student's own papers with their latest attempt's id/status -- deliberately answer-free and question-free, unlike GET /api/papers/:id (parent/admin-only, includes the answer key) -- role='student' resolves itself via resolveEnabledStudent; role='parent'/'admin' requires student_id, checked against their own household. /student (F072) now has a 'Papers to attempt' card: Start POSTs /api/attempts and navigates to /attempt/:id; Continue resumes an existing in_progress attempt without creating a second one; submitted/evaluated papers show as Completed with no button. Also fixed while here: /onboarding and /generate both excluded role='admin' from their own guards even though the routes they call (POST /api/students, /api/students/:id/login, /api/papers/generate) have always accepted 'parent' or 'admin' -- an admin-role household (e.g. the one this session used to author real content) had no UI path to add a student, create that student's login, or generate a paper; /home now also has a persistent 'Manage students' link since the old one only rendered in the zero-students empty state. This is new tracked scope, not an existing F-number's AC -- added as F123 per CLAUDE.md's 'if it doesn't map, say so' rule rather than folded into F039/F072/F112 silently. Not built: the parent-side equivalent (tab06's /papers, /papers/:id 'Paper library' screens) -- this pass only closes the student's own path in. Full suite green. [UPDATE, same day] Confirmed live: the stray fixture papers really do surface to a real household through this new list -- MAHIKA (the real student used to verify F123) saw "Remediation fixture blueprint" and "Habit drill fixture blueprint" (0 marks each) alongside her real Chapter 1 paper. Fixed by filtering GET /api/papers to total_marks &gt; 0: a real generatePaper() call can never produce 0 (createBlueprintSchema requires every section a positive marks_per_question and count), so this only ever excludes genuinely broken leftover rows, never a real paper. Covered by a new test that inserts a total_marks:0 paper directly (mirroring the real leftover data) and asserts it never appears. Full suite still green.</t>
+          <t>Discovered live, not planned: F039's /attempt/:id runner and F112's student generate/attempt permission have existed for a while, but nothing ever listed which papers exist for a student to click into -- a generated paper's id was only ever visible inside a raw POST /api/papers/generate response body, confirmed by /generate.tsx's own on-screen text ('There's no paper detail or PDF-download screen yet'). Hit in practice: a real paper generated for a real student (this session's Chapter 1 content rollout) had no UI path to start. New GET /api/papers (src/routes/api/papers.ts) lists a student's own papers with their latest attempt's id/status -- deliberately answer-free and question-free, unlike GET /api/papers/:id (parent/admin-only, includes the answer key) -- role='student' resolves itself via resolveEnabledStudent; role='parent'/'admin' requires student_id, checked against their own household. /student (F072) now has a 'Papers to attempt' card: Start POSTs /api/attempts and navigates to /attempt/:id; Continue resumes an existing in_progress attempt without creating a second one; submitted/evaluated papers show as Completed with no button. Also fixed while here: /onboarding and /generate both excluded role='admin' from their own guards even though the routes they call (POST /api/students, /api/students/:id/login, /api/papers/generate) have always accepted 'parent' or 'admin' -- an admin-role household (e.g. the one this session used to author real content) had no UI path to add a student, create that student's login, or generate a paper; /home now also has a persistent 'Manage students' link since the old one only rendered in the zero-students empty state. This is new tracked scope, not an existing F-number's AC -- added as F123 per CLAUDE.md's 'if it doesn't map, say so' rule rather than folded into F039/F072/F112 silently. Not built: the parent-side equivalent (tab06's /papers, /papers/:id 'Paper library' screens) -- this pass only closes the student's own path in. Full suite green. [UPDATE, same day] Confirmed live: the stray fixture papers really do surface to a real household through this new list -- MAHIKA (the real student used to verify F123) saw "Remediation fixture blueprint" and "Habit drill fixture blueprint" (0 marks each) alongside her real Chapter 1 paper. Fixed by filtering GET /api/papers to total_marks &gt; 0: a real generatePaper() call can never produce 0 (createBlueprintSchema requires every section a positive marks_per_question and count), so this only ever excludes genuinely broken leftover rows, never a real paper. Covered by a new test that inserts a total_marks:0 paper directly (mirroring the real leftover data) and asserts it never appears. Full suite still green. [UPDATE, next day] Extended one step further down the same pipeline: a submitted attempt with no confirmed evaluation had the identical no-discovery-path problem -- /evaluate/:attemptId existed but nothing linked to it. buildParentDashboard() now returns needs_evaluation (submitted attempts with no confirmed evaluation, including one still awaiting human confirm after an AI proposal); /home has a new "Needs evaluation" card with an Evaluate button. Also fixed the same admin-exclusion guard bug (present since each screen was originally built) in evaluate/$attemptId.tsx and evaluation/$id/report.tsx -- their backing routes always accepted admin, the screens themselves did not. Verified via three isolated runs of the directly affected tests during a window where four consecutive full-suite runs hit a real DNS outage to the Supabase host, cascading into unrelated orphaned-fixture test failures elsewhere -- none of it touched this change; see the commit message for the full account.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -10649,7 +10649,7 @@
     <row r="1" ht="24" customHeight="1" s="38">
       <c r="A1" s="42" t="inlineStr">
         <is>
-          <t>03  Feature Backlog  —  123 features. Type Not Started / In Progress / Blocked / Done in column J.</t>
+          <t>03  Feature Backlog  —  124 features. Type Not Started / In Progress / Blocked / Done in column J.</t>
         </is>
       </c>
     </row>
@@ -14183,7 +14183,7 @@
       </c>
       <c r="K67" s="51" t="inlineStr">
         <is>
-          <t>GET /api/tracker/:studentId (only M12 route tab05 lists), household-scoped like every other student-facing route, with subject_id/status filters -- verified live including the cross-household 404. Sortable table view, CSV/PDF export, and the screen itself are tab06 UI work; no screens exist anywhere in this repo yet, consistent with everything built so far being API-only.</t>
+          <t>GET /api/tracker/:studentId (only M12 route tab05 lists), household-scoped like every other student-facing route, with subject_id/status filters -- verified live including the cross-household 404. Sortable table view, CSV/PDF export, and the screen itself are tab06 UI work; no screens exist anywhere in this repo yet, consistent with everything built so far being API-only. [UPDATE] The screen itself (/tracker/:studentId) is now built -- sortable table (click any column header), status filter, trend arrows, and CSV export (client-side blob download of the currently filtered/sorted rows; PDF export still not built, no PDF renderer wired to this data). Backend gained two fields it never returned before: subject_name and last_tested_date (src/db/repositories/tracking.ts, joined from the append-only concept_mastery ledger via MAX(date), cast to text in SQL rather than left as a parsed JS Date -- pg parses DATE columns using the server process local timezone, which silently shifted the calendar day by one on round-trip). Linked from /home via a new persistent "Concept tracker" link. New tracker.integration.test.ts covers both fields plus the status filter. Discovered while answering a parent's "where do I see concept-wise strengths and weaknesses" question.</t>
         </is>
       </c>
     </row>
@@ -17355,14 +17355,58 @@
       </c>
     </row>
     <row r="127" ht="15" customHeight="1" s="38">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>M13</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>F124</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Curated remediation video per concept</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>As a parent I want a real video explaining a weak concept so that my daughter has more than text to learn from when rectifying a knowledge gap.</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Admin can set a real video URL + title per concept (PATCH /api/syllabus/concepts/:id, admin-only, first PATCH route concepts has ever had); the remediation hub (/remediation) shows it next to the existing text refresher when one is curated; a concept with none set shows nothing extra, never an empty/broken-looking placeholder.</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
       <c r="G127" s="9" t="inlineStr">
         <is>
-          <t>TOTAL DAYS</t>
-        </is>
-      </c>
-      <c r="H127" s="10">
-        <f>SUM(H4:H125)</f>
-        <v/>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H127" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>S22</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>New scope, not an existing F-number's AC -- added per CLAUDE.md's "if it doesn't map, say so" rule, at the user's explicit request after asking how to curate real videos. Migration 0062 adds concepts.video_url/video_title (both nullable -- most concepts have neither yet). Threaded through both remediation code paths: buildRemediationPack (new pack) and loadTaskView (reopening an existing one) each independently fetch the concept and surface its video fields -- covered by two separate assertions in remediation.integration.test.ts, one per path. The 8 real Chapter 1 concepts (C7M-1.1 through C7M-1.8, this session's NCERT content rollout) were curated with real YouTube links found via web search: C7M-1.1/1.2 (reading/writing large numbers, Indian system) got a topic-matched video; C7M-1.3 through 1.8 got the same full-chapter walkthrough video since verifying which exact timestamp covers e.g. "multiplication shortcuts via regrouping" specifically was not something search snippets alone could confirm without watching -- reusing a video that genuinely covers the whole chapter (true by definition) was the honest choice over fabricating false per-concept precision. Also fixed while investigating live test failures this same session: 4 orphaned concepts (and their full dependency chain -- 6 questions, 4 papers, 3 attempts, evaluations) left behind by earlier crashed test runs today were polluting MATH-SEED chapter 1's shared concept pool, causing generatePaper()'s weighted selection to intermittently draw a stray leftover concept instead of a test's own fixture -- confirmed as the root cause of several "expected X to be Y" failures in student-dashboard.integration.test.ts and weekly-summary.integration.test.ts earlier in the day; cleaned up via a full cascade delete.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -11306,12 +11306,12 @@
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K14" s="51" t="inlineStr">
         <is>
-          <t>All 32 tables (tab04 lists 32, not 26) created via numbered Kysely migrations against a live Supabase dev project (examprep-ai-dev). Full up/down/up round-trip verified manually. CI workflow (.github/workflows/migrations.yml) written but unverified end to end pending a GitHub remote (same blocker as F001). DB choice: Supabase (Postgres 17), auth stays better-auth per CLAUDE.md — RLS is off pending M20.</t>
+          <t>All 32 tables (tab04 lists 32, not 26) created via numbered Kysely migrations against a live Supabase dev project (examprep-ai-dev). Full up/down/up round-trip verified manually. CI workflow (.github/workflows/migrations.yml) verified green on GitHub Actions 2026-09-20 (migrate up, all the way down, back up against a scratch Postgres 17). DB choice: Supabase (Postgres 17), auth stays better-auth per CLAUDE.md — RLS is off pending M20.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -10632,7 +10632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K127"/>
+  <dimension ref="A1:K128"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col width="10" customWidth="1" style="38" min="1" max="2"/>
@@ -17406,6 +17406,61 @@
       <c r="K127" t="inlineStr">
         <is>
           <t>New scope, not an existing F-number's AC -- added per CLAUDE.md's "if it doesn't map, say so" rule, at the user's explicit request after asking how to curate real videos. Migration 0062 adds concepts.video_url/video_title (both nullable -- most concepts have neither yet). Threaded through both remediation code paths: buildRemediationPack (new pack) and loadTaskView (reopening an existing one) each independently fetch the concept and surface its video fields -- covered by two separate assertions in remediation.integration.test.ts, one per path. The 8 real Chapter 1 concepts (C7M-1.1 through C7M-1.8, this session's NCERT content rollout) were curated with real YouTube links found via web search: C7M-1.1/1.2 (reading/writing large numbers, Indian system) got a topic-matched video; C7M-1.3 through 1.8 got the same full-chapter walkthrough video since verifying which exact timestamp covers e.g. "multiplication shortcuts via regrouping" specifically was not something search snippets alone could confirm without watching -- reusing a video that genuinely covers the whole chapter (true by definition) was the honest choice over fabricating false per-concept precision. Also fixed while investigating live test failures this same session: 4 orphaned concepts (and their full dependency chain -- 6 questions, 4 papers, 3 attempts, evaluations) left behind by earlier crashed test runs today were polluting MATH-SEED chapter 1's shared concept pool, causing generatePaper()'s weighted selection to intermittently draw a stray leftover concept instead of a test's own fixture -- confirmed as the root cause of several "expected X to be Y" failures in student-dashboard.integration.test.ts and weekly-summary.integration.test.ts earlier in the day; cleaned up via a full cascade delete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="15" customHeight="1" s="38">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>F125</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Points, coins &amp; anonymous board/class/subject leaderboard</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>As a student I want to earn points and gold coins for correct MCQ answers (more for harder questions), with a reward animation and sound, and see my rank against other students anonymously so that practice feels rewarding without exposing my real identity or performance to strangers.</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Points are awarded only on MCQ (objective, answer-key-deterministic) questions, at submit -- the same instant-confirm moment F119 already established for adaptive-practice MCQs; written/subjective questions never award points before a mark is confirmed. Point values are a documented default (Easy 10, Hard 20, Hardest 30 -- no external spec exists, same convention F118/F063 use). A coin animation + sound effect plays client-side (respects prefers-reduced-motion and a mute toggle; never delays or blocks the result). Leaderboard participation is opt-in, off by default, consent captured the same way F095 captures guardian consent. The leaderboard shows an anonymous nickname/avatar only, never a real name; a student can regenerate her nickname. Scope is the same (board, class, subject) triple -- never cross-class or cross-subject. Only an aggregate point total and rank are shown, never a competitor's concept-level performance, answers, or any other student's data, keeping T09 intact.</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="G128" s="9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="H128" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>New tracked scope, not an existing F-number's AC -- added as F125 per CLAUDE.md's "if it doesn't map, say so" rule, at the user's explicit request (2026-09-22). Three rounds of clarifying questions settled the open design questions: display identity = anonymous nickname/avatar only (T09-adjacent privacy, not a T09 violation since no underlying student data is exposed, only an opted-in point total); scope = same board+class+subject, not global and not siblings-only; points trigger = MCQ submit via the existing deterministic answer-key check, not written/subjective questions pending a confirmed mark. Filed under M15 (Study Planner / P3 Engagement) as the closest existing module -- no module for gamification exists yet. Not yet built.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -17455,12 +17455,12 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>New tracked scope, not an existing F-number's AC -- added as F125 per CLAUDE.md's "if it doesn't map, say so" rule, at the user's explicit request (2026-09-22). Three rounds of clarifying questions settled the open design questions: display identity = anonymous nickname/avatar only (T09-adjacent privacy, not a T09 violation since no underlying student data is exposed, only an opted-in point total); scope = same board+class+subject, not global and not siblings-only; points trigger = MCQ submit via the existing deterministic answer-key check, not written/subjective questions pending a confirmed mark. Filed under M15 (Study Planner / P3 Engagement) as the closest existing module -- no module for gamification exists yet. Not yet built.</t>
+          <t>New tracked scope, not an existing F-number's AC -- added as F125 per CLAUDE.md's "if it doesn't map, say so" rule, at the user's explicit request (2026-09-22). Three rounds of clarifying questions settled the open design questions: display identity = anonymous nickname/avatar only (T09-adjacent privacy, not a T09 violation since no underlying student data is exposed, only an opted-in point total); scope = same board+class+subject, not global and not siblings-only; points trigger = MCQ submit via the existing deterministic answer-key check, not written/subjective questions pending a confirmed mark. Filed under M15 (Study Planner / P3 Engagement) as the closest existing module -- no module for gamification exists yet. Not yet built. [UPDATE] Schema + points-earning logic shipped (migration 0068, src/lib/points.ts, hooked into confirmEvaluation): student_points_ledger append-only table, students.leaderboard_opt_in/leaderboard_nickname columns, points/coins awarded for a correctly-answered MCQ-family item at the moment its mark is confirmed (Easy 10 / Hard 20 / Hardest 30). Covered by student-points.integration.test.ts (3 tests); full suite green (505 tests). Not yet built: the reward animation/sound, the opt-in consent UI, and the leaderboard screen/API itself -- this slice is schema + earning logic only.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -17460,7 +17460,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>New tracked scope, not an existing F-number's AC -- added as F125 per CLAUDE.md's "if it doesn't map, say so" rule, at the user's explicit request (2026-09-22). Three rounds of clarifying questions settled the open design questions: display identity = anonymous nickname/avatar only (T09-adjacent privacy, not a T09 violation since no underlying student data is exposed, only an opted-in point total); scope = same board+class+subject, not global and not siblings-only; points trigger = MCQ submit via the existing deterministic answer-key check, not written/subjective questions pending a confirmed mark. Filed under M15 (Study Planner / P3 Engagement) as the closest existing module -- no module for gamification exists yet. Not yet built. [UPDATE] Schema + points-earning logic shipped (migration 0068, src/lib/points.ts, hooked into confirmEvaluation): student_points_ledger append-only table, students.leaderboard_opt_in/leaderboard_nickname columns, points/coins awarded for a correctly-answered MCQ-family item at the moment its mark is confirmed (Easy 10 / Hard 20 / Hardest 30). Covered by student-points.integration.test.ts (3 tests); full suite green (505 tests). Not yet built: the reward animation/sound, the opt-in consent UI, and the leaderboard screen/API itself -- this slice is schema + earning logic only.</t>
+          <t>New tracked scope, not an existing F-number's AC -- added as F125 per CLAUDE.md's "if it doesn't map, say so" rule, at the user's explicit request (2026-09-22). Three rounds of clarifying questions settled the open design questions: display identity = anonymous nickname/avatar only (T09-adjacent privacy, not a T09 violation since no underlying student data is exposed, only an opted-in point total); scope = same board+class+subject, not global and not siblings-only; points trigger = MCQ submit via the existing deterministic answer-key check, not written/subjective questions pending a confirmed mark. Filed under M15 (Study Planner / P3 Engagement) as the closest existing module -- no module for gamification exists yet. Not yet built. [UPDATE] Schema + points-earning logic shipped (migration 0068, src/lib/points.ts, hooked into confirmEvaluation): student_points_ledger append-only table, students.leaderboard_opt_in/leaderboard_nickname columns, points/coins awarded for a correctly-answered MCQ-family item at the moment its mark is confirmed (Easy 10 / Hard 20 / Hardest 30). Covered by student-points.integration.test.ts (3 tests); full suite green (505 tests). Not yet built: the reward animation/sound, the opt-in consent UI, and the leaderboard screen/API itself -- this slice is schema + earning logic only. [UPDATE 2] Opt-in + leaderboard read shipped: migration 0069 adds student_points_ledger.subject_id (the cohort key -- one subject_id already is board+class+subject); src/lib/leaderboard.ts (anonymous nickname generator, rank/points aggregation, opted-out students stay privately visible to themselves only); PATCH /api/students/me/leaderboard-opt-in (student-SELF controls this, not the parent -- a deliberate call, documented in the commit, since it only ever exposes an anonymous nickname + aggregate point total, never real identity or per-question data, the same posture already used for her own theme choice on /my-paper); GET /api/leaderboard (student-self only for now; a parent viewing any of her students leaderboard, the pattern F123 set for GET /api/papers, is a reasonable follow-up, not built this pass); new /leaderboard screen (tab06 has no row for this screen -- same as the rest of F125). Verified against a real running dev server with real earned points (screenshot walkthrough of both the pre-opt-in private state and the post-opt-in ranked state). Also fixed two test-fixture bugs surfaced while verifying under the full suite: this slices own integration tests were fixturing MATH-SEED chapter 1 (already flagged as shared/contested by F012s own migration note) instead of a dedicated isolated chapter, occasionally starving other tests (F118) of their own fixture question; and this sessions ad-hoc screenshot-verification scripts had left real leftover fixture rows in real Mathematics chapter 1 content, found and removed. Full suite 509/509 green. Not yet built: reward animation/sound, a parent-facing leaderboard view.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -17460,7 +17460,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>New tracked scope, not an existing F-number's AC -- added as F125 per CLAUDE.md's "if it doesn't map, say so" rule, at the user's explicit request (2026-09-22). Three rounds of clarifying questions settled the open design questions: display identity = anonymous nickname/avatar only (T09-adjacent privacy, not a T09 violation since no underlying student data is exposed, only an opted-in point total); scope = same board+class+subject, not global and not siblings-only; points trigger = MCQ submit via the existing deterministic answer-key check, not written/subjective questions pending a confirmed mark. Filed under M15 (Study Planner / P3 Engagement) as the closest existing module -- no module for gamification exists yet. Not yet built. [UPDATE] Schema + points-earning logic shipped (migration 0068, src/lib/points.ts, hooked into confirmEvaluation): student_points_ledger append-only table, students.leaderboard_opt_in/leaderboard_nickname columns, points/coins awarded for a correctly-answered MCQ-family item at the moment its mark is confirmed (Easy 10 / Hard 20 / Hardest 30). Covered by student-points.integration.test.ts (3 tests); full suite green (505 tests). Not yet built: the reward animation/sound, the opt-in consent UI, and the leaderboard screen/API itself -- this slice is schema + earning logic only. [UPDATE 2] Opt-in + leaderboard read shipped: migration 0069 adds student_points_ledger.subject_id (the cohort key -- one subject_id already is board+class+subject); src/lib/leaderboard.ts (anonymous nickname generator, rank/points aggregation, opted-out students stay privately visible to themselves only); PATCH /api/students/me/leaderboard-opt-in (student-SELF controls this, not the parent -- a deliberate call, documented in the commit, since it only ever exposes an anonymous nickname + aggregate point total, never real identity or per-question data, the same posture already used for her own theme choice on /my-paper); GET /api/leaderboard (student-self only for now; a parent viewing any of her students leaderboard, the pattern F123 set for GET /api/papers, is a reasonable follow-up, not built this pass); new /leaderboard screen (tab06 has no row for this screen -- same as the rest of F125). Verified against a real running dev server with real earned points (screenshot walkthrough of both the pre-opt-in private state and the post-opt-in ranked state). Also fixed two test-fixture bugs surfaced while verifying under the full suite: this slices own integration tests were fixturing MATH-SEED chapter 1 (already flagged as shared/contested by F012s own migration note) instead of a dedicated isolated chapter, occasionally starving other tests (F118) of their own fixture question; and this sessions ad-hoc screenshot-verification scripts had left real leftover fixture rows in real Mathematics chapter 1 content, found and removed. Full suite 509/509 green. Not yet built: reward animation/sound, a parent-facing leaderboard view.</t>
+          <t>New tracked scope, not an existing F-number's AC -- added as F125 per CLAUDE.md's "if it doesn't map, say so" rule, at the user's explicit request (2026-09-22). Three rounds of clarifying questions settled the open design questions: display identity = anonymous nickname/avatar only (T09-adjacent privacy, not a T09 violation since no underlying student data is exposed, only an opted-in point total); scope = same board+class+subject, not global and not siblings-only; points trigger = MCQ submit via the existing deterministic answer-key check, not written/subjective questions pending a confirmed mark. Filed under M15 (Study Planner / P3 Engagement) as the closest existing module -- no module for gamification exists yet. Not yet built. [UPDATE] Schema + points-earning logic shipped (migration 0068, src/lib/points.ts, hooked into confirmEvaluation): student_points_ledger append-only table, students.leaderboard_opt_in/leaderboard_nickname columns, points/coins awarded for a correctly-answered MCQ-family item at the moment its mark is confirmed (Easy 10 / Hard 20 / Hardest 30). Covered by student-points.integration.test.ts (3 tests); full suite green (505 tests). Not yet built: the reward animation/sound, the opt-in consent UI, and the leaderboard screen/API itself -- this slice is schema + earning logic only. [UPDATE 2] Opt-in + leaderboard read shipped: migration 0069 adds student_points_ledger.subject_id (the cohort key -- one subject_id already is board+class+subject); src/lib/leaderboard.ts (anonymous nickname generator, rank/points aggregation, opted-out students stay privately visible to themselves only); PATCH /api/students/me/leaderboard-opt-in (student-SELF controls this, not the parent -- a deliberate call, documented in the commit, since it only ever exposes an anonymous nickname + aggregate point total, never real identity or per-question data, the same posture already used for her own theme choice on /my-paper); GET /api/leaderboard (student-self only for now; a parent viewing any of her students leaderboard, the pattern F123 set for GET /api/papers, is a reasonable follow-up, not built this pass); new /leaderboard screen (tab06 has no row for this screen -- same as the rest of F125). Verified against a real running dev server with real earned points (screenshot walkthrough of both the pre-opt-in private state and the post-opt-in ranked state). Also fixed two test-fixture bugs surfaced while verifying under the full suite: this slices own integration tests were fixturing MATH-SEED chapter 1 (already flagged as shared/contested by F012s own migration note) instead of a dedicated isolated chapter, occasionally starving other tests (F118) of their own fixture question; and this sessions ad-hoc screenshot-verification scripts had left real leftover fixture rows in real Mathematics chapter 1 content, found and removed. Full suite 509/509 green. Not yet built: reward animation/sound, a parent-facing leaderboard view. [UPDATE 3] Reward animation/sound shipped: POST /api/attempts/:id/submit now returns points_earned ({points, coins}) whenever the just-confirmed evaluation actually paid out (the all-MCQ adaptive-paper auto-confirm path only -- null otherwise, since nothing has been confirmed yet for a parent-gated paper). /attempt/:id shows a coin badge on the results card (prefers-reduced-motion respected) and plays a short synthesized Web Audio chime (src/lib/reward-sound.ts -- no external audio asset, best-effort, never blocks showing the result). Covered by a new assertion in the existing adaptive-learning.integration.test.ts (the exact points/coins total for a controlled right/wrong mix), full suite still 509/509, and confirmed live against the real e2e adaptive-flow spec in isolation (that spec and happy-path both hit pre-existing, unrelated flakes on /profile-setup and under DB-pool contention when run concurrently with the full suite -- neither touches this change). Status stays In Progress: the one item left is a parent-facing leaderboard view.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -17455,12 +17455,12 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>New tracked scope, not an existing F-number's AC -- added as F125 per CLAUDE.md's "if it doesn't map, say so" rule, at the user's explicit request (2026-09-22). Three rounds of clarifying questions settled the open design questions: display identity = anonymous nickname/avatar only (T09-adjacent privacy, not a T09 violation since no underlying student data is exposed, only an opted-in point total); scope = same board+class+subject, not global and not siblings-only; points trigger = MCQ submit via the existing deterministic answer-key check, not written/subjective questions pending a confirmed mark. Filed under M15 (Study Planner / P3 Engagement) as the closest existing module -- no module for gamification exists yet. Not yet built. [UPDATE] Schema + points-earning logic shipped (migration 0068, src/lib/points.ts, hooked into confirmEvaluation): student_points_ledger append-only table, students.leaderboard_opt_in/leaderboard_nickname columns, points/coins awarded for a correctly-answered MCQ-family item at the moment its mark is confirmed (Easy 10 / Hard 20 / Hardest 30). Covered by student-points.integration.test.ts (3 tests); full suite green (505 tests). Not yet built: the reward animation/sound, the opt-in consent UI, and the leaderboard screen/API itself -- this slice is schema + earning logic only. [UPDATE 2] Opt-in + leaderboard read shipped: migration 0069 adds student_points_ledger.subject_id (the cohort key -- one subject_id already is board+class+subject); src/lib/leaderboard.ts (anonymous nickname generator, rank/points aggregation, opted-out students stay privately visible to themselves only); PATCH /api/students/me/leaderboard-opt-in (student-SELF controls this, not the parent -- a deliberate call, documented in the commit, since it only ever exposes an anonymous nickname + aggregate point total, never real identity or per-question data, the same posture already used for her own theme choice on /my-paper); GET /api/leaderboard (student-self only for now; a parent viewing any of her students leaderboard, the pattern F123 set for GET /api/papers, is a reasonable follow-up, not built this pass); new /leaderboard screen (tab06 has no row for this screen -- same as the rest of F125). Verified against a real running dev server with real earned points (screenshot walkthrough of both the pre-opt-in private state and the post-opt-in ranked state). Also fixed two test-fixture bugs surfaced while verifying under the full suite: this slices own integration tests were fixturing MATH-SEED chapter 1 (already flagged as shared/contested by F012s own migration note) instead of a dedicated isolated chapter, occasionally starving other tests (F118) of their own fixture question; and this sessions ad-hoc screenshot-verification scripts had left real leftover fixture rows in real Mathematics chapter 1 content, found and removed. Full suite 509/509 green. Not yet built: reward animation/sound, a parent-facing leaderboard view. [UPDATE 3] Reward animation/sound shipped: POST /api/attempts/:id/submit now returns points_earned ({points, coins}) whenever the just-confirmed evaluation actually paid out (the all-MCQ adaptive-paper auto-confirm path only -- null otherwise, since nothing has been confirmed yet for a parent-gated paper). /attempt/:id shows a coin badge on the results card (prefers-reduced-motion respected) and plays a short synthesized Web Audio chime (src/lib/reward-sound.ts -- no external audio asset, best-effort, never blocks showing the result). Covered by a new assertion in the existing adaptive-learning.integration.test.ts (the exact points/coins total for a controlled right/wrong mix), full suite still 509/509, and confirmed live against the real e2e adaptive-flow spec in isolation (that spec and happy-path both hit pre-existing, unrelated flakes on /profile-setup and under DB-pool contention when run concurrently with the full suite -- neither touches this change). Status stays In Progress: the one item left is a parent-facing leaderboard view.</t>
+          <t>New tracked scope, not an existing F-number's AC -- added as F125 per CLAUDE.md's "if it doesn't map, say so" rule, at the user's explicit request (2026-09-22). Three rounds of clarifying questions settled the open design questions: display identity = anonymous nickname/avatar only (T09-adjacent privacy, not a T09 violation since no underlying student data is exposed, only an opted-in point total); scope = same board+class+subject, not global and not siblings-only; points trigger = MCQ submit via the existing deterministic answer-key check, not written/subjective questions pending a confirmed mark. Filed under M15 (Study Planner / P3 Engagement) as the closest existing module -- no module for gamification exists yet. Not yet built. [UPDATE] Schema + points-earning logic shipped (migration 0068, src/lib/points.ts, hooked into confirmEvaluation): student_points_ledger append-only table, students.leaderboard_opt_in/leaderboard_nickname columns, points/coins awarded for a correctly-answered MCQ-family item at the moment its mark is confirmed (Easy 10 / Hard 20 / Hardest 30). Covered by student-points.integration.test.ts (3 tests); full suite green (505 tests). Not yet built: the reward animation/sound, the opt-in consent UI, and the leaderboard screen/API itself -- this slice is schema + earning logic only. [UPDATE 2] Opt-in + leaderboard read shipped: migration 0069 adds student_points_ledger.subject_id (the cohort key -- one subject_id already is board+class+subject); src/lib/leaderboard.ts (anonymous nickname generator, rank/points aggregation, opted-out students stay privately visible to themselves only); PATCH /api/students/me/leaderboard-opt-in (student-SELF controls this, not the parent -- a deliberate call, documented in the commit, since it only ever exposes an anonymous nickname + aggregate point total, never real identity or per-question data, the same posture already used for her own theme choice on /my-paper); GET /api/leaderboard (student-self only for now; a parent viewing any of her students leaderboard, the pattern F123 set for GET /api/papers, is a reasonable follow-up, not built this pass); new /leaderboard screen (tab06 has no row for this screen -- same as the rest of F125). Verified against a real running dev server with real earned points (screenshot walkthrough of both the pre-opt-in private state and the post-opt-in ranked state). Also fixed two test-fixture bugs surfaced while verifying under the full suite: this slices own integration tests were fixturing MATH-SEED chapter 1 (already flagged as shared/contested by F012s own migration note) instead of a dedicated isolated chapter, occasionally starving other tests (F118) of their own fixture question; and this sessions ad-hoc screenshot-verification scripts had left real leftover fixture rows in real Mathematics chapter 1 content, found and removed. Full suite 509/509 green. Not yet built: reward animation/sound, a parent-facing leaderboard view. [UPDATE 3] Reward animation/sound shipped: POST /api/attempts/:id/submit now returns points_earned ({points, coins}) whenever the just-confirmed evaluation actually paid out (the all-MCQ adaptive-paper auto-confirm path only -- null otherwise, since nothing has been confirmed yet for a parent-gated paper). /attempt/:id shows a coin badge on the results card (prefers-reduced-motion respected) and plays a short synthesized Web Audio chime (src/lib/reward-sound.ts -- no external audio asset, best-effort, never blocks showing the result). Covered by a new assertion in the existing adaptive-learning.integration.test.ts (the exact points/coins total for a controlled right/wrong mix), full suite still 509/509, and confirmed live against the real e2e adaptive-flow spec in isolation (that spec and happy-path both hit pre-existing, unrelated flakes on /profile-setup and under DB-pool contention when run concurrently with the full suite -- neither touches this change). Status stays In Progress: the one item left is a parent-facing leaderboard view. [UPDATE 4] User decision 2026-09-22: no parent-facing leaderboard view needed -- GET /api/leaderboard stays student-self only, by design, not a gap. Every stated AC item is built and verified (points by difficulty on MCQ submit, coin+sound reward, opt-in anonymous same-board/class/subject leaderboard, T09 kept intact). Status -&gt; Done.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -10632,7 +10632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K128"/>
+  <dimension ref="A1:K129"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col width="10" customWidth="1" style="38" min="1" max="2"/>
@@ -17461,6 +17461,63 @@
       <c r="K128" t="inlineStr">
         <is>
           <t>New tracked scope, not an existing F-number's AC -- added as F125 per CLAUDE.md's "if it doesn't map, say so" rule, at the user's explicit request (2026-09-22). Three rounds of clarifying questions settled the open design questions: display identity = anonymous nickname/avatar only (T09-adjacent privacy, not a T09 violation since no underlying student data is exposed, only an opted-in point total); scope = same board+class+subject, not global and not siblings-only; points trigger = MCQ submit via the existing deterministic answer-key check, not written/subjective questions pending a confirmed mark. Filed under M15 (Study Planner / P3 Engagement) as the closest existing module -- no module for gamification exists yet. Not yet built. [UPDATE] Schema + points-earning logic shipped (migration 0068, src/lib/points.ts, hooked into confirmEvaluation): student_points_ledger append-only table, students.leaderboard_opt_in/leaderboard_nickname columns, points/coins awarded for a correctly-answered MCQ-family item at the moment its mark is confirmed (Easy 10 / Hard 20 / Hardest 30). Covered by student-points.integration.test.ts (3 tests); full suite green (505 tests). Not yet built: the reward animation/sound, the opt-in consent UI, and the leaderboard screen/API itself -- this slice is schema + earning logic only. [UPDATE 2] Opt-in + leaderboard read shipped: migration 0069 adds student_points_ledger.subject_id (the cohort key -- one subject_id already is board+class+subject); src/lib/leaderboard.ts (anonymous nickname generator, rank/points aggregation, opted-out students stay privately visible to themselves only); PATCH /api/students/me/leaderboard-opt-in (student-SELF controls this, not the parent -- a deliberate call, documented in the commit, since it only ever exposes an anonymous nickname + aggregate point total, never real identity or per-question data, the same posture already used for her own theme choice on /my-paper); GET /api/leaderboard (student-self only for now; a parent viewing any of her students leaderboard, the pattern F123 set for GET /api/papers, is a reasonable follow-up, not built this pass); new /leaderboard screen (tab06 has no row for this screen -- same as the rest of F125). Verified against a real running dev server with real earned points (screenshot walkthrough of both the pre-opt-in private state and the post-opt-in ranked state). Also fixed two test-fixture bugs surfaced while verifying under the full suite: this slices own integration tests were fixturing MATH-SEED chapter 1 (already flagged as shared/contested by F012s own migration note) instead of a dedicated isolated chapter, occasionally starving other tests (F118) of their own fixture question; and this sessions ad-hoc screenshot-verification scripts had left real leftover fixture rows in real Mathematics chapter 1 content, found and removed. Full suite 509/509 green. Not yet built: reward animation/sound, a parent-facing leaderboard view. [UPDATE 3] Reward animation/sound shipped: POST /api/attempts/:id/submit now returns points_earned ({points, coins}) whenever the just-confirmed evaluation actually paid out (the all-MCQ adaptive-paper auto-confirm path only -- null otherwise, since nothing has been confirmed yet for a parent-gated paper). /attempt/:id shows a coin badge on the results card (prefers-reduced-motion respected) and plays a short synthesized Web Audio chime (src/lib/reward-sound.ts -- no external audio asset, best-effort, never blocks showing the result). Covered by a new assertion in the existing adaptive-learning.integration.test.ts (the exact points/coins total for a controlled right/wrong mix), full suite still 509/509, and confirmed live against the real e2e adaptive-flow spec in isolation (that spec and happy-path both hit pre-existing, unrelated flakes on /profile-setup and under DB-pool contention when run concurrently with the full suite -- neither touches this change). Status stays In Progress: the one item left is a parent-facing leaderboard view. [UPDATE 4] User decision 2026-09-22: no parent-facing leaderboard view needed -- GET /api/leaderboard stays student-self only, by design, not a gap. Every stated AC item is built and verified (points by difficulty on MCQ submit, coin+sound reward, opt-in anonymous same-board/class/subject leaderboard, T09 kept intact). Status -&gt; Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>M13</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>F126</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Per-question worked explanation after submission</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>As a student reviewing my marked paper, I want to see why the correct answer is correct, so I learn the method instead of only learning that I was wrong.</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Given a paper whose marks are confirmed, when she opens a question on her result screen and asks for an explanation, then a short worked explanation is shown and cached per question and reused for every student who sees that question afterwards; questions that already carry a question_step_marks scheme use it verbatim with no AI call; with no AI provider configured nothing is invented and she is told it is unavailable; never available before marks are confirmed (T09 amendment 2026-09-22).</t>
+        </is>
+      </c>
+      <c r="G129" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H129" s="10" t="inlineStr">
+        <is>
+          <t>AI-13</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>F049, F067</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Added 2026-09-23 at the owner's request. Lazy generation only -- an ~8,000 question MCQ bank is explained on demand, never bulk-backfilled. Cache lives in question_explanations (migration 0070).</t>
         </is>
       </c>
     </row>
@@ -20426,7 +20483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col width="8" customWidth="1" style="38" min="1" max="1"/>
@@ -20988,6 +21045,28 @@
       <c r="H15" s="51" t="inlineStr">
         <is>
           <t>Admin authors scope manually</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="51" t="inlineStr">
+        <is>
+          <t>AI-13</t>
+        </is>
+      </c>
+      <c r="B16" s="51" t="inlineStr">
+        <is>
+          <t>Per-question worked explanation</t>
+        </is>
+      </c>
+      <c r="C16" s="51" t="inlineStr">
+        <is>
+          <t>Student asks for an explanation on a confirmed result</t>
+        </is>
+      </c>
+      <c r="D16" s="51" t="inlineStr">
+        <is>
+          <t>Strong model (a confidently wrong explanation shown to a child is worse than none)</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -10632,7 +10632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K129"/>
+  <dimension ref="A1:K130"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col width="10" customWidth="1" style="38" min="1" max="2"/>
@@ -17518,6 +17518,61 @@
       <c r="K129" t="inlineStr">
         <is>
           <t>Added 2026-09-23 at the owner's request. Lazy generation only -- an ~8,000 question MCQ bank is explained on demand, never bulk-backfilled. Cache lives in question_explanations (migration 0070).</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="15" customHeight="1" s="38">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>M14</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>F127</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Usability pass: navigation, student home, parent dashboard, loading states</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>As a parent or student I want every screen to show what to do next first, and to move between sections easily on a phone, so that the app is simple to use without explanation.</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Sign out and the signed-in name are reachable from the shell on every page; below the lg breakpoint a bottom tab bar shows the main sections. Student home leads with Recommended next and papers to attempt, then four stat tiles, then needs-improvement/revise/strong, with subjects collapsed until opened. On /my-paper the Generate Assessment button stays in view in a sticky bar below the chapter list. Parent dashboard leads with what waits on the parent (Needs evaluation, Today's action), shows the recap as three numbers, puts each subject's next action first and folds its charts away, shows Delivery Gap in marks with a plain-language definition, and gives the habit dots a legend. Every screen shows skeleton placeholders instead of a bare "Loading..." line. No API, schema or permission changes.</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G130" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H130" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>S22</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Added 2026-09-30 at the owner's request ("make it userfriendly"), after a UX review; the owner chose an in-place overhaul over a rewrite, student screens first. Also fixes a real display bug: /home printed delivery_gap (knowledge_score - actual_score, a count of marks) with a "%" suffix. /student no longer crashes when GET /api/papers returns an error body. e2e/adaptive-flow.spec.ts now opens the fixture subject before checking its concept, since subjects start collapsed. Full e2e (10) and unit (231) suites green.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -10649,7 +10649,7 @@
     <row r="1" ht="24" customHeight="1" s="38">
       <c r="A1" s="42" t="inlineStr">
         <is>
-          <t>03  Feature Backlog  —  124 features. Type Not Started / In Progress / Blocked / Done in column J.</t>
+          <t>03  Feature Backlog  —  127 features. Type Not Started / In Progress / Blocked / Done in column J.</t>
         </is>
       </c>
     </row>
@@ -17482,16 +17482,11 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Student</t>
+          <t>As a student reviewing my marked paper, I want to see why the correct answer is correct, so I learn the method instead of only learning that I was wrong.</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>As a student reviewing my marked paper, I want to see why the correct answer is correct, so I learn the method instead of only learning that I was wrong.</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
           <t>Given a paper whose marks are confirmed, when she opens a question on her result screen and asks for an explanation, then a short worked explanation is shown and cached per question and reused for every student who sees that question afterwards; questions that already carry a question_step_marks scheme use it verbatim with no AI call; with no AI provider configured nothing is invented and she is told it is unavailable; never available before marks are confirmed (T09 amendment 2026-09-22).</t>
         </is>
       </c>
@@ -17500,14 +17495,10 @@
           <t>M</t>
         </is>
       </c>
-      <c r="H129" s="10" t="inlineStr">
-        <is>
-          <t>AI-13</t>
-        </is>
-      </c>
+      <c r="H129" s="10" t="n"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>F049, F067</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -17517,7 +17508,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Added 2026-09-23 at the owner's request. Lazy generation only -- an ~8,000 question MCQ bank is explained on demand, never bulk-backfilled. Cache lives in question_explanations (migration 0070).</t>
+          <t>Added 2026-09-23 at the owner's request. Lazy generation only -- an ~8,000 question MCQ bank is explained on demand, never bulk-backfilled. Cache lives in question_explanations (migration 0070). AI layer: AI-13 (tab 07). Depends on F049, F067. (Row realigned 2026-09-30: values had been entered one column to the right, with a "Student" persona in the User Story column; priority and estimate were never recorded.)</t>
         </is>
       </c>
     </row>
@@ -17582,7 +17573,7 @@
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="J4:J125" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J4:J130" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not Started,In Progress,Blocked,Done"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -10632,7 +10632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K130"/>
+  <dimension ref="A1:K131"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col width="10" customWidth="1" style="38" min="1" max="2"/>
@@ -10649,7 +10649,7 @@
     <row r="1" ht="24" customHeight="1" s="38">
       <c r="A1" s="42" t="inlineStr">
         <is>
-          <t>03  Feature Backlog  —  127 features. Type Not Started / In Progress / Blocked / Done in column J.</t>
+          <t>03  Feature Backlog  —  128 features. Type Not Started / In Progress / Blocked / Done in column J.</t>
         </is>
       </c>
     </row>
@@ -17564,6 +17564,61 @@
       <c r="K130" t="inlineStr">
         <is>
           <t>Added 2026-09-30 at the owner's request ("make it userfriendly"), after a UX review; the owner chose an in-place overhaul over a rewrite, student screens first. Also fixes a real display bug: /home printed delivery_gap (knowledge_score - actual_score, a count of marks) with a "%" suffix. /student no longer crashes when GET /api/papers returns an error body. e2e/adaptive-flow.spec.ts now opens the fixture subject before checking its concept, since subjects start collapsed. Full e2e (10) and unit (231) suites green.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="15" customHeight="1" s="38">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>M14</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>F128</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Aurora visual theme: 3D glass UI, gradient colours, interface sounds</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>As a student I want the app to look and sound exciting and modern, so that I enjoy opening it and practising every day.</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Theme tokens (src/styles.css) define an original violet-pink-orange gradient palette with cyan and lime highlights, in light and dark mode; a slowly drifting colour field sits behind every screen; cards are translucent glass with layered shadows; primary buttons are chunky 3D buttons that press down on click; the active nav item is a glowing gradient pill; Recommended next is a gradient hero card; stat tiles are colour-coded. Every button, link and choice plays a short synthesized sound (Web Audio, no audio files); a sound switch next to the theme toggle turns sounds off, remembered per device, and also silences the F125 coin chime. Animations stop for anyone whose device asks for reduced motion. Printouts stay plain black-on-white. No franchise palette, character or typeface is imitated.</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G131" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H131" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>S22</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Added 2026-09-30 at the owner's request ("most stunning, 3D layers... sound and colour effects" for students born after 2010). Headings now use Outfit instead of Fraunces. Checked with real screenshots (desktop, phone, dark mode). Full e2e (10) and unit (231) suites green.</t>
         </is>
       </c>
     </row>
@@ -17573,7 +17628,7 @@
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="J4:J130" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J4:J131" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not Started,In Progress,Blocked,Done"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -10632,7 +10632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K131"/>
+  <dimension ref="A1:K133"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col width="10" customWidth="1" style="38" min="1" max="2"/>
@@ -10649,7 +10649,7 @@
     <row r="1" ht="24" customHeight="1" s="38">
       <c r="A1" s="42" t="inlineStr">
         <is>
-          <t>03  Feature Backlog  —  128 features. Type Not Started / In Progress / Blocked / Done in column J.</t>
+          <t>03  Feature Backlog  —  130 features. Type Not Started / In Progress / Blocked / Done in column J.</t>
         </is>
       </c>
     </row>
@@ -17580,17 +17580,17 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Aurora visual theme: 3D glass UI, gradient colours, interface sounds</t>
+          <t>Calm pastel visual theme: glass cards, 3D buttons, interface sounds</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>As a student I want the app to look and sound exciting and modern, so that I enjoy opening it and practising every day.</t>
+          <t>As a student I want the app to look calm, modern and pleasant, and to respond with gentle sounds, so that I enjoy opening it and practising every day.</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Theme tokens (src/styles.css) define an original violet-pink-orange gradient palette with cyan and lime highlights, in light and dark mode; a slowly drifting colour field sits behind every screen; cards are translucent glass with layered shadows; primary buttons are chunky 3D buttons that press down on click; the active nav item is a glowing gradient pill; Recommended next is a gradient hero card; stat tiles are colour-coded. Every button, link and choice plays a short synthesized sound (Web Audio, no audio files); a sound switch next to the theme toggle turns sounds off, remembered per device, and also silences the F125 coin chime. Animations stop for anyone whose device asks for reduced motion. Printouts stay plain black-on-white. No franchise palette, character or typeface is imitated.</t>
+          <t>Theme tokens (src/styles.css) define an original calm palette -- warm beige/white base with soft light-pink, baby-blue and butter-yellow washes drifting slowly behind every screen -- and one deep blue for every action so buttons and links stay readable; light and dark mode. Cards are translucent glass with gentle shadows; primary buttons are 3D buttons that press down on click; the active nav item is a soft blue pill; stat tiles carry pastel accents. Every button, link and choice plays a short synthesized sound (Web Audio, no audio files); a sound switch next to the theme toggle turns sounds off, remembered per device, and also silences the F125 coin chime. Animations stop under reduced-motion. Printouts stay plain. No franchise palette, character or typeface is imitated.</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -17618,7 +17618,117 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Added 2026-09-30 at the owner's request ("most stunning, 3D layers... sound and colour effects" for students born after 2010). Headings now use Outfit instead of Fraunces. Checked with real screenshots (desktop, phone, dark mode). Full e2e (10) and unit (231) suites green.</t>
+          <t>Added 2026-09-30 at the owner's request. First shipped as a bright violet/pink/orange "Aurora" theme; revised the same day, at the owner's request, to calm pastels (beige, white, light pink, blue, yellow). Checked with real screenshots in light and dark mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="15" customHeight="1" s="38">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>M09</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>F129</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Readable question typography, spelling-tolerant marking, "Report a problem"</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>As a student I want questions, answers and headings to look clearly different, not to lose marks for a spelling slip, and to be able to tell someone when a question or its marking is wrong, so that my marks reflect what I actually know.</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Typography: headings in Plus Jakarta Sans, question text in Lexend a size above body text with a "Q1" badge, options as tappable tiles, answers in Manrope under small uppercase labels (YOUR ANSWER / CORRECT ANSWER) in tinted boxes -- on the answering, result and review screens. Spelling: a fill-in-the-blank answer that is the right word with a small slip (edits scale with length, first letter must match, numbers must match exactly) earns full marks; the AI grading and re-review prompts explicitly treat recognisable misspellings as correct. Report a problem: on every question, during the attempt and on the result, a student picks a reason (marked wrong but right / question has a mistake / answer key has a mistake / unclear / other) and writes 3-300 characters; one report per question per attempt; own attempt only. Reports never change a mark. Admins see their own household's reports (question, key and the student's answer side by side) at /admin/reports and mark them resolved/dismissed.</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G132" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H132" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>S22</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Added 2026-09-30 at the owner's request. Root cause of the spelling complaint: fill_blank was marked by exact text match (scoring.ts), so "photosynthsis" scored 0. New table question_reports (migration 0071). Admin queue is household-scoped because admin is a household role here, not a cross-tenant superadmin (F083). Tests: question-reports.integration.test.ts, scoring.test.ts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="15" customHeight="1" s="38">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>M07</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>F130</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Student downloads her own question paper as PDF</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>As a student I want to download my question paper as a PDF so that I can print it or practise on paper.</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>A "Download this paper as PDF" button sits above the question paper on the attempt screen and on the result screen. GET /api/papers/:id/pdf now also accepts the student role, but only for a paper generated for her (a sibling's paper is 404) and never with the answer key (include_key from a student is 403). ?download=1 saves it under a readable file name.</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G133" s="9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H133" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>S22</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Added 2026-09-30 at the owner's request. The PDF template never receives answers or which option is correct, so the plain paper is within the T09 rule. Tests in papers-pdf.integration.test.ts.</t>
         </is>
       </c>
     </row>
@@ -17628,7 +17738,7 @@
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="J4:J131" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J4:J133" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not Started,In Progress,Blocked,Done"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -9009,12 +9009,12 @@
       </c>
       <c r="C17" s="51" t="inlineStr">
         <is>
-          <t>Responsive web only. PWA install is acceptable; App Store submission is not in v1.</t>
+          <t>Responsive web only in v1. Revised 2026-09-30 at the owner's request: an Android app ships on Google Play as a Trusted Web Activity over the same web app (F131). iOS/App Store is still excluded.</t>
         </is>
       </c>
       <c r="D17" s="51" t="inlineStr">
         <is>
-          <t>Excluded</t>
+          <t>Revised (F131)</t>
         </is>
       </c>
     </row>
@@ -10632,7 +10632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K133"/>
+  <dimension ref="A1:K134"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col width="10" customWidth="1" style="38" min="1" max="2"/>
@@ -10649,7 +10649,7 @@
     <row r="1" ht="24" customHeight="1" s="38">
       <c r="A1" s="42" t="inlineStr">
         <is>
-          <t>03  Feature Backlog  —  130 features. Type Not Started / In Progress / Blocked / Done in column J.</t>
+          <t>03  Feature Backlog  —  131 features. Type Not Started / In Progress / Blocked / Done in column J.</t>
         </is>
       </c>
     </row>
@@ -17729,6 +17729,61 @@
       <c r="K133" t="inlineStr">
         <is>
           <t>Added 2026-09-30 at the owner's request. The PDF template never receives answers or which option is correct, so the plain paper is within the T09 rule. Tests in papers-pdf.integration.test.ts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="15" customHeight="1" s="38">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>M01</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>F131</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Android app on Google Play (Trusted Web Activity)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>As a parent I want to install ExamPrep AI from the Google Play Store so that my child and I can open it like any other app on our Android phones.</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>An Android app, built as a Trusted Web Activity over the production web app, is published on Google Play. It opens full-screen with no browser URL bar, which proves Digital Asset Links is verified: /.well-known/assetlinks.json is served by the web app, and its SHA-256 fingerprints come from configuration, not code. Every web feature works inside it: sign-in (email and Google), taking an attempt, photographing a handwritten answer with the camera, and downloading a paper PDF. A service worker shows a friendly offline page when there is no network, and never caches API responses or answer data. Phones without a TWA-capable browser fall back to a WebView. A signed AAB is built in CI, never on a developer laptop, and the signing keystore is not in the repo. The Families Policy declarations, a public privacy policy URL and the Data Safety form are complete. iOS/App Store is still excluded.</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G134" s="9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H134" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>S23</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Added 2026-09-30 at the owner's request, reversing tab 01's 'Native mobile apps: out of scope v1'. TWA, not a native rewrite (owner approved): every web feature ships on day one and web deploys reach the app without a Play update. Owner arranging: personal Play Console account (needs a 12-tester, 14-day closed test before production) and a custom domain (the app is bound to its domain, so this must be set before the first Play upload).</t>
         </is>
       </c>
     </row>
@@ -17738,7 +17793,7 @@
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="J4:J133" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J4:J134" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not Started,In Progress,Blocked,Done"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -17783,7 +17783,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Added 2026-09-30 at the owner's request, reversing tab 01's 'Native mobile apps: out of scope v1'. TWA, not a native rewrite (owner approved): every web feature ships on day one and web deploys reach the app without a Play update. Owner arranging: personal Play Console account (needs a 12-tester, 14-day closed test before production) and a custom domain (the app is bound to its domain, so this must be set before the first Play upload).</t>
+          <t>Added 2026-09-30 at the owner's request, reversing tab 01's 'Native mobile apps: out of scope v1'. TWA, not a native rewrite (owner approved): every web feature ships on day one and web deploys reach the app without a Play update. Owner arranging: personal Play Console account (needs a 12-tester, 14-day closed test before production) and a custom domain (the app is bound to its domain, so this must be set before the first Play upload). 2026-09-30 later, owner decisions: domain www.prepplan.in (registered at GoDaddy; the apex redirects to www), Android appId in.prepplan.app (permanent), user-facing brand renamed ExamPrep AI -&gt; PrepPlan across web + app (internal names unchanged), support email support@prepplan.in. Also added public /privacy and /delete-account pages and docs/android/play-console-answers.md. Open blocker: a student who signed up alone cannot delete her own account.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -13428,10 +13428,14 @@
       </c>
       <c r="J53" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K53" s="51" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K53" s="51" t="inlineStr">
+        <is>
+          <t>Built 2026-09-30. /scan/:attemptId: multi-photo, camera and PDF (pdf.js renders pages in the browser), client-side compression to &lt;=1800px JPEG, orientation from EXIF plus a manual quarter-turn, per-page preview and reorder (before and after upload), 20 MB / 20 pages / 3 MB-per-page caps with clear errors. Entry points: 'Wrote it on paper? Upload photos' on the attempt screen; 'Upload photos of her answers' on the parent's paper page (POST /api/papers/:id/scan-attempt). Tests: scan-upload.integration.test.ts, plus a real-browser check with a photo, a sideways photo and a 2-page PDF.</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="23.25" customHeight="1" s="38">
       <c r="A54" s="51" t="inlineStr">
@@ -13479,10 +13483,14 @@
       </c>
       <c r="J54" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K54" s="51" t="n"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="K54" s="51" t="inlineStr">
+        <is>
+          <t>Page reader built 2026-09-30 (transcribePage, AI-06): per-answer text or option, confidence and position; prompt keeps Telugu script, never romanised. Vision-only provider chain (VISION_PROVIDERS: Anthropic, Gemini), which also fixes the old single-answer reader possibly reaching text-only Groq/Cerebras. NOT yet verified against real handwriting with a live model -- T15 (20 real pages, English and Telugu) still to run; stays In Progress until then.</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="23.25" customHeight="1" s="38">
       <c r="A55" s="51" t="inlineStr">
@@ -13530,10 +13538,14 @@
       </c>
       <c r="J55" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K55" s="51" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K55" s="51" t="inlineStr">
+        <is>
+          <t>Built 2026-09-30 (scan-mapping.ts). OR pairs keyed 7A/7B and told apart by content, never by print order (the template's order within a pair isn't stable). A bare OR number, an unknown number, or two answers for one question (including both halves of an OR pair) are raised for manual assignment; the server refuses to mark until settled. T16 manual run still to do on real pages; logic covered by unit + integration tests.</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="23.25" customHeight="1" s="38">
       <c r="A56" s="51" t="inlineStr">
@@ -13581,10 +13593,14 @@
       </c>
       <c r="J56" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K56" s="51" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K56" s="51" t="inlineStr">
+        <is>
+          <t>Built 2026-09-30. Threshold 0.85 (OCR_CONFIDENCE_THRESHOLD). Each reading is shown under its crop of the photo; unclear ones must be confirmed or corrected; an MCQ option the question never printed drops to confidence 0. POST /api/attempts/:id/scan/apply re-checks everything server-side (409 needs_review). The parent or the student can confirm.</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="23.25" customHeight="1" s="38">
       <c r="A57" s="51" t="inlineStr">
@@ -15942,10 +15958,14 @@
       </c>
       <c r="J100" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K100" s="51" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K100" s="51" t="inlineStr">
+        <is>
+          <t>Built 2026-09-30. Pages AES-256-GCM encrypted by the app (key HKDF-derived from BETTER_AUTH_SECRET) before the database; served only by GET /api/scan-pages/:id with a 10-minute HMAC-signed link AND a session with access; Cache-Control no-store; no bucket, no public path. Images purged 30 days after upload by the daily cron. /privacy updated. Tests cover tamper, wrong key, expiry, forged/moved signatures, cross-household, retention.</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="23.25" customHeight="1" s="38">
       <c r="A101" s="51" t="inlineStr">
@@ -17809,7 +17829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" style="38" min="1" max="1"/>
@@ -18741,6 +18761,60 @@
       <c r="E36" t="inlineStr">
         <is>
           <t>M20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>scan_pages</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>F050/F097: one photographed page of a written paper, AES-256-GCM encrypted by the app. Image nulled 30 days after upload (row kept).</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>id, attempt_id, student_id, upload_id, page_number, mime, size_bytes, image (bytea, encrypted), extracted_at, extraction_error, uploaded_by_user_id, created_at, purged_at</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>-&gt; attempts, students, uploads, users</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>M10/M20</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>scan_detections</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>F051-F053: one answer the vision model found on a page, its mapping to a question, confidence, position on the page, and review status.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>id, attempt_id, student_id, scan_page_id, detected_label, paper_question_id, response_text, selected_option, confidence, bbox, status, confirmed_by_user_id, confirmed_at, created_at</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>-&gt; attempts, students, scan_pages, paper_questions, users</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>M10</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col width="10" customWidth="1" style="38" min="1" max="1"/>
@@ -20021,6 +20095,294 @@
         </is>
       </c>
       <c r="F41" s="51" t="inlineStr">
+        <is>
+          <t>M20</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="51" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B42" s="51" t="inlineStr">
+        <is>
+          <t>/api/papers/:id/scan-attempt</t>
+        </is>
+      </c>
+      <c r="C42" s="51" t="inlineStr">
+        <is>
+          <t>Student (own) or Parent/Admin (household)</t>
+        </is>
+      </c>
+      <c r="D42" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E42" s="51" t="inlineStr">
+        <is>
+          <t>attempt_id (open attempt reused, else new mode=uploaded)</t>
+        </is>
+      </c>
+      <c r="F42" s="51" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="51" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B43" s="51" t="inlineStr">
+        <is>
+          <t>/api/attempts/:id/scan</t>
+        </is>
+      </c>
+      <c r="C43" s="51" t="inlineStr">
+        <is>
+          <t>Student (own) or Parent/Admin (household)</t>
+        </is>
+      </c>
+      <c r="D43" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" s="51" t="inlineStr">
+        <is>
+          <t>pages (signed 10-min links), questions (no key), readings, blockers</t>
+        </is>
+      </c>
+      <c r="F43" s="51" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="51" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="B44" s="51" t="inlineStr">
+        <is>
+          <t>/api/attempts/:id/scan</t>
+        </is>
+      </c>
+      <c r="C44" s="51" t="inlineStr">
+        <is>
+          <t>Student (own) or Parent/Admin (household)</t>
+        </is>
+      </c>
+      <c r="D44" s="51" t="inlineStr">
+        <is>
+          <t>page_ids[] (new order)</t>
+        </is>
+      </c>
+      <c r="E44" s="51" t="inlineStr">
+        <is>
+          <t>scan state</t>
+        </is>
+      </c>
+      <c r="F44" s="51" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="51" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B45" s="51" t="inlineStr">
+        <is>
+          <t>/api/attempts/:id/scan/pages</t>
+        </is>
+      </c>
+      <c r="C45" s="51" t="inlineStr">
+        <is>
+          <t>Student (own) or Parent/Admin (household)</t>
+        </is>
+      </c>
+      <c r="D45" s="51" t="inlineStr">
+        <is>
+          <t>media_type, image_base64 (&lt;=3 MB; 20 MB / 20 pages per paper)</t>
+        </is>
+      </c>
+      <c r="E45" s="51" t="inlineStr">
+        <is>
+          <t>page id, page_number</t>
+        </is>
+      </c>
+      <c r="F45" s="51" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="51" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="B46" s="51" t="inlineStr">
+        <is>
+          <t>/api/attempts/:id/scan/pages/:pageId</t>
+        </is>
+      </c>
+      <c r="C46" s="51" t="inlineStr">
+        <is>
+          <t>Student (own) or Parent/Admin (household)</t>
+        </is>
+      </c>
+      <c r="D46" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E46" s="51" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="F46" s="51" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="51" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B47" s="51" t="inlineStr">
+        <is>
+          <t>/api/attempts/:id/scan/pages/:pageId/extract</t>
+        </is>
+      </c>
+      <c r="C47" s="51" t="inlineStr">
+        <is>
+          <t>Student (own) or Parent/Admin (household)</t>
+        </is>
+      </c>
+      <c r="D47" s="51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E47" s="51" t="inlineStr">
+        <is>
+          <t>found (count); vision read + question mapping</t>
+        </is>
+      </c>
+      <c r="F47" s="51" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="51" t="inlineStr">
+        <is>
+          <t>PATCH</t>
+        </is>
+      </c>
+      <c r="B48" s="51" t="inlineStr">
+        <is>
+          <t>/api/attempts/:id/scan/detections/:detectionId</t>
+        </is>
+      </c>
+      <c r="C48" s="51" t="inlineStr">
+        <is>
+          <t>Student (own) or Parent/Admin (household)</t>
+        </is>
+      </c>
+      <c r="D48" s="51" t="inlineStr">
+        <is>
+          <t>action confirm|discard|restore, paper_question_id?, response_text?, selected_option?</t>
+        </is>
+      </c>
+      <c r="E48" s="51" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="F48" s="51" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="51" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B49" s="51" t="inlineStr">
+        <is>
+          <t>/api/attempts/:id/scan/apply</t>
+        </is>
+      </c>
+      <c r="C49" s="51" t="inlineStr">
+        <is>
+          <t>Student (own) or Parent/Admin (household)</t>
+        </is>
+      </c>
+      <c r="D49" s="51" t="inlineStr">
+        <is>
+          <t>confirm_blanks?</t>
+        </is>
+      </c>
+      <c r="E49" s="51" t="inlineStr">
+        <is>
+          <t>submitted attempt; 409 needs_review / blank_answers</t>
+        </is>
+      </c>
+      <c r="F49" s="51" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="51" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B50" s="51" t="inlineStr">
+        <is>
+          <t>/api/scan-pages/:pageId</t>
+        </is>
+      </c>
+      <c r="C50" s="51" t="inlineStr">
+        <is>
+          <t>Signed URL AND session with access</t>
+        </is>
+      </c>
+      <c r="D50" s="51" t="inlineStr">
+        <is>
+          <t>exp, sig</t>
+        </is>
+      </c>
+      <c r="E50" s="51" t="inlineStr">
+        <is>
+          <t>page image (no-store)</t>
+        </is>
+      </c>
+      <c r="F50" s="51" t="inlineStr">
         <is>
           <t>M20</t>
         </is>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -16018,7 +16018,7 @@
       </c>
       <c r="K101" s="51" t="inlineStr">
         <is>
-          <t>POST /api/privacy/export (tab05's exact route) returns the full household export synchronously in the response rather than the AC's async-job-plus-email flow -- there is no job queue or email provider in this app (M16 is Not Started), and a household's data isn't large enough at launch scope for synchronous to be a real problem; the export's own `notes` field says so rather than silently pretending PDFs/scans are bundled (they aren't -- papers are rendered on demand, and there's no real scan storage since M10 wasn't built this pass). POST /api/privacy/delete (not in tab05, but the AC's other half) hard-deletes the household -- a deliberate, DPDP-driven exception to CLAUDE.md invariant 4 ('nothing is deleted'), justified explicitly by this feature's own right-to-erasure requirement. Verified against the actual migrations, not assumed, that every table genuinely cascades from households.id (directly or transitively through students.id) before relying on a single DELETE to erase everything. New deletion_log table (migration 0048) is the erasure audit trail -- household_id is deliberately a plain column, not a foreign key, or the audit row would cascade away in the same transaction as the data it's proving was deleted. Requires typing the household's real name back (not just a boolean) as the confirmation gesture, matching common practice for a genuinely irreversible action. New /settings screen (tab06's exact route). Verified live end to end against the real dev server and dev DB with Playwright: the delete button stays disabled until the typed name matches exactly, and clicking it actually erased the household (re-queried after, not assumed) while the deletion_log row survived and the session correctly stopped authenticating afterward. New integration test suite exercises the same: real export contents, wrong-name rejection, real cascade-delete, and post-delete session invalidation. The AC's exact 30-day SLA and any formal legal notice requirements need real legal review, same caveat F095 already flagged for verifiable parental consent -- the mechanical capability is what's built here. Full suite green (181 tests, up from 176).</t>
+          <t>POST /api/privacy/export (tab05's exact route) returns the full household export synchronously in the response rather than the AC's async-job-plus-email flow -- there is no job queue or email provider in this app (M16 is Not Started), and a household's data isn't large enough at launch scope for synchronous to be a real problem; the export's own `notes` field says so rather than silently pretending PDFs/scans are bundled (they aren't -- papers are rendered on demand, and there's no real scan storage since M10 wasn't built this pass). POST /api/privacy/delete (not in tab05, but the AC's other half) hard-deletes the household -- a deliberate, DPDP-driven exception to CLAUDE.md invariant 4 ('nothing is deleted'), justified explicitly by this feature's own right-to-erasure requirement. Verified against the actual migrations, not assumed, that every table genuinely cascades from households.id (directly or transitively through students.id) before relying on a single DELETE to erase everything. New deletion_log table (migration 0048) is the erasure audit trail -- household_id is deliberately a plain column, not a foreign key, or the audit row would cascade away in the same transaction as the data it's proving was deleted. Requires typing the household's real name back (not just a boolean) as the confirmation gesture, matching common practice for a genuinely irreversible action. New /settings screen (tab06's exact route). Verified live end to end against the real dev server and dev DB with Playwright: the delete button stays disabled until the typed name matches exactly, and clicking it actually erased the household (re-queried after, not assumed) while the deletion_log row survived and the session correctly stopped authenticating afterward. New integration test suite exercises the same: real export contents, wrong-name rejection, real cascade-delete, and post-delete session invalidation. The AC's exact 30-day SLA and any formal legal notice requirements need real legal review, same caveat F095 already flagged for verifiable parental consent -- the mechanical capability is what's built here. Full suite green (181 tests, up from 176). 2026-10-01 (owner decision, Google Play requirement): a student who signed up on her own and is not linked to a parent can delete her own account from Settings (typed DELETE; GET/POST /api/privacy/delete-self); a parent-added or parent-linked student is refused and must ask the parent. Also fixed a real bug: a parent deleting a household that a self-signed-up student had been linked into failed with a 500 (two interlocking RESTRICT keys: consents.given_by_user_id and students.own_household_id); deleteHouseholdData now deletes her original household's consents, then the household, then the original. Tests: student-self-delete.integration.test.ts.</t>
         </is>
       </c>
     </row>

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -11471,10 +11471,14 @@
       </c>
       <c r="J17" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K17" s="51" t="n"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="K17" s="51" t="inlineStr">
+        <is>
+          <t>Built 2026-10-01. Finding: the Supabase project is on the FREE plan, which keeps no restorable backups and no PITR, so there was no backup of any real student data. Now: .github/workflows/backup.yml runs daily 02:00 IST: pg_dump of the public schema, AES-256 encrypted (scripts/db-backup.sh), then restored into a scratch Postgres 17 and every table's row count checked (scripts/db-restore.sh); artifact kept 30 days. Restore refuses the production host, a non-empty target and a weak passphrase (all four refusals tested). Local drill on the test DB: 59/59 tables verified in 12 s. RPO 24 h, RTO ~30 min, PITR none (needs Supabase Pro + add-on), all stated in docs/runbooks/backup-restore.md. Stays In Progress until the owner adds the PROD_DATABASE_URL + BACKUP_PASSPHRASE secrets and the first production run is green; that run is the 'documented restore tested once' on real data.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="23.25" customHeight="1" s="38">
       <c r="A18" s="51" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -15424,10 +15424,14 @@
       </c>
       <c r="J90" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K90" s="51" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="K90" s="51" t="inlineStr">
+        <is>
+          <t>Built 2026-10-01. PDF: Noto Sans Telugu (OFL, Google Fonts Telugu subset, 124 KB variable font, src/lib/pdf/fonts/) is inlined into every PDF template's HTML as a data URL with a Telugu-only unicode-range, so the serverless renderer needs no system font; render.ts now waits for document.fonts.ready before printing. Screen: Noto Sans Telugu added to the Google Fonts import and every font stack (downloaded only when a page contains Telugu). Verified on a 209-word sample (telugu-sample.fixture.ts) with ottulu (క్ష స్త్ర ద్ధ శ్రీ జ్ఞ ఙ్మ త్మ ర్య ప్ర), deerghalu (కా కీ కూ కే కో ఐ ఔ), reph, ZWNJ, visarga and Telugu digits: visually in a real PDF and on screen, and automatically in telugu-pdf.integration.test.ts (the bundled face loads and covers the sample in all 3 themes; the PDF embeds it as Type3 glyphs, never a system Telugu font). Mutation-checked: removing the font fails 4 tests. Mallanna not added (AC says Noto Sans Telugu / Mallanna; one is enough). Not covered: diagram SVG labels still use Helvetica.</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="23.25" customHeight="1" s="38">
       <c r="A91" s="51" t="inlineStr">

--- a/docs/ExamPrep_AI_Module_Development_Plan.xlsx
+++ b/docs/ExamPrep_AI_Module_Development_Plan.xlsx
@@ -16500,10 +16500,14 @@
       </c>
       <c r="J110" s="8" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K110" s="51" t="n"/>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="K110" s="51" t="inlineStr">
+        <is>
+          <t>2026-10-01. Automated half done: src/lib/pdf/print-qa.integration.test.ts renders a 45-question stress paper (MCQ, long answers, diagrams, OR pairs, 3 sections) in all 3 themes at 9 page-break offsets each (27 layouts), then reads the PDF back with pdf.js. Every page is A4; no question is split across pages; no section title is left alone at a page bottom; no text falls in the 14/12 mm margins. Found and fixed a real bug: section titles were orphaned at the foot of a page (Clean School: Section B on p3, its questions on p4). Fixed with break-after: avoid; the answer key and report also keep their h2 with what follows and never split a table row. Both checks mutation-tested (removing either rule fails the test). Also checked in MuPDF as a second engine. Still manual, owner: open a sample PDF in Acrobat Reader and Edge, and print one from an Android phone onto A4 (set PRINT_QA_OUT to get the exact files).</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="23.25" customHeight="1" s="38">
       <c r="A111" s="51" t="inlineStr">
